--- a/fifa_latest.xlsx
+++ b/fifa_latest.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="212">
   <si>
     <t>NAME</t>
   </si>
@@ -28,34 +28,13 @@
     <t>TOTAL GOALS</t>
   </si>
   <si>
-    <t>QF1</t>
-  </si>
-  <si>
-    <t>QF2</t>
-  </si>
-  <si>
-    <t>QF3</t>
-  </si>
-  <si>
-    <t>QF4</t>
-  </si>
-  <si>
     <t>ABU (ECE)</t>
-  </si>
-  <si>
-    <t>DRA</t>
   </si>
   <si>
     <t>POR</t>
   </si>
   <si>
-    <t>ABY (ECE)</t>
-  </si>
-  <si>
-    <t>AUS</t>
-  </si>
-  <si>
-    <t>ENG</t>
+    <t>CRO</t>
   </si>
   <si>
     <t>GHA</t>
@@ -67,13 +46,16 @@
     <t>CZE</t>
   </si>
   <si>
+    <t>ABY (ECE)</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
     <t>AJITH (ME)</t>
   </si>
   <si>
     <t>ALBIN (ECE)</t>
-  </si>
-  <si>
-    <t>CRO</t>
   </si>
   <si>
     <t>ANISH J (ME)</t>
@@ -161,6 +143,9 @@
   </si>
   <si>
     <t>VINU (EEE)</t>
+  </si>
+  <si>
+    <t>DRA</t>
   </si>
   <si>
     <t>RULES:</t>
@@ -649,7 +634,7 @@
     <t>Final: Winner Match 101 vs Winner Match 102</t>
   </si>
   <si>
-    <t>*AFTER 1⃣9⃣ MATCHES*</t>
+    <t>*AFTER 2⃣0⃣ MATCHES*</t>
   </si>
   <si>
     <t>PARTICIPANTS</t>
@@ -770,9 +755,9 @@
       </bottom>
     </border>
     <border>
-      <left style="thin">
+      <right style="thin">
         <color rgb="FF000000"/>
-      </left>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -781,9 +766,9 @@
       </bottom>
     </border>
     <border>
-      <right style="thin">
+      <left style="thin">
         <color rgb="FF000000"/>
-      </right>
+      </left>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -886,13 +871,19 @@
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -904,16 +895,10 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -926,10 +911,10 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -944,23 +929,23 @@
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
@@ -972,7 +957,7 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1353,26 +1338,9 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="12.0"/>
     <col customWidth="1" min="2" max="2" width="8.75"/>
-    <col customWidth="1" min="3" max="6" width="2.63"/>
-    <col customWidth="1" min="7" max="8" width="5.13"/>
-    <col customWidth="1" min="9" max="9" width="8.0"/>
-    <col customWidth="1" min="10" max="10" width="6.63"/>
-    <col customWidth="1" min="11" max="11" width="5.13"/>
-    <col customWidth="1" min="12" max="12" width="3.88"/>
-    <col customWidth="1" min="13" max="13" width="3.75"/>
-    <col customWidth="1" min="14" max="14" width="4.25"/>
-    <col customWidth="1" min="15" max="15" width="7.0"/>
-    <col customWidth="1" min="16" max="17" width="4.5"/>
-    <col customWidth="1" min="18" max="18" width="4.63"/>
-    <col customWidth="1" min="19" max="19" width="4.0"/>
-    <col customWidth="1" min="20" max="20" width="7.25"/>
-    <col customWidth="1" min="21" max="21" width="8.63"/>
-    <col customWidth="1" min="22" max="22" width="4.38"/>
-    <col customWidth="1" min="23" max="23" width="4.0"/>
-    <col customWidth="1" min="24" max="24" width="8.13"/>
-    <col customWidth="1" min="25" max="25" width="4.75"/>
-    <col customWidth="1" min="26" max="26" width="5.63"/>
-    <col customWidth="1" min="27" max="27" width="5.25"/>
+    <col customWidth="1" min="3" max="21" width="2.25"/>
+    <col customWidth="1" min="22" max="22" width="3.13"/>
+    <col customWidth="1" min="23" max="27" width="5.75"/>
     <col customWidth="1" min="28" max="62" width="3.25"/>
     <col customWidth="1" min="63" max="63" width="4.5"/>
   </cols>
@@ -1536,19 +1504,19 @@
       </c>
       <c r="X2" s="11">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y2" s="11">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z2" s="11">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA2" s="11">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB2" s="11">
         <f t="shared" si="1"/>
@@ -1867,27 +1835,29 @@
       <c r="BF3" s="13">
         <v>56.0</v>
       </c>
-      <c r="BG3" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="BH3" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="BI3" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="BJ3" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="BK3" s="14"/>
+      <c r="BG3" s="13">
+        <v>57.0</v>
+      </c>
+      <c r="BH3" s="13">
+        <v>58.0</v>
+      </c>
+      <c r="BI3" s="13">
+        <v>59.0</v>
+      </c>
+      <c r="BJ3" s="14">
+        <v>60.0</v>
+      </c>
+      <c r="BK3" s="14">
+        <v>61.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="15" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B4" s="16">
         <f t="shared" ref="B4:B33" si="2">sum(C4:BJ4)</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="16">
         <v>-1.0</v>
@@ -1946,16 +1916,24 @@
       <c r="U4" s="20">
         <v>2.0</v>
       </c>
-      <c r="V4" s="15" t="s">
+      <c r="V4" s="15">
+        <v>-1.0</v>
+      </c>
+      <c r="W4" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="X4" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y4" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z4" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="W4" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="X4" s="20"/>
-      <c r="Y4" s="20"/>
-      <c r="Z4" s="20"/>
-      <c r="AA4" s="20"/>
       <c r="AB4" s="19"/>
       <c r="AC4" s="15"/>
       <c r="AD4" s="15"/>
@@ -1965,7 +1943,7 @@
       <c r="AH4" s="15"/>
       <c r="AI4" s="20"/>
       <c r="AJ4" s="20"/>
-      <c r="AK4" s="21"/>
+      <c r="AK4" s="23"/>
       <c r="AL4" s="20"/>
       <c r="AM4" s="18"/>
       <c r="AN4" s="15"/>
@@ -1973,33 +1951,33 @@
       <c r="AP4" s="15"/>
       <c r="AQ4" s="20"/>
       <c r="AR4" s="20"/>
-      <c r="AS4" s="22"/>
+      <c r="AS4" s="24"/>
       <c r="AT4" s="15"/>
       <c r="AU4" s="15"/>
       <c r="AV4" s="15"/>
       <c r="AW4" s="15"/>
       <c r="AX4" s="15"/>
-      <c r="AY4" s="22"/>
-      <c r="AZ4" s="22"/>
+      <c r="AY4" s="24"/>
+      <c r="AZ4" s="24"/>
       <c r="BA4" s="15"/>
       <c r="BB4" s="15"/>
       <c r="BC4" s="15"/>
       <c r="BD4" s="15"/>
       <c r="BE4" s="18"/>
-      <c r="BF4" s="23"/>
-      <c r="BG4" s="24"/>
-      <c r="BH4" s="24"/>
-      <c r="BI4" s="24"/>
-      <c r="BJ4" s="24"/>
-      <c r="BK4" s="25"/>
+      <c r="BF4" s="25"/>
+      <c r="BG4" s="26"/>
+      <c r="BH4" s="26"/>
+      <c r="BI4" s="26"/>
+      <c r="BJ4" s="26"/>
+      <c r="BK4" s="27"/>
     </row>
     <row r="5">
       <c r="A5" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="16">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="15">
@@ -2056,23 +2034,23 @@
       <c r="U5" s="20">
         <v>2.0</v>
       </c>
-      <c r="V5" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="W5" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X5" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y5" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z5" s="28" t="s">
-        <v>15</v>
+      <c r="V5" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="W5" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="X5" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y5" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z5" s="22" t="s">
+        <v>8</v>
       </c>
       <c r="AA5" s="29" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AB5" s="30"/>
       <c r="AC5" s="31"/>
@@ -2083,7 +2061,7 @@
       <c r="AH5" s="15"/>
       <c r="AI5" s="20"/>
       <c r="AJ5" s="20"/>
-      <c r="AK5" s="21"/>
+      <c r="AK5" s="23"/>
       <c r="AL5" s="20"/>
       <c r="AM5" s="18"/>
       <c r="AN5" s="15"/>
@@ -2091,33 +2069,33 @@
       <c r="AP5" s="18"/>
       <c r="AQ5" s="20"/>
       <c r="AR5" s="20"/>
-      <c r="AS5" s="22"/>
+      <c r="AS5" s="24"/>
       <c r="AT5" s="15"/>
       <c r="AU5" s="15"/>
       <c r="AV5" s="15"/>
       <c r="AW5" s="15"/>
       <c r="AX5" s="15"/>
-      <c r="AY5" s="22"/>
-      <c r="AZ5" s="22"/>
+      <c r="AY5" s="24"/>
+      <c r="AZ5" s="24"/>
       <c r="BA5" s="15"/>
       <c r="BB5" s="15"/>
       <c r="BC5" s="15"/>
       <c r="BD5" s="15"/>
       <c r="BE5" s="18"/>
-      <c r="BF5" s="23"/>
+      <c r="BF5" s="25"/>
       <c r="BG5" s="32"/>
-      <c r="BH5" s="24"/>
+      <c r="BH5" s="26"/>
       <c r="BI5" s="33"/>
-      <c r="BJ5" s="24"/>
-      <c r="BK5" s="25"/>
+      <c r="BJ5" s="26"/>
+      <c r="BK5" s="27"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B6" s="16">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="15">
@@ -2174,23 +2152,23 @@
       <c r="U6" s="20">
         <v>2.0</v>
       </c>
-      <c r="V6" s="15" t="s">
-        <v>12</v>
+      <c r="V6" s="18">
+        <v>2.0</v>
       </c>
       <c r="W6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="X6" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y6" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z6" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA6" s="28" t="s">
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="X6" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y6" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z6" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA6" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="AB6" s="19"/>
       <c r="AC6" s="34"/>
@@ -2201,7 +2179,7 @@
       <c r="AH6" s="15"/>
       <c r="AI6" s="20"/>
       <c r="AJ6" s="20"/>
-      <c r="AK6" s="21"/>
+      <c r="AK6" s="23"/>
       <c r="AL6" s="20"/>
       <c r="AM6" s="18"/>
       <c r="AN6" s="15"/>
@@ -2209,33 +2187,33 @@
       <c r="AP6" s="15"/>
       <c r="AQ6" s="20"/>
       <c r="AR6" s="20"/>
-      <c r="AS6" s="22"/>
+      <c r="AS6" s="24"/>
       <c r="AT6" s="15"/>
       <c r="AU6" s="15"/>
       <c r="AV6" s="15"/>
       <c r="AW6" s="15"/>
       <c r="AX6" s="15"/>
-      <c r="AY6" s="22"/>
-      <c r="AZ6" s="22"/>
+      <c r="AY6" s="24"/>
+      <c r="AZ6" s="24"/>
       <c r="BA6" s="15"/>
       <c r="BB6" s="15"/>
       <c r="BC6" s="15"/>
       <c r="BD6" s="15"/>
       <c r="BE6" s="18"/>
-      <c r="BF6" s="23"/>
-      <c r="BG6" s="24"/>
-      <c r="BH6" s="24"/>
-      <c r="BI6" s="24"/>
-      <c r="BJ6" s="24"/>
-      <c r="BK6" s="25"/>
+      <c r="BF6" s="25"/>
+      <c r="BG6" s="26"/>
+      <c r="BH6" s="26"/>
+      <c r="BI6" s="26"/>
+      <c r="BJ6" s="26"/>
+      <c r="BK6" s="27"/>
     </row>
     <row r="7">
       <c r="A7" s="15" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B7" s="16">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="16">
         <v>2.0</v>
@@ -2268,7 +2246,7 @@
       <c r="M7" s="16">
         <v>-1.0</v>
       </c>
-      <c r="N7" s="21">
+      <c r="N7" s="23">
         <v>-1.0</v>
       </c>
       <c r="O7" s="16">
@@ -2292,23 +2270,23 @@
       <c r="U7" s="20">
         <v>2.0</v>
       </c>
-      <c r="V7" s="36" t="s">
-        <v>12</v>
+      <c r="V7" s="18">
+        <v>2.0</v>
       </c>
       <c r="W7" s="36" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X7" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y7" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z7" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA7" s="28" t="s">
-        <v>16</v>
+        <v>6</v>
+      </c>
+      <c r="Y7" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z7" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA7" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="AB7" s="19"/>
       <c r="AC7" s="34"/>
@@ -2327,33 +2305,33 @@
       <c r="AP7" s="15"/>
       <c r="AQ7" s="20"/>
       <c r="AR7" s="20"/>
-      <c r="AS7" s="22"/>
+      <c r="AS7" s="24"/>
       <c r="AT7" s="15"/>
       <c r="AU7" s="15"/>
       <c r="AV7" s="15"/>
       <c r="AW7" s="15"/>
       <c r="AX7" s="15"/>
-      <c r="AY7" s="22"/>
-      <c r="AZ7" s="22"/>
+      <c r="AY7" s="24"/>
+      <c r="AZ7" s="24"/>
       <c r="BA7" s="15"/>
       <c r="BB7" s="15"/>
       <c r="BC7" s="18"/>
       <c r="BD7" s="15"/>
       <c r="BE7" s="18"/>
-      <c r="BF7" s="23"/>
-      <c r="BG7" s="24"/>
+      <c r="BF7" s="25"/>
+      <c r="BG7" s="26"/>
       <c r="BH7" s="32"/>
-      <c r="BI7" s="24"/>
-      <c r="BJ7" s="24"/>
-      <c r="BK7" s="25"/>
+      <c r="BI7" s="26"/>
+      <c r="BJ7" s="26"/>
+      <c r="BK7" s="27"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B8" s="16">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="37"/>
       <c r="D8" s="31"/>
@@ -2408,23 +2386,23 @@
       <c r="U8" s="20">
         <v>2.0</v>
       </c>
-      <c r="V8" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="W8" s="26" t="s">
-        <v>10</v>
+      <c r="V8" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="W8" s="28" t="s">
+        <v>5</v>
       </c>
       <c r="X8" s="20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y8" s="20" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Z8" s="20" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AA8" s="20" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AB8" s="19"/>
       <c r="AC8" s="34"/>
@@ -2435,7 +2413,7 @@
       <c r="AH8" s="15"/>
       <c r="AI8" s="15"/>
       <c r="AJ8" s="20"/>
-      <c r="AK8" s="21"/>
+      <c r="AK8" s="23"/>
       <c r="AL8" s="20"/>
       <c r="AM8" s="31"/>
       <c r="AN8" s="31"/>
@@ -2443,33 +2421,33 @@
       <c r="AP8" s="31"/>
       <c r="AQ8" s="20"/>
       <c r="AR8" s="20"/>
-      <c r="AS8" s="22"/>
+      <c r="AS8" s="24"/>
       <c r="AT8" s="15"/>
       <c r="AU8" s="15"/>
       <c r="AV8" s="15"/>
       <c r="AW8" s="15"/>
       <c r="AX8" s="15"/>
-      <c r="AY8" s="22"/>
-      <c r="AZ8" s="22"/>
+      <c r="AY8" s="24"/>
+      <c r="AZ8" s="24"/>
       <c r="BA8" s="15"/>
       <c r="BB8" s="15"/>
       <c r="BC8" s="31"/>
       <c r="BD8" s="31"/>
       <c r="BE8" s="18"/>
-      <c r="BF8" s="23"/>
-      <c r="BG8" s="24"/>
+      <c r="BF8" s="25"/>
+      <c r="BG8" s="26"/>
       <c r="BH8" s="32"/>
-      <c r="BI8" s="24"/>
-      <c r="BJ8" s="24"/>
-      <c r="BK8" s="25"/>
+      <c r="BI8" s="26"/>
+      <c r="BJ8" s="26"/>
+      <c r="BK8" s="27"/>
     </row>
     <row r="9">
       <c r="A9" s="15" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B9" s="16">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" s="16">
         <v>2.0</v>
@@ -2528,23 +2506,23 @@
       <c r="U9" s="20">
         <v>2.0</v>
       </c>
-      <c r="V9" s="36" t="s">
-        <v>12</v>
+      <c r="V9" s="18">
+        <v>2.0</v>
       </c>
       <c r="W9" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="X9" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y9" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z9" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA9" s="28" t="s">
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="X9" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y9" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z9" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA9" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="AB9" s="19"/>
       <c r="AC9" s="34"/>
@@ -2563,33 +2541,33 @@
       <c r="AP9" s="18"/>
       <c r="AQ9" s="20"/>
       <c r="AR9" s="20"/>
-      <c r="AS9" s="22"/>
+      <c r="AS9" s="24"/>
       <c r="AT9" s="15"/>
       <c r="AU9" s="15"/>
       <c r="AV9" s="15"/>
       <c r="AW9" s="15"/>
       <c r="AX9" s="15"/>
-      <c r="AY9" s="22"/>
-      <c r="AZ9" s="22"/>
+      <c r="AY9" s="24"/>
+      <c r="AZ9" s="24"/>
       <c r="BA9" s="15"/>
       <c r="BB9" s="15"/>
       <c r="BC9" s="15"/>
       <c r="BD9" s="15"/>
       <c r="BE9" s="18"/>
-      <c r="BF9" s="23"/>
-      <c r="BG9" s="24"/>
-      <c r="BH9" s="24"/>
-      <c r="BI9" s="24"/>
+      <c r="BF9" s="25"/>
+      <c r="BG9" s="26"/>
+      <c r="BH9" s="26"/>
+      <c r="BI9" s="26"/>
       <c r="BJ9" s="38"/>
       <c r="BK9" s="39"/>
     </row>
     <row r="10">
       <c r="A10" s="15" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B10" s="16">
         <f t="shared" si="2"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" s="16">
         <v>2.0</v>
@@ -2648,23 +2626,23 @@
       <c r="U10" s="20">
         <v>2.0</v>
       </c>
-      <c r="V10" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="W10" s="26" t="s">
-        <v>10</v>
+      <c r="V10" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="W10" s="28" t="s">
+        <v>5</v>
       </c>
       <c r="X10" s="40" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y10" s="29" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Z10" s="29" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AA10" s="29" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AB10" s="19"/>
       <c r="AC10" s="34"/>
@@ -2683,33 +2661,33 @@
       <c r="AP10" s="18"/>
       <c r="AQ10" s="20"/>
       <c r="AR10" s="20"/>
-      <c r="AS10" s="22"/>
+      <c r="AS10" s="24"/>
       <c r="AT10" s="15"/>
       <c r="AU10" s="15"/>
       <c r="AV10" s="15"/>
       <c r="AW10" s="15"/>
       <c r="AX10" s="15"/>
-      <c r="AY10" s="22"/>
-      <c r="AZ10" s="22"/>
+      <c r="AY10" s="24"/>
+      <c r="AZ10" s="24"/>
       <c r="BA10" s="15"/>
       <c r="BB10" s="15"/>
       <c r="BC10" s="15"/>
       <c r="BD10" s="15"/>
       <c r="BE10" s="15"/>
       <c r="BF10" s="41"/>
-      <c r="BG10" s="24"/>
-      <c r="BH10" s="24"/>
+      <c r="BG10" s="26"/>
+      <c r="BH10" s="26"/>
       <c r="BI10" s="33"/>
       <c r="BJ10" s="38"/>
       <c r="BK10" s="39"/>
     </row>
     <row r="11">
       <c r="A11" s="15" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B11" s="16">
         <f t="shared" si="2"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" s="16">
         <v>2.0</v>
@@ -2768,11 +2746,11 @@
       <c r="U11" s="20">
         <v>2.0</v>
       </c>
-      <c r="V11" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="W11" s="26" t="s">
-        <v>10</v>
+      <c r="V11" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="W11" s="28" t="s">
+        <v>5</v>
       </c>
       <c r="X11" s="20"/>
       <c r="Y11" s="20"/>
@@ -2795,29 +2773,29 @@
       <c r="AP11" s="15"/>
       <c r="AQ11" s="20"/>
       <c r="AR11" s="20"/>
-      <c r="AS11" s="22"/>
+      <c r="AS11" s="24"/>
       <c r="AT11" s="15"/>
       <c r="AU11" s="15"/>
       <c r="AV11" s="15"/>
       <c r="AW11" s="15"/>
       <c r="AX11" s="15"/>
-      <c r="AY11" s="22"/>
-      <c r="AZ11" s="22"/>
+      <c r="AY11" s="24"/>
+      <c r="AZ11" s="24"/>
       <c r="BA11" s="15"/>
       <c r="BB11" s="15"/>
       <c r="BC11" s="18"/>
       <c r="BD11" s="15"/>
       <c r="BE11" s="18"/>
-      <c r="BF11" s="23"/>
-      <c r="BG11" s="24"/>
-      <c r="BH11" s="24"/>
-      <c r="BI11" s="24"/>
-      <c r="BJ11" s="24"/>
-      <c r="BK11" s="25"/>
+      <c r="BF11" s="25"/>
+      <c r="BG11" s="26"/>
+      <c r="BH11" s="26"/>
+      <c r="BI11" s="26"/>
+      <c r="BJ11" s="26"/>
+      <c r="BK11" s="27"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B12" s="16">
         <f t="shared" si="2"/>
@@ -2860,7 +2838,7 @@
       <c r="U12" s="31"/>
       <c r="V12" s="31"/>
       <c r="W12" s="15" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X12" s="31"/>
       <c r="Y12" s="31"/>
@@ -2899,17 +2877,17 @@
       <c r="BF12" s="43"/>
       <c r="BG12" s="32"/>
       <c r="BH12" s="32"/>
-      <c r="BI12" s="24"/>
-      <c r="BJ12" s="24"/>
-      <c r="BK12" s="25"/>
+      <c r="BI12" s="26"/>
+      <c r="BJ12" s="26"/>
+      <c r="BK12" s="27"/>
     </row>
     <row r="13">
       <c r="A13" s="15" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B13" s="16">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" s="16">
         <v>2.0</v>
@@ -2968,23 +2946,23 @@
       <c r="U13" s="20">
         <v>2.0</v>
       </c>
-      <c r="V13" s="36" t="s">
-        <v>12</v>
+      <c r="V13" s="18">
+        <v>2.0</v>
       </c>
       <c r="W13" s="36" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X13" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y13" s="28" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="Y13" s="22" t="s">
+        <v>7</v>
       </c>
       <c r="Z13" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA13" s="28" t="s">
-        <v>16</v>
+        <v>21</v>
+      </c>
+      <c r="AA13" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="AB13" s="19"/>
       <c r="AC13" s="34"/>
@@ -2995,7 +2973,7 @@
       <c r="AH13" s="15"/>
       <c r="AI13" s="20"/>
       <c r="AJ13" s="20"/>
-      <c r="AK13" s="21"/>
+      <c r="AK13" s="23"/>
       <c r="AL13" s="20"/>
       <c r="AM13" s="18"/>
       <c r="AN13" s="15"/>
@@ -3003,33 +2981,33 @@
       <c r="AP13" s="15"/>
       <c r="AQ13" s="20"/>
       <c r="AR13" s="20"/>
-      <c r="AS13" s="22"/>
+      <c r="AS13" s="24"/>
       <c r="AT13" s="15"/>
       <c r="AU13" s="15"/>
       <c r="AV13" s="15"/>
       <c r="AW13" s="15"/>
       <c r="AX13" s="15"/>
-      <c r="AY13" s="22"/>
-      <c r="AZ13" s="22"/>
+      <c r="AY13" s="24"/>
+      <c r="AZ13" s="24"/>
       <c r="BA13" s="15"/>
       <c r="BB13" s="15"/>
       <c r="BC13" s="18"/>
       <c r="BD13" s="15"/>
       <c r="BE13" s="18"/>
-      <c r="BF13" s="23"/>
-      <c r="BG13" s="24"/>
-      <c r="BH13" s="24"/>
-      <c r="BI13" s="24"/>
-      <c r="BJ13" s="24"/>
-      <c r="BK13" s="25"/>
+      <c r="BF13" s="25"/>
+      <c r="BG13" s="26"/>
+      <c r="BH13" s="26"/>
+      <c r="BI13" s="26"/>
+      <c r="BJ13" s="26"/>
+      <c r="BK13" s="27"/>
     </row>
     <row r="14">
       <c r="A14" s="15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B14" s="16">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C14" s="16">
         <v>2.0</v>
@@ -3088,23 +3066,23 @@
       <c r="U14" s="20">
         <v>2.0</v>
       </c>
-      <c r="V14" s="30" t="s">
-        <v>12</v>
+      <c r="V14" s="18">
+        <v>2.0</v>
       </c>
       <c r="W14" s="30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X14" s="20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y14" s="20" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Z14" s="20" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AA14" s="20" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AB14" s="31"/>
       <c r="AC14" s="31"/>
@@ -3123,33 +3101,33 @@
       <c r="AP14" s="15"/>
       <c r="AQ14" s="20"/>
       <c r="AR14" s="20"/>
-      <c r="AS14" s="22"/>
+      <c r="AS14" s="24"/>
       <c r="AT14" s="15"/>
       <c r="AU14" s="15"/>
       <c r="AV14" s="15"/>
       <c r="AW14" s="15"/>
       <c r="AX14" s="15"/>
-      <c r="AY14" s="22"/>
-      <c r="AZ14" s="22"/>
+      <c r="AY14" s="24"/>
+      <c r="AZ14" s="24"/>
       <c r="BA14" s="15"/>
       <c r="BB14" s="15"/>
       <c r="BC14" s="15"/>
       <c r="BD14" s="15"/>
       <c r="BE14" s="18"/>
-      <c r="BF14" s="23"/>
-      <c r="BG14" s="24"/>
-      <c r="BH14" s="24"/>
-      <c r="BI14" s="24"/>
-      <c r="BJ14" s="24"/>
-      <c r="BK14" s="25"/>
+      <c r="BF14" s="25"/>
+      <c r="BG14" s="26"/>
+      <c r="BH14" s="26"/>
+      <c r="BI14" s="26"/>
+      <c r="BJ14" s="26"/>
+      <c r="BK14" s="27"/>
     </row>
     <row r="15">
       <c r="A15" s="15" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B15" s="16">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C15" s="16">
         <v>2.0</v>
@@ -3208,23 +3186,23 @@
       <c r="U15" s="20">
         <v>2.0</v>
       </c>
-      <c r="V15" s="36" t="s">
-        <v>12</v>
+      <c r="V15" s="18">
+        <v>2.0</v>
       </c>
       <c r="W15" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="X15" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y15" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z15" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA15" s="28" t="s">
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="X15" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y15" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z15" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA15" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="AB15" s="19"/>
       <c r="AC15" s="34"/>
@@ -3243,33 +3221,33 @@
       <c r="AP15" s="15"/>
       <c r="AQ15" s="20"/>
       <c r="AR15" s="20"/>
-      <c r="AS15" s="22"/>
+      <c r="AS15" s="24"/>
       <c r="AT15" s="15"/>
       <c r="AU15" s="15"/>
       <c r="AV15" s="15"/>
       <c r="AW15" s="15"/>
       <c r="AX15" s="15"/>
-      <c r="AY15" s="22"/>
-      <c r="AZ15" s="22"/>
+      <c r="AY15" s="24"/>
+      <c r="AZ15" s="24"/>
       <c r="BA15" s="15"/>
       <c r="BB15" s="15"/>
       <c r="BC15" s="18"/>
       <c r="BD15" s="15"/>
       <c r="BE15" s="18"/>
-      <c r="BF15" s="23"/>
-      <c r="BG15" s="24"/>
-      <c r="BH15" s="24"/>
-      <c r="BI15" s="24"/>
+      <c r="BF15" s="25"/>
+      <c r="BG15" s="26"/>
+      <c r="BH15" s="26"/>
+      <c r="BI15" s="26"/>
       <c r="BJ15" s="38"/>
       <c r="BK15" s="39"/>
     </row>
     <row r="16">
       <c r="A16" s="44" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B16" s="16">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C16" s="16">
         <v>2.0</v>
@@ -3326,23 +3304,23 @@
       <c r="U16" s="20">
         <v>2.0</v>
       </c>
-      <c r="V16" s="36" t="s">
-        <v>12</v>
+      <c r="V16" s="18">
+        <v>2.0</v>
       </c>
       <c r="W16" s="36" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X16" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y16" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z16" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA16" s="28" t="s">
-        <v>16</v>
+        <v>6</v>
+      </c>
+      <c r="Y16" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z16" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA16" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="AB16" s="19"/>
       <c r="AC16" s="34"/>
@@ -3361,33 +3339,33 @@
       <c r="AP16" s="40"/>
       <c r="AQ16" s="20"/>
       <c r="AR16" s="20"/>
-      <c r="AS16" s="22"/>
+      <c r="AS16" s="24"/>
       <c r="AT16" s="15"/>
       <c r="AU16" s="15"/>
       <c r="AV16" s="15"/>
       <c r="AW16" s="15"/>
       <c r="AX16" s="15"/>
-      <c r="AY16" s="22"/>
-      <c r="AZ16" s="22"/>
+      <c r="AY16" s="24"/>
+      <c r="AZ16" s="24"/>
       <c r="BA16" s="15"/>
       <c r="BB16" s="15"/>
       <c r="BC16" s="18"/>
       <c r="BD16" s="15"/>
       <c r="BE16" s="18"/>
-      <c r="BF16" s="23"/>
-      <c r="BG16" s="24"/>
-      <c r="BH16" s="24"/>
-      <c r="BI16" s="24"/>
-      <c r="BJ16" s="24"/>
-      <c r="BK16" s="25"/>
+      <c r="BF16" s="25"/>
+      <c r="BG16" s="26"/>
+      <c r="BH16" s="26"/>
+      <c r="BI16" s="26"/>
+      <c r="BJ16" s="26"/>
+      <c r="BK16" s="27"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B17" s="16">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C17" s="16">
         <v>2.0</v>
@@ -3446,23 +3424,23 @@
       <c r="U17" s="20">
         <v>2.0</v>
       </c>
-      <c r="V17" s="36" t="s">
-        <v>12</v>
+      <c r="V17" s="18">
+        <v>2.0</v>
       </c>
       <c r="W17" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="X17" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y17" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z17" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA17" s="28" t="s">
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="X17" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y17" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z17" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA17" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="AB17" s="19"/>
       <c r="AC17" s="34"/>
@@ -3473,7 +3451,7 @@
       <c r="AH17" s="15"/>
       <c r="AI17" s="20"/>
       <c r="AJ17" s="20"/>
-      <c r="AK17" s="21"/>
+      <c r="AK17" s="23"/>
       <c r="AL17" s="20"/>
       <c r="AM17" s="18"/>
       <c r="AN17" s="15"/>
@@ -3481,33 +3459,33 @@
       <c r="AP17" s="15"/>
       <c r="AQ17" s="20"/>
       <c r="AR17" s="20"/>
-      <c r="AS17" s="22"/>
+      <c r="AS17" s="24"/>
       <c r="AT17" s="15"/>
       <c r="AU17" s="15"/>
       <c r="AV17" s="15"/>
       <c r="AW17" s="15"/>
       <c r="AX17" s="15"/>
-      <c r="AY17" s="22"/>
-      <c r="AZ17" s="22"/>
+      <c r="AY17" s="24"/>
+      <c r="AZ17" s="24"/>
       <c r="BA17" s="15"/>
       <c r="BB17" s="15"/>
       <c r="BC17" s="15"/>
       <c r="BD17" s="15"/>
       <c r="BE17" s="18"/>
-      <c r="BF17" s="23"/>
-      <c r="BG17" s="24"/>
-      <c r="BH17" s="24"/>
-      <c r="BI17" s="24"/>
-      <c r="BJ17" s="24"/>
-      <c r="BK17" s="25"/>
+      <c r="BF17" s="25"/>
+      <c r="BG17" s="26"/>
+      <c r="BH17" s="26"/>
+      <c r="BI17" s="26"/>
+      <c r="BJ17" s="26"/>
+      <c r="BK17" s="27"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B18" s="16">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C18" s="16">
         <v>2.0</v>
@@ -3566,23 +3544,23 @@
       <c r="U18" s="20">
         <v>2.0</v>
       </c>
-      <c r="V18" s="36" t="s">
-        <v>12</v>
+      <c r="V18" s="18">
+        <v>2.0</v>
       </c>
       <c r="W18" s="36" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X18" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y18" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z18" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA18" s="28" t="s">
-        <v>16</v>
+        <v>6</v>
+      </c>
+      <c r="Y18" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z18" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA18" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="AB18" s="19"/>
       <c r="AC18" s="34"/>
@@ -3601,33 +3579,33 @@
       <c r="AP18" s="15"/>
       <c r="AQ18" s="20"/>
       <c r="AR18" s="20"/>
-      <c r="AS18" s="22"/>
+      <c r="AS18" s="24"/>
       <c r="AT18" s="15"/>
       <c r="AU18" s="15"/>
       <c r="AV18" s="15"/>
       <c r="AW18" s="15"/>
       <c r="AX18" s="15"/>
-      <c r="AY18" s="22"/>
-      <c r="AZ18" s="22"/>
+      <c r="AY18" s="24"/>
+      <c r="AZ18" s="24"/>
       <c r="BA18" s="15"/>
       <c r="BB18" s="15"/>
       <c r="BC18" s="18"/>
       <c r="BD18" s="15"/>
       <c r="BE18" s="18"/>
-      <c r="BF18" s="23"/>
-      <c r="BG18" s="24"/>
-      <c r="BH18" s="24"/>
-      <c r="BI18" s="24"/>
-      <c r="BJ18" s="24"/>
-      <c r="BK18" s="25"/>
+      <c r="BF18" s="25"/>
+      <c r="BG18" s="26"/>
+      <c r="BH18" s="26"/>
+      <c r="BI18" s="26"/>
+      <c r="BJ18" s="26"/>
+      <c r="BK18" s="27"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B19" s="16">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C19" s="16">
         <v>2.0</v>
@@ -3686,23 +3664,23 @@
       <c r="U19" s="20">
         <v>2.0</v>
       </c>
-      <c r="V19" s="30" t="s">
-        <v>12</v>
+      <c r="V19" s="18">
+        <v>2.0</v>
       </c>
       <c r="W19" s="30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X19" s="40" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y19" s="29" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Z19" s="29" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AA19" s="29" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AB19" s="30"/>
       <c r="AC19" s="31"/>
@@ -3727,7 +3705,7 @@
       <c r="AV19" s="31"/>
       <c r="AW19" s="31"/>
       <c r="AX19" s="31"/>
-      <c r="AY19" s="22"/>
+      <c r="AY19" s="24"/>
       <c r="AZ19" s="15"/>
       <c r="BA19" s="15"/>
       <c r="BB19" s="15"/>
@@ -3742,11 +3720,11 @@
     </row>
     <row r="20">
       <c r="A20" s="15" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B20" s="16">
         <f t="shared" si="2"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C20" s="16">
         <v>2.0</v>
@@ -3805,23 +3783,23 @@
       <c r="U20" s="20">
         <v>2.0</v>
       </c>
-      <c r="V20" s="36" t="s">
-        <v>12</v>
+      <c r="V20" s="18">
+        <v>2.0</v>
       </c>
       <c r="W20" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="X20" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y20" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z20" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA20" s="28" t="s">
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="X20" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y20" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z20" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA20" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="AB20" s="19"/>
       <c r="AC20" s="34"/>
@@ -3832,7 +3810,7 @@
       <c r="AH20" s="15"/>
       <c r="AI20" s="20"/>
       <c r="AJ20" s="20"/>
-      <c r="AK20" s="21"/>
+      <c r="AK20" s="23"/>
       <c r="AL20" s="20"/>
       <c r="AM20" s="18"/>
       <c r="AN20" s="15"/>
@@ -3840,33 +3818,33 @@
       <c r="AP20" s="18"/>
       <c r="AQ20" s="20"/>
       <c r="AR20" s="20"/>
-      <c r="AS20" s="22"/>
+      <c r="AS20" s="24"/>
       <c r="AT20" s="15"/>
-      <c r="AU20" s="22"/>
+      <c r="AU20" s="24"/>
       <c r="AV20" s="15"/>
       <c r="AW20" s="15"/>
       <c r="AX20" s="15"/>
-      <c r="AY20" s="22"/>
-      <c r="AZ20" s="22"/>
+      <c r="AY20" s="24"/>
+      <c r="AZ20" s="24"/>
       <c r="BA20" s="15"/>
       <c r="BB20" s="15"/>
       <c r="BC20" s="15"/>
       <c r="BD20" s="15"/>
       <c r="BE20" s="18"/>
-      <c r="BF20" s="23"/>
-      <c r="BG20" s="24"/>
-      <c r="BH20" s="24"/>
-      <c r="BI20" s="24"/>
+      <c r="BF20" s="25"/>
+      <c r="BG20" s="26"/>
+      <c r="BH20" s="26"/>
+      <c r="BI20" s="26"/>
       <c r="BJ20" s="38"/>
       <c r="BK20" s="39"/>
     </row>
     <row r="21">
       <c r="A21" s="15" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B21" s="16">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="31"/>
@@ -3921,23 +3899,23 @@
       <c r="U21" s="20">
         <v>2.0</v>
       </c>
-      <c r="V21" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="W21" s="26" t="s">
-        <v>10</v>
+      <c r="V21" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="W21" s="28" t="s">
+        <v>5</v>
       </c>
       <c r="X21" s="20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y21" s="20" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Z21" s="20" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AA21" s="20" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AB21" s="19"/>
       <c r="AC21" s="34"/>
@@ -3948,7 +3926,7 @@
       <c r="AH21" s="15"/>
       <c r="AI21" s="20"/>
       <c r="AJ21" s="20"/>
-      <c r="AK21" s="21"/>
+      <c r="AK21" s="23"/>
       <c r="AL21" s="20"/>
       <c r="AM21" s="18"/>
       <c r="AN21" s="15"/>
@@ -3956,33 +3934,33 @@
       <c r="AP21" s="15"/>
       <c r="AQ21" s="20"/>
       <c r="AR21" s="20"/>
-      <c r="AS21" s="22"/>
+      <c r="AS21" s="24"/>
       <c r="AT21" s="15"/>
       <c r="AU21" s="15"/>
       <c r="AV21" s="15"/>
       <c r="AW21" s="15"/>
       <c r="AX21" s="15"/>
-      <c r="AY21" s="22"/>
-      <c r="AZ21" s="22"/>
+      <c r="AY21" s="24"/>
+      <c r="AZ21" s="24"/>
       <c r="BA21" s="15"/>
       <c r="BB21" s="15"/>
       <c r="BC21" s="15"/>
       <c r="BD21" s="15"/>
       <c r="BE21" s="18"/>
-      <c r="BF21" s="23"/>
-      <c r="BG21" s="24"/>
-      <c r="BH21" s="24"/>
-      <c r="BI21" s="24"/>
-      <c r="BJ21" s="24"/>
-      <c r="BK21" s="25"/>
+      <c r="BF21" s="25"/>
+      <c r="BG21" s="26"/>
+      <c r="BH21" s="26"/>
+      <c r="BI21" s="26"/>
+      <c r="BJ21" s="26"/>
+      <c r="BK21" s="27"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B22" s="16">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C22" s="16">
         <v>2.0</v>
@@ -4041,23 +4019,23 @@
       <c r="U22" s="20">
         <v>2.0</v>
       </c>
-      <c r="V22" s="36" t="s">
-        <v>12</v>
+      <c r="V22" s="18">
+        <v>2.0</v>
       </c>
       <c r="W22" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="X22" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y22" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z22" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA22" s="28" t="s">
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="X22" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y22" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z22" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="AB22" s="15"/>
       <c r="AC22" s="15"/>
@@ -4068,7 +4046,7 @@
       <c r="AH22" s="15"/>
       <c r="AI22" s="20"/>
       <c r="AJ22" s="15"/>
-      <c r="AK22" s="21"/>
+      <c r="AK22" s="23"/>
       <c r="AL22" s="15"/>
       <c r="AM22" s="15"/>
       <c r="AN22" s="15"/>
@@ -4076,33 +4054,33 @@
       <c r="AP22" s="18"/>
       <c r="AQ22" s="20"/>
       <c r="AR22" s="20"/>
-      <c r="AS22" s="22"/>
+      <c r="AS22" s="24"/>
       <c r="AT22" s="15"/>
-      <c r="AU22" s="22"/>
+      <c r="AU22" s="24"/>
       <c r="AV22" s="15"/>
       <c r="AW22" s="15"/>
       <c r="AX22" s="15"/>
-      <c r="AY22" s="22"/>
+      <c r="AY22" s="24"/>
       <c r="AZ22" s="15"/>
       <c r="BA22" s="15"/>
       <c r="BB22" s="15"/>
       <c r="BC22" s="18"/>
       <c r="BD22" s="15"/>
       <c r="BE22" s="18"/>
-      <c r="BF22" s="23"/>
-      <c r="BG22" s="24"/>
+      <c r="BF22" s="25"/>
+      <c r="BG22" s="26"/>
       <c r="BH22" s="32"/>
-      <c r="BI22" s="24"/>
+      <c r="BI22" s="26"/>
       <c r="BJ22" s="38"/>
       <c r="BK22" s="39"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B23" s="16">
         <f t="shared" si="2"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C23" s="16">
         <v>2.0</v>
@@ -4155,23 +4133,23 @@
       <c r="U23" s="20">
         <v>2.0</v>
       </c>
-      <c r="V23" s="30" t="s">
-        <v>12</v>
+      <c r="V23" s="18">
+        <v>2.0</v>
       </c>
       <c r="W23" s="36" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X23" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y23" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z23" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA23" s="28" t="s">
-        <v>16</v>
+        <v>6</v>
+      </c>
+      <c r="Y23" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z23" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA23" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="AB23" s="19"/>
       <c r="AC23" s="34"/>
@@ -4182,7 +4160,7 @@
       <c r="AH23" s="15"/>
       <c r="AI23" s="20"/>
       <c r="AJ23" s="20"/>
-      <c r="AK23" s="21"/>
+      <c r="AK23" s="23"/>
       <c r="AL23" s="20"/>
       <c r="AM23" s="18"/>
       <c r="AN23" s="15"/>
@@ -4190,33 +4168,33 @@
       <c r="AP23" s="15"/>
       <c r="AQ23" s="20"/>
       <c r="AR23" s="20"/>
-      <c r="AS23" s="22"/>
+      <c r="AS23" s="24"/>
       <c r="AT23" s="15"/>
       <c r="AU23" s="15"/>
       <c r="AV23" s="15"/>
       <c r="AW23" s="15"/>
       <c r="AX23" s="15"/>
-      <c r="AY23" s="22"/>
-      <c r="AZ23" s="22"/>
+      <c r="AY23" s="24"/>
+      <c r="AZ23" s="24"/>
       <c r="BA23" s="15"/>
       <c r="BB23" s="15"/>
       <c r="BC23" s="18"/>
       <c r="BD23" s="15"/>
       <c r="BE23" s="18"/>
-      <c r="BF23" s="23"/>
-      <c r="BG23" s="24"/>
-      <c r="BH23" s="24"/>
-      <c r="BI23" s="24"/>
-      <c r="BJ23" s="24"/>
-      <c r="BK23" s="25"/>
+      <c r="BF23" s="25"/>
+      <c r="BG23" s="26"/>
+      <c r="BH23" s="26"/>
+      <c r="BI23" s="26"/>
+      <c r="BJ23" s="26"/>
+      <c r="BK23" s="27"/>
     </row>
     <row r="24">
       <c r="A24" s="15" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B24" s="16">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C24" s="16">
         <v>2.0</v>
@@ -4275,23 +4253,23 @@
       <c r="U24" s="20">
         <v>2.0</v>
       </c>
-      <c r="V24" s="36" t="s">
-        <v>12</v>
+      <c r="V24" s="18">
+        <v>2.0</v>
       </c>
       <c r="W24" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="X24" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y24" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z24" s="28" t="s">
-        <v>15</v>
+        <v>5</v>
+      </c>
+      <c r="X24" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y24" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z24" s="22" t="s">
+        <v>8</v>
       </c>
       <c r="AA24" s="35" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="AB24" s="19"/>
       <c r="AC24" s="34"/>
@@ -4302,7 +4280,7 @@
       <c r="AH24" s="31"/>
       <c r="AI24" s="15"/>
       <c r="AJ24" s="15"/>
-      <c r="AK24" s="21"/>
+      <c r="AK24" s="23"/>
       <c r="AL24" s="20"/>
       <c r="AM24" s="18"/>
       <c r="AN24" s="15"/>
@@ -4310,13 +4288,13 @@
       <c r="AP24" s="18"/>
       <c r="AQ24" s="20"/>
       <c r="AR24" s="20"/>
-      <c r="AS24" s="22"/>
+      <c r="AS24" s="24"/>
       <c r="AT24" s="15"/>
       <c r="AU24" s="15"/>
       <c r="AV24" s="15"/>
       <c r="AW24" s="15"/>
       <c r="AX24" s="15"/>
-      <c r="AY24" s="22"/>
+      <c r="AY24" s="24"/>
       <c r="AZ24" s="15"/>
       <c r="BA24" s="15"/>
       <c r="BB24" s="15"/>
@@ -4327,16 +4305,16 @@
       <c r="BG24" s="32"/>
       <c r="BH24" s="32"/>
       <c r="BI24" s="33"/>
-      <c r="BJ24" s="24"/>
-      <c r="BK24" s="25"/>
+      <c r="BJ24" s="26"/>
+      <c r="BK24" s="27"/>
     </row>
     <row r="25">
       <c r="A25" s="44" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B25" s="16">
         <f t="shared" si="2"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C25" s="16">
         <v>2.0</v>
@@ -4395,11 +4373,11 @@
       <c r="U25" s="20">
         <v>2.0</v>
       </c>
-      <c r="V25" s="36" t="s">
-        <v>12</v>
+      <c r="V25" s="18">
+        <v>2.0</v>
       </c>
       <c r="W25" s="36" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X25" s="20"/>
       <c r="Y25" s="20"/>
@@ -4422,33 +4400,33 @@
       <c r="AP25" s="15"/>
       <c r="AQ25" s="20"/>
       <c r="AR25" s="20"/>
-      <c r="AS25" s="22"/>
+      <c r="AS25" s="24"/>
       <c r="AT25" s="15"/>
-      <c r="AU25" s="22"/>
+      <c r="AU25" s="24"/>
       <c r="AV25" s="15"/>
       <c r="AW25" s="15"/>
       <c r="AX25" s="15"/>
-      <c r="AY25" s="22"/>
-      <c r="AZ25" s="22"/>
+      <c r="AY25" s="24"/>
+      <c r="AZ25" s="24"/>
       <c r="BA25" s="15"/>
       <c r="BB25" s="15"/>
       <c r="BC25" s="15"/>
       <c r="BD25" s="15"/>
       <c r="BE25" s="18"/>
       <c r="BF25" s="41"/>
-      <c r="BG25" s="24"/>
-      <c r="BH25" s="24"/>
-      <c r="BI25" s="24"/>
+      <c r="BG25" s="26"/>
+      <c r="BH25" s="26"/>
+      <c r="BI25" s="26"/>
       <c r="BJ25" s="38"/>
       <c r="BK25" s="39"/>
     </row>
     <row r="26">
       <c r="A26" s="15" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B26" s="16">
         <f t="shared" si="2"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C26" s="16">
         <v>2.0</v>
@@ -4507,23 +4485,23 @@
       <c r="U26" s="20">
         <v>2.0</v>
       </c>
-      <c r="V26" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="W26" s="47" t="s">
-        <v>10</v>
+      <c r="V26" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="W26" s="46" t="s">
+        <v>5</v>
       </c>
       <c r="X26" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y26" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z26" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA26" s="28" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="Y26" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z26" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA26" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="AB26" s="19"/>
       <c r="AC26" s="34"/>
@@ -4534,7 +4512,7 @@
       <c r="AH26" s="15"/>
       <c r="AI26" s="20"/>
       <c r="AJ26" s="20"/>
-      <c r="AK26" s="21"/>
+      <c r="AK26" s="23"/>
       <c r="AL26" s="20"/>
       <c r="AM26" s="18"/>
       <c r="AN26" s="15"/>
@@ -4542,33 +4520,33 @@
       <c r="AP26" s="18"/>
       <c r="AQ26" s="20"/>
       <c r="AR26" s="20"/>
-      <c r="AS26" s="22"/>
+      <c r="AS26" s="24"/>
       <c r="AT26" s="15"/>
       <c r="AU26" s="15"/>
       <c r="AV26" s="15"/>
       <c r="AW26" s="15"/>
       <c r="AX26" s="15"/>
-      <c r="AY26" s="22"/>
-      <c r="AZ26" s="22"/>
+      <c r="AY26" s="24"/>
+      <c r="AZ26" s="24"/>
       <c r="BA26" s="15"/>
       <c r="BB26" s="15"/>
       <c r="BC26" s="18"/>
       <c r="BD26" s="15"/>
       <c r="BE26" s="18"/>
-      <c r="BF26" s="23"/>
-      <c r="BG26" s="24"/>
-      <c r="BH26" s="24"/>
-      <c r="BI26" s="24"/>
-      <c r="BJ26" s="24"/>
-      <c r="BK26" s="25"/>
+      <c r="BF26" s="25"/>
+      <c r="BG26" s="26"/>
+      <c r="BH26" s="26"/>
+      <c r="BI26" s="26"/>
+      <c r="BJ26" s="26"/>
+      <c r="BK26" s="27"/>
     </row>
     <row r="27">
       <c r="A27" s="15" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B27" s="16">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="15"/>
@@ -4619,23 +4597,23 @@
       <c r="U27" s="20">
         <v>2.0</v>
       </c>
-      <c r="V27" s="36" t="s">
-        <v>12</v>
+      <c r="V27" s="18">
+        <v>2.0</v>
       </c>
       <c r="W27" s="36" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X27" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y27" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z27" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA27" s="28" t="s">
-        <v>16</v>
+        <v>6</v>
+      </c>
+      <c r="Y27" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z27" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA27" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="AB27" s="19"/>
       <c r="AC27" s="15"/>
@@ -4654,33 +4632,33 @@
       <c r="AP27" s="15"/>
       <c r="AQ27" s="20"/>
       <c r="AR27" s="20"/>
-      <c r="AS27" s="22"/>
+      <c r="AS27" s="24"/>
       <c r="AT27" s="15"/>
       <c r="AU27" s="15"/>
       <c r="AV27" s="15"/>
       <c r="AW27" s="15"/>
       <c r="AX27" s="15"/>
-      <c r="AY27" s="22"/>
-      <c r="AZ27" s="22"/>
+      <c r="AY27" s="24"/>
+      <c r="AZ27" s="24"/>
       <c r="BA27" s="15"/>
       <c r="BB27" s="15"/>
       <c r="BC27" s="15"/>
       <c r="BD27" s="15"/>
       <c r="BE27" s="18"/>
       <c r="BF27" s="41"/>
-      <c r="BG27" s="24"/>
+      <c r="BG27" s="26"/>
       <c r="BH27" s="32"/>
-      <c r="BI27" s="24"/>
+      <c r="BI27" s="26"/>
       <c r="BJ27" s="38"/>
       <c r="BK27" s="39"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B28" s="16">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="15"/>
@@ -4735,23 +4713,23 @@
       <c r="U28" s="20">
         <v>2.0</v>
       </c>
-      <c r="V28" s="36" t="s">
-        <v>12</v>
+      <c r="V28" s="18">
+        <v>2.0</v>
       </c>
       <c r="W28" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="X28" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y28" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z28" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA28" s="28" t="s">
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="X28" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y28" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z28" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA28" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="AB28" s="19"/>
       <c r="AC28" s="34"/>
@@ -4762,7 +4740,7 @@
       <c r="AH28" s="15"/>
       <c r="AI28" s="20"/>
       <c r="AJ28" s="20"/>
-      <c r="AK28" s="21"/>
+      <c r="AK28" s="23"/>
       <c r="AL28" s="20"/>
       <c r="AM28" s="18"/>
       <c r="AN28" s="15"/>
@@ -4770,33 +4748,33 @@
       <c r="AP28" s="15"/>
       <c r="AQ28" s="20"/>
       <c r="AR28" s="20"/>
-      <c r="AS28" s="22"/>
+      <c r="AS28" s="24"/>
       <c r="AT28" s="15"/>
       <c r="AU28" s="15"/>
       <c r="AV28" s="15"/>
       <c r="AW28" s="15"/>
       <c r="AX28" s="15"/>
-      <c r="AY28" s="22"/>
-      <c r="AZ28" s="22"/>
+      <c r="AY28" s="24"/>
+      <c r="AZ28" s="24"/>
       <c r="BA28" s="15"/>
       <c r="BB28" s="15"/>
       <c r="BC28" s="15"/>
       <c r="BD28" s="15"/>
       <c r="BE28" s="18"/>
-      <c r="BF28" s="23"/>
-      <c r="BG28" s="24"/>
-      <c r="BH28" s="24"/>
-      <c r="BI28" s="24"/>
-      <c r="BJ28" s="24"/>
-      <c r="BK28" s="25"/>
+      <c r="BF28" s="25"/>
+      <c r="BG28" s="26"/>
+      <c r="BH28" s="26"/>
+      <c r="BI28" s="26"/>
+      <c r="BJ28" s="26"/>
+      <c r="BK28" s="27"/>
     </row>
     <row r="29">
       <c r="A29" s="15" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B29" s="16">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="15"/>
@@ -4851,23 +4829,23 @@
       <c r="U29" s="20">
         <v>2.0</v>
       </c>
-      <c r="V29" s="36" t="s">
-        <v>12</v>
+      <c r="V29" s="18">
+        <v>2.0</v>
       </c>
       <c r="W29" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="X29" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y29" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z29" s="28" t="s">
-        <v>15</v>
+        <v>5</v>
+      </c>
+      <c r="X29" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y29" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z29" s="22" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="35" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="AB29" s="19"/>
       <c r="AC29" s="34"/>
@@ -4892,23 +4870,23 @@
       <c r="AV29" s="31"/>
       <c r="AW29" s="31"/>
       <c r="AX29" s="31"/>
-      <c r="AY29" s="22"/>
-      <c r="AZ29" s="22"/>
+      <c r="AY29" s="24"/>
+      <c r="AZ29" s="24"/>
       <c r="BA29" s="31"/>
       <c r="BB29" s="31"/>
       <c r="BC29" s="31"/>
       <c r="BD29" s="31"/>
       <c r="BE29" s="18"/>
-      <c r="BF29" s="23"/>
-      <c r="BG29" s="24"/>
-      <c r="BH29" s="24"/>
-      <c r="BI29" s="24"/>
-      <c r="BJ29" s="24"/>
-      <c r="BK29" s="25"/>
+      <c r="BF29" s="25"/>
+      <c r="BG29" s="26"/>
+      <c r="BH29" s="26"/>
+      <c r="BI29" s="26"/>
+      <c r="BJ29" s="26"/>
+      <c r="BK29" s="27"/>
     </row>
     <row r="30">
       <c r="A30" s="44" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B30" s="16">
         <f t="shared" si="2"/>
@@ -4933,7 +4911,7 @@
       <c r="K30" s="17"/>
       <c r="L30" s="19"/>
       <c r="M30" s="16"/>
-      <c r="N30" s="21"/>
+      <c r="N30" s="23"/>
       <c r="O30" s="16"/>
       <c r="P30" s="15">
         <v>1.0</v>
@@ -4962,7 +4940,7 @@
       <c r="AH30" s="15"/>
       <c r="AI30" s="20"/>
       <c r="AJ30" s="20"/>
-      <c r="AK30" s="21"/>
+      <c r="AK30" s="23"/>
       <c r="AL30" s="20"/>
       <c r="AM30" s="18"/>
       <c r="AN30" s="15"/>
@@ -4970,29 +4948,29 @@
       <c r="AP30" s="18"/>
       <c r="AQ30" s="20"/>
       <c r="AR30" s="20"/>
-      <c r="AS30" s="22"/>
+      <c r="AS30" s="24"/>
       <c r="AT30" s="15"/>
       <c r="AU30" s="15"/>
       <c r="AV30" s="15"/>
       <c r="AW30" s="15"/>
       <c r="AX30" s="15"/>
-      <c r="AY30" s="22"/>
-      <c r="AZ30" s="22"/>
+      <c r="AY30" s="24"/>
+      <c r="AZ30" s="24"/>
       <c r="BA30" s="15"/>
       <c r="BB30" s="15"/>
       <c r="BC30" s="15"/>
       <c r="BD30" s="15"/>
       <c r="BE30" s="18"/>
-      <c r="BF30" s="23"/>
-      <c r="BG30" s="24"/>
-      <c r="BH30" s="24"/>
-      <c r="BI30" s="24"/>
+      <c r="BF30" s="25"/>
+      <c r="BG30" s="26"/>
+      <c r="BH30" s="26"/>
+      <c r="BI30" s="26"/>
       <c r="BJ30" s="38"/>
       <c r="BK30" s="39"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B31" s="16">
         <f t="shared" si="2"/>
@@ -5011,7 +4989,7 @@
         <v>2.0</v>
       </c>
       <c r="G31" s="16"/>
-      <c r="H31" s="48"/>
+      <c r="H31" s="47"/>
       <c r="I31" s="16">
         <v>2.0</v>
       </c>
@@ -5024,7 +5002,7 @@
       <c r="L31" s="18">
         <v>1.0</v>
       </c>
-      <c r="M31" s="48">
+      <c r="M31" s="47">
         <v>-1.0</v>
       </c>
       <c r="N31" s="16">
@@ -5042,10 +5020,10 @@
       <c r="R31" s="15">
         <v>1.0</v>
       </c>
-      <c r="S31" s="21"/>
+      <c r="S31" s="23"/>
       <c r="T31" s="35"/>
       <c r="U31" s="35"/>
-      <c r="V31" s="47"/>
+      <c r="V31" s="46"/>
       <c r="W31" s="35"/>
       <c r="X31" s="20"/>
       <c r="Y31" s="20"/>
@@ -5060,7 +5038,7 @@
       <c r="AH31" s="15"/>
       <c r="AI31" s="15"/>
       <c r="AJ31" s="20"/>
-      <c r="AK31" s="21"/>
+      <c r="AK31" s="23"/>
       <c r="AL31" s="20"/>
       <c r="AM31" s="18"/>
       <c r="AN31" s="15"/>
@@ -5068,33 +5046,33 @@
       <c r="AP31" s="15"/>
       <c r="AQ31" s="20"/>
       <c r="AR31" s="20"/>
-      <c r="AS31" s="22"/>
+      <c r="AS31" s="24"/>
       <c r="AT31" s="15"/>
       <c r="AU31" s="15"/>
       <c r="AV31" s="15"/>
       <c r="AW31" s="15"/>
       <c r="AX31" s="15"/>
-      <c r="AY31" s="22"/>
-      <c r="AZ31" s="22"/>
+      <c r="AY31" s="24"/>
+      <c r="AZ31" s="24"/>
       <c r="BA31" s="15"/>
       <c r="BB31" s="15"/>
       <c r="BC31" s="18"/>
       <c r="BD31" s="15"/>
       <c r="BE31" s="15"/>
-      <c r="BF31" s="23"/>
-      <c r="BG31" s="24"/>
-      <c r="BH31" s="24"/>
-      <c r="BI31" s="24"/>
-      <c r="BJ31" s="24"/>
-      <c r="BK31" s="25"/>
+      <c r="BF31" s="25"/>
+      <c r="BG31" s="26"/>
+      <c r="BH31" s="26"/>
+      <c r="BI31" s="26"/>
+      <c r="BJ31" s="26"/>
+      <c r="BK31" s="27"/>
     </row>
     <row r="32">
       <c r="A32" s="15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B32" s="16">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C32" s="37"/>
       <c r="D32" s="31"/>
@@ -5149,11 +5127,11 @@
       <c r="U32" s="20">
         <v>2.0</v>
       </c>
-      <c r="V32" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="W32" s="26" t="s">
-        <v>10</v>
+      <c r="V32" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="W32" s="28" t="s">
+        <v>5</v>
       </c>
       <c r="X32" s="20"/>
       <c r="Y32" s="20"/>
@@ -5197,11 +5175,11 @@
     </row>
     <row r="33">
       <c r="A33" s="15" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B33" s="16">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C33" s="37"/>
       <c r="D33" s="31"/>
@@ -5248,23 +5226,23 @@
       <c r="U33" s="35">
         <v>2.0</v>
       </c>
-      <c r="V33" s="36" t="s">
-        <v>12</v>
+      <c r="V33" s="48">
+        <v>2.0</v>
       </c>
       <c r="W33" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="X33" s="27" t="s">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="X33" s="21" t="s">
+        <v>11</v>
       </c>
       <c r="Y33" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z33" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA33" s="22" t="s">
         <v>9</v>
-      </c>
-      <c r="Z33" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA33" s="28" t="s">
-        <v>16</v>
       </c>
       <c r="AB33" s="19"/>
       <c r="AC33" s="34"/>
@@ -5289,26 +5267,26 @@
       <c r="AV33" s="31"/>
       <c r="AW33" s="31"/>
       <c r="AX33" s="31"/>
-      <c r="AY33" s="22"/>
-      <c r="AZ33" s="22"/>
+      <c r="AY33" s="24"/>
+      <c r="AZ33" s="24"/>
       <c r="BA33" s="31"/>
       <c r="BB33" s="31"/>
       <c r="BC33" s="15"/>
       <c r="BD33" s="15"/>
       <c r="BE33" s="18"/>
-      <c r="BF33" s="23"/>
-      <c r="BG33" s="24"/>
-      <c r="BH33" s="24"/>
-      <c r="BI33" s="24"/>
-      <c r="BJ33" s="24"/>
-      <c r="BK33" s="25"/>
+      <c r="BF33" s="25"/>
+      <c r="BG33" s="26"/>
+      <c r="BH33" s="26"/>
+      <c r="BI33" s="26"/>
+      <c r="BJ33" s="26"/>
+      <c r="BK33" s="27"/>
     </row>
     <row r="34">
       <c r="A34" s="15"/>
       <c r="B34" s="49"/>
       <c r="C34" s="16"/>
       <c r="D34" s="15"/>
-      <c r="E34" s="21"/>
+      <c r="E34" s="23"/>
       <c r="F34" s="16"/>
       <c r="G34" s="16"/>
       <c r="H34" s="16"/>
@@ -5316,12 +5294,12 @@
       <c r="J34" s="16"/>
       <c r="K34" s="15"/>
       <c r="L34" s="19"/>
-      <c r="M34" s="21"/>
+      <c r="M34" s="23"/>
       <c r="O34" s="15"/>
       <c r="P34" s="15"/>
       <c r="Q34" s="15"/>
       <c r="R34" s="15"/>
-      <c r="S34" s="21"/>
+      <c r="S34" s="23"/>
       <c r="T34" s="20"/>
       <c r="U34" s="20"/>
       <c r="V34" s="15"/>
@@ -5339,7 +5317,7 @@
       <c r="AH34" s="31"/>
       <c r="AI34" s="20"/>
       <c r="AJ34" s="20"/>
-      <c r="AK34" s="21"/>
+      <c r="AK34" s="23"/>
       <c r="AL34" s="20"/>
       <c r="AM34" s="18"/>
       <c r="AN34" s="15"/>
@@ -5347,32 +5325,32 @@
       <c r="AP34" s="15"/>
       <c r="AQ34" s="20"/>
       <c r="AR34" s="20"/>
-      <c r="AS34" s="22"/>
+      <c r="AS34" s="24"/>
       <c r="AT34" s="15"/>
       <c r="AU34" s="15"/>
       <c r="AV34" s="15"/>
       <c r="AW34" s="15"/>
       <c r="AX34" s="15"/>
-      <c r="AY34" s="22"/>
-      <c r="AZ34" s="22"/>
+      <c r="AY34" s="24"/>
+      <c r="AZ34" s="24"/>
       <c r="BA34" s="15"/>
       <c r="BB34" s="15"/>
       <c r="BC34" s="15"/>
       <c r="BD34" s="15"/>
       <c r="BE34" s="18"/>
-      <c r="BF34" s="23"/>
-      <c r="BG34" s="24"/>
-      <c r="BH34" s="24"/>
-      <c r="BI34" s="24"/>
-      <c r="BJ34" s="24"/>
-      <c r="BK34" s="25"/>
+      <c r="BF34" s="25"/>
+      <c r="BG34" s="26"/>
+      <c r="BH34" s="26"/>
+      <c r="BI34" s="26"/>
+      <c r="BJ34" s="26"/>
+      <c r="BK34" s="27"/>
     </row>
     <row r="35">
       <c r="A35" s="44"/>
       <c r="B35" s="40"/>
       <c r="C35" s="20"/>
       <c r="D35" s="15"/>
-      <c r="E35" s="21"/>
+      <c r="E35" s="23"/>
       <c r="F35" s="20"/>
       <c r="G35" s="20"/>
       <c r="H35" s="20"/>
@@ -5381,12 +5359,12 @@
       <c r="K35" s="15"/>
       <c r="L35" s="19"/>
       <c r="M35" s="20"/>
-      <c r="N35" s="21"/>
+      <c r="N35" s="23"/>
       <c r="O35" s="15"/>
       <c r="P35" s="15"/>
       <c r="Q35" s="15"/>
       <c r="R35" s="19"/>
-      <c r="S35" s="21"/>
+      <c r="S35" s="23"/>
       <c r="T35" s="20"/>
       <c r="U35" s="20"/>
       <c r="V35" s="15"/>
@@ -5404,7 +5382,7 @@
       <c r="AH35" s="15"/>
       <c r="AI35" s="20"/>
       <c r="AJ35" s="20"/>
-      <c r="AK35" s="21"/>
+      <c r="AK35" s="23"/>
       <c r="AL35" s="20"/>
       <c r="AM35" s="18"/>
       <c r="AN35" s="15"/>
@@ -5412,32 +5390,32 @@
       <c r="AP35" s="15"/>
       <c r="AQ35" s="20"/>
       <c r="AR35" s="20"/>
-      <c r="AS35" s="22"/>
+      <c r="AS35" s="24"/>
       <c r="AT35" s="15"/>
       <c r="AU35" s="15"/>
       <c r="AV35" s="15"/>
       <c r="AW35" s="15"/>
       <c r="AX35" s="15"/>
-      <c r="AY35" s="22"/>
-      <c r="AZ35" s="22"/>
+      <c r="AY35" s="24"/>
+      <c r="AZ35" s="24"/>
       <c r="BA35" s="15"/>
       <c r="BB35" s="15"/>
       <c r="BC35" s="18"/>
       <c r="BD35" s="15"/>
       <c r="BE35" s="18"/>
-      <c r="BF35" s="23"/>
-      <c r="BG35" s="24"/>
-      <c r="BH35" s="24"/>
-      <c r="BI35" s="24"/>
-      <c r="BJ35" s="24"/>
-      <c r="BK35" s="25"/>
+      <c r="BF35" s="25"/>
+      <c r="BG35" s="26"/>
+      <c r="BH35" s="26"/>
+      <c r="BI35" s="26"/>
+      <c r="BJ35" s="26"/>
+      <c r="BK35" s="27"/>
     </row>
     <row r="36">
       <c r="A36" s="15"/>
       <c r="B36" s="40"/>
       <c r="C36" s="17"/>
       <c r="D36" s="15"/>
-      <c r="E36" s="21"/>
+      <c r="E36" s="23"/>
       <c r="F36" s="20"/>
       <c r="G36" s="20"/>
       <c r="H36" s="20"/>
@@ -5446,7 +5424,7 @@
       <c r="K36" s="15"/>
       <c r="L36" s="19"/>
       <c r="M36" s="20"/>
-      <c r="N36" s="21"/>
+      <c r="N36" s="23"/>
       <c r="O36" s="20"/>
       <c r="P36" s="15"/>
       <c r="Q36" s="15"/>
@@ -5469,7 +5447,7 @@
       <c r="AH36" s="15"/>
       <c r="AI36" s="20"/>
       <c r="AJ36" s="20"/>
-      <c r="AK36" s="21"/>
+      <c r="AK36" s="23"/>
       <c r="AL36" s="20"/>
       <c r="AM36" s="18"/>
       <c r="AN36" s="15"/>
@@ -5477,25 +5455,25 @@
       <c r="AP36" s="15"/>
       <c r="AQ36" s="20"/>
       <c r="AR36" s="20"/>
-      <c r="AS36" s="22"/>
+      <c r="AS36" s="24"/>
       <c r="AT36" s="15"/>
       <c r="AU36" s="15"/>
       <c r="AV36" s="15"/>
       <c r="AW36" s="15"/>
       <c r="AX36" s="15"/>
-      <c r="AY36" s="22"/>
-      <c r="AZ36" s="22"/>
+      <c r="AY36" s="24"/>
+      <c r="AZ36" s="24"/>
       <c r="BA36" s="15"/>
       <c r="BB36" s="15"/>
       <c r="BC36" s="18"/>
       <c r="BD36" s="15"/>
       <c r="BE36" s="18"/>
-      <c r="BF36" s="23"/>
-      <c r="BG36" s="24"/>
-      <c r="BH36" s="24"/>
-      <c r="BI36" s="24"/>
-      <c r="BJ36" s="24"/>
-      <c r="BK36" s="25"/>
+      <c r="BF36" s="25"/>
+      <c r="BG36" s="26"/>
+      <c r="BH36" s="26"/>
+      <c r="BI36" s="26"/>
+      <c r="BJ36" s="26"/>
+      <c r="BK36" s="27"/>
     </row>
     <row r="37">
       <c r="A37" s="15"/>
@@ -5566,7 +5544,7 @@
       <c r="B38" s="40"/>
       <c r="C38" s="37"/>
       <c r="D38" s="15"/>
-      <c r="E38" s="21"/>
+      <c r="E38" s="23"/>
       <c r="F38" s="20"/>
       <c r="G38" s="20"/>
       <c r="H38" s="20"/>
@@ -5575,12 +5553,12 @@
       <c r="K38" s="15"/>
       <c r="L38" s="31"/>
       <c r="M38" s="20"/>
-      <c r="N38" s="21"/>
+      <c r="N38" s="23"/>
       <c r="O38" s="20"/>
       <c r="P38" s="15"/>
       <c r="Q38" s="15"/>
       <c r="R38" s="19"/>
-      <c r="S38" s="21"/>
+      <c r="S38" s="23"/>
       <c r="T38" s="20"/>
       <c r="U38" s="20"/>
       <c r="V38" s="15"/>
@@ -5606,32 +5584,32 @@
       <c r="AP38" s="15"/>
       <c r="AQ38" s="20"/>
       <c r="AR38" s="20"/>
-      <c r="AS38" s="22"/>
+      <c r="AS38" s="24"/>
       <c r="AT38" s="15"/>
       <c r="AU38" s="15"/>
       <c r="AV38" s="15"/>
       <c r="AW38" s="15"/>
       <c r="AX38" s="15"/>
-      <c r="AY38" s="22"/>
-      <c r="AZ38" s="22"/>
+      <c r="AY38" s="24"/>
+      <c r="AZ38" s="24"/>
       <c r="BA38" s="15"/>
       <c r="BB38" s="15"/>
       <c r="BC38" s="15"/>
       <c r="BD38" s="15"/>
       <c r="BE38" s="18"/>
-      <c r="BF38" s="23"/>
-      <c r="BG38" s="24"/>
-      <c r="BH38" s="24"/>
-      <c r="BI38" s="24"/>
-      <c r="BJ38" s="24"/>
-      <c r="BK38" s="25"/>
+      <c r="BF38" s="25"/>
+      <c r="BG38" s="26"/>
+      <c r="BH38" s="26"/>
+      <c r="BI38" s="26"/>
+      <c r="BJ38" s="26"/>
+      <c r="BK38" s="27"/>
     </row>
     <row r="39">
       <c r="A39" s="15"/>
       <c r="B39" s="40"/>
       <c r="C39" s="20"/>
       <c r="D39" s="15"/>
-      <c r="E39" s="21"/>
+      <c r="E39" s="23"/>
       <c r="F39" s="20"/>
       <c r="G39" s="20"/>
       <c r="H39" s="20"/>
@@ -5640,12 +5618,12 @@
       <c r="K39" s="15"/>
       <c r="L39" s="19"/>
       <c r="M39" s="20"/>
-      <c r="N39" s="21"/>
+      <c r="N39" s="23"/>
       <c r="O39" s="20"/>
       <c r="P39" s="15"/>
       <c r="Q39" s="15"/>
       <c r="R39" s="19"/>
-      <c r="S39" s="21"/>
+      <c r="S39" s="23"/>
       <c r="T39" s="20"/>
       <c r="U39" s="20"/>
       <c r="V39" s="15"/>
@@ -5671,32 +5649,32 @@
       <c r="AP39" s="15"/>
       <c r="AQ39" s="20"/>
       <c r="AR39" s="20"/>
-      <c r="AS39" s="22"/>
+      <c r="AS39" s="24"/>
       <c r="AT39" s="15"/>
       <c r="AU39" s="15"/>
       <c r="AV39" s="15"/>
       <c r="AW39" s="15"/>
       <c r="AX39" s="15"/>
-      <c r="AY39" s="22"/>
-      <c r="AZ39" s="22"/>
+      <c r="AY39" s="24"/>
+      <c r="AZ39" s="24"/>
       <c r="BA39" s="15"/>
       <c r="BB39" s="15"/>
       <c r="BC39" s="15"/>
       <c r="BD39" s="15"/>
       <c r="BE39" s="18"/>
-      <c r="BF39" s="23"/>
-      <c r="BG39" s="24"/>
-      <c r="BH39" s="24"/>
-      <c r="BI39" s="24"/>
-      <c r="BJ39" s="24"/>
-      <c r="BK39" s="25"/>
+      <c r="BF39" s="25"/>
+      <c r="BG39" s="26"/>
+      <c r="BH39" s="26"/>
+      <c r="BI39" s="26"/>
+      <c r="BJ39" s="26"/>
+      <c r="BK39" s="27"/>
     </row>
     <row r="40">
       <c r="A40" s="15"/>
       <c r="B40" s="40"/>
       <c r="C40" s="20"/>
       <c r="D40" s="15"/>
-      <c r="E40" s="21"/>
+      <c r="E40" s="23"/>
       <c r="F40" s="20"/>
       <c r="G40" s="20"/>
       <c r="H40" s="20"/>
@@ -5705,12 +5683,12 @@
       <c r="K40" s="15"/>
       <c r="L40" s="19"/>
       <c r="M40" s="20"/>
-      <c r="N40" s="21"/>
+      <c r="N40" s="23"/>
       <c r="O40" s="20"/>
       <c r="P40" s="15"/>
       <c r="Q40" s="15"/>
       <c r="R40" s="19"/>
-      <c r="S40" s="21"/>
+      <c r="S40" s="23"/>
       <c r="T40" s="20"/>
       <c r="U40" s="20"/>
       <c r="V40" s="15"/>
@@ -5728,7 +5706,7 @@
       <c r="AH40" s="15"/>
       <c r="AI40" s="20"/>
       <c r="AJ40" s="20"/>
-      <c r="AK40" s="21"/>
+      <c r="AK40" s="23"/>
       <c r="AL40" s="20"/>
       <c r="AM40" s="18"/>
       <c r="AN40" s="15"/>
@@ -5736,32 +5714,32 @@
       <c r="AP40" s="15"/>
       <c r="AQ40" s="20"/>
       <c r="AR40" s="20"/>
-      <c r="AS40" s="22"/>
+      <c r="AS40" s="24"/>
       <c r="AT40" s="15"/>
       <c r="AU40" s="15"/>
       <c r="AV40" s="15"/>
       <c r="AW40" s="15"/>
       <c r="AX40" s="15"/>
-      <c r="AY40" s="22"/>
-      <c r="AZ40" s="22"/>
+      <c r="AY40" s="24"/>
+      <c r="AZ40" s="24"/>
       <c r="BA40" s="15"/>
       <c r="BB40" s="15"/>
       <c r="BC40" s="15"/>
       <c r="BD40" s="15"/>
       <c r="BE40" s="18"/>
-      <c r="BF40" s="23"/>
-      <c r="BG40" s="24"/>
-      <c r="BH40" s="24"/>
-      <c r="BI40" s="24"/>
-      <c r="BJ40" s="24"/>
-      <c r="BK40" s="25"/>
+      <c r="BF40" s="25"/>
+      <c r="BG40" s="26"/>
+      <c r="BH40" s="26"/>
+      <c r="BI40" s="26"/>
+      <c r="BJ40" s="26"/>
+      <c r="BK40" s="27"/>
     </row>
     <row r="41">
       <c r="A41" s="15"/>
       <c r="B41" s="40"/>
       <c r="C41" s="17"/>
       <c r="D41" s="15"/>
-      <c r="E41" s="21"/>
+      <c r="E41" s="23"/>
       <c r="F41" s="20"/>
       <c r="G41" s="15"/>
       <c r="H41" s="20"/>
@@ -5793,7 +5771,7 @@
       <c r="AH41" s="15"/>
       <c r="AI41" s="15"/>
       <c r="AJ41" s="15"/>
-      <c r="AK41" s="21"/>
+      <c r="AK41" s="23"/>
       <c r="AL41" s="15"/>
       <c r="AM41" s="15"/>
       <c r="AN41" s="15"/>
@@ -5803,11 +5781,11 @@
       <c r="AR41" s="20"/>
       <c r="AS41" s="15"/>
       <c r="AT41" s="15"/>
-      <c r="AU41" s="22"/>
+      <c r="AU41" s="24"/>
       <c r="AV41" s="15"/>
       <c r="AW41" s="15"/>
       <c r="AX41" s="15"/>
-      <c r="AY41" s="22"/>
+      <c r="AY41" s="24"/>
       <c r="AZ41" s="15"/>
       <c r="BA41" s="15"/>
       <c r="BB41" s="15"/>
@@ -5826,7 +5804,7 @@
       <c r="B42" s="40"/>
       <c r="C42" s="20"/>
       <c r="D42" s="15"/>
-      <c r="E42" s="21"/>
+      <c r="E42" s="23"/>
       <c r="F42" s="20"/>
       <c r="G42" s="20"/>
       <c r="H42" s="20"/>
@@ -5835,7 +5813,7 @@
       <c r="K42" s="15"/>
       <c r="L42" s="19"/>
       <c r="M42" s="20"/>
-      <c r="N42" s="21"/>
+      <c r="N42" s="23"/>
       <c r="O42" s="15"/>
       <c r="P42" s="15"/>
       <c r="Q42" s="15"/>
@@ -5858,7 +5836,7 @@
       <c r="AH42" s="15"/>
       <c r="AI42" s="15"/>
       <c r="AJ42" s="20"/>
-      <c r="AK42" s="21"/>
+      <c r="AK42" s="23"/>
       <c r="AL42" s="20"/>
       <c r="AM42" s="18"/>
       <c r="AN42" s="15"/>
@@ -5866,23 +5844,23 @@
       <c r="AP42" s="15"/>
       <c r="AQ42" s="20"/>
       <c r="AR42" s="20"/>
-      <c r="AS42" s="22"/>
+      <c r="AS42" s="24"/>
       <c r="AT42" s="15"/>
       <c r="AU42" s="15"/>
       <c r="AV42" s="15"/>
       <c r="AW42" s="15"/>
       <c r="AX42" s="15"/>
-      <c r="AY42" s="22"/>
-      <c r="AZ42" s="22"/>
+      <c r="AY42" s="24"/>
+      <c r="AZ42" s="24"/>
       <c r="BA42" s="15"/>
       <c r="BB42" s="15"/>
       <c r="BC42" s="18"/>
       <c r="BD42" s="15"/>
       <c r="BE42" s="18"/>
-      <c r="BF42" s="23"/>
-      <c r="BG42" s="24"/>
+      <c r="BF42" s="25"/>
+      <c r="BG42" s="26"/>
       <c r="BH42" s="32"/>
-      <c r="BI42" s="24"/>
+      <c r="BI42" s="26"/>
       <c r="BJ42" s="38"/>
       <c r="BK42" s="39"/>
     </row>
@@ -5923,7 +5901,7 @@
       <c r="AH43" s="15"/>
       <c r="AI43" s="15"/>
       <c r="AJ43" s="15"/>
-      <c r="AK43" s="21"/>
+      <c r="AK43" s="23"/>
       <c r="AL43" s="15"/>
       <c r="AM43" s="15"/>
       <c r="AN43" s="15"/>
@@ -5933,11 +5911,11 @@
       <c r="AR43" s="20"/>
       <c r="AS43" s="15"/>
       <c r="AT43" s="15"/>
-      <c r="AU43" s="22"/>
+      <c r="AU43" s="24"/>
       <c r="AV43" s="15"/>
       <c r="AW43" s="15"/>
       <c r="AX43" s="15"/>
-      <c r="AY43" s="22"/>
+      <c r="AY43" s="24"/>
       <c r="AZ43" s="15"/>
       <c r="BA43" s="15"/>
       <c r="BB43" s="15"/>
@@ -5945,7 +5923,7 @@
       <c r="BD43" s="50"/>
       <c r="BE43" s="15"/>
       <c r="BF43" s="41"/>
-      <c r="BG43" s="24"/>
+      <c r="BG43" s="26"/>
       <c r="BH43" s="32"/>
       <c r="BI43" s="32"/>
       <c r="BJ43" s="32"/>
@@ -5998,20 +5976,20 @@
       <c r="AR44" s="20"/>
       <c r="AS44" s="15"/>
       <c r="AT44" s="15"/>
-      <c r="AU44" s="22"/>
+      <c r="AU44" s="24"/>
       <c r="AV44" s="15"/>
       <c r="AW44" s="15"/>
       <c r="AX44" s="15"/>
-      <c r="AY44" s="22"/>
+      <c r="AY44" s="24"/>
       <c r="AZ44" s="15"/>
       <c r="BA44" s="31"/>
       <c r="BB44" s="31"/>
       <c r="BC44" s="31"/>
       <c r="BD44" s="31"/>
       <c r="BE44" s="15"/>
-      <c r="BF44" s="23"/>
+      <c r="BF44" s="25"/>
       <c r="BG44" s="32"/>
-      <c r="BH44" s="24"/>
+      <c r="BH44" s="26"/>
       <c r="BI44" s="33"/>
       <c r="BJ44" s="38"/>
       <c r="BK44" s="39"/>
@@ -6021,7 +5999,7 @@
       <c r="B45" s="40"/>
       <c r="C45" s="20"/>
       <c r="D45" s="15"/>
-      <c r="E45" s="21"/>
+      <c r="E45" s="23"/>
       <c r="F45" s="20"/>
       <c r="G45" s="20"/>
       <c r="H45" s="20"/>
@@ -6030,12 +6008,12 @@
       <c r="K45" s="15"/>
       <c r="L45" s="19"/>
       <c r="M45" s="20"/>
-      <c r="N45" s="21"/>
+      <c r="N45" s="23"/>
       <c r="O45" s="20"/>
       <c r="P45" s="15"/>
       <c r="Q45" s="15"/>
       <c r="R45" s="19"/>
-      <c r="S45" s="21"/>
+      <c r="S45" s="23"/>
       <c r="T45" s="20"/>
       <c r="U45" s="20"/>
       <c r="V45" s="15"/>
@@ -6061,32 +6039,32 @@
       <c r="AP45" s="15"/>
       <c r="AQ45" s="20"/>
       <c r="AR45" s="20"/>
-      <c r="AS45" s="22"/>
+      <c r="AS45" s="24"/>
       <c r="AT45" s="15"/>
-      <c r="AU45" s="22"/>
+      <c r="AU45" s="24"/>
       <c r="AV45" s="15"/>
       <c r="AW45" s="15"/>
       <c r="AX45" s="15"/>
-      <c r="AY45" s="22"/>
-      <c r="AZ45" s="22"/>
+      <c r="AY45" s="24"/>
+      <c r="AZ45" s="24"/>
       <c r="BA45" s="15"/>
       <c r="BB45" s="15"/>
       <c r="BC45" s="18"/>
       <c r="BD45" s="15"/>
       <c r="BE45" s="18"/>
-      <c r="BF45" s="23"/>
-      <c r="BG45" s="24"/>
-      <c r="BH45" s="24"/>
+      <c r="BF45" s="25"/>
+      <c r="BG45" s="26"/>
+      <c r="BH45" s="26"/>
       <c r="BI45" s="33"/>
-      <c r="BJ45" s="24"/>
-      <c r="BK45" s="25"/>
+      <c r="BJ45" s="26"/>
+      <c r="BK45" s="27"/>
     </row>
     <row r="46">
       <c r="A46" s="44"/>
       <c r="B46" s="40"/>
       <c r="C46" s="17"/>
       <c r="D46" s="15"/>
-      <c r="E46" s="21"/>
+      <c r="E46" s="23"/>
       <c r="F46" s="20"/>
       <c r="G46" s="20"/>
       <c r="H46" s="20"/>
@@ -6095,12 +6073,12 @@
       <c r="K46" s="15"/>
       <c r="L46" s="19"/>
       <c r="M46" s="20"/>
-      <c r="N46" s="21"/>
+      <c r="N46" s="23"/>
       <c r="O46" s="20"/>
       <c r="P46" s="15"/>
       <c r="Q46" s="15"/>
       <c r="R46" s="19"/>
-      <c r="S46" s="21"/>
+      <c r="S46" s="23"/>
       <c r="T46" s="20"/>
       <c r="U46" s="20"/>
       <c r="V46" s="15"/>
@@ -6126,32 +6104,32 @@
       <c r="AP46" s="15"/>
       <c r="AQ46" s="20"/>
       <c r="AR46" s="20"/>
-      <c r="AS46" s="22"/>
+      <c r="AS46" s="24"/>
       <c r="AT46" s="15"/>
       <c r="AU46" s="15"/>
       <c r="AV46" s="15"/>
       <c r="AW46" s="15"/>
       <c r="AX46" s="15"/>
-      <c r="AY46" s="22"/>
-      <c r="AZ46" s="22"/>
+      <c r="AY46" s="24"/>
+      <c r="AZ46" s="24"/>
       <c r="BA46" s="15"/>
       <c r="BB46" s="15"/>
       <c r="BC46" s="15"/>
       <c r="BD46" s="15"/>
       <c r="BE46" s="18"/>
-      <c r="BF46" s="23"/>
-      <c r="BG46" s="24"/>
-      <c r="BH46" s="24"/>
-      <c r="BI46" s="24"/>
-      <c r="BJ46" s="24"/>
-      <c r="BK46" s="25"/>
+      <c r="BF46" s="25"/>
+      <c r="BG46" s="26"/>
+      <c r="BH46" s="26"/>
+      <c r="BI46" s="26"/>
+      <c r="BJ46" s="26"/>
+      <c r="BK46" s="27"/>
     </row>
     <row r="47">
       <c r="A47" s="44"/>
       <c r="B47" s="40"/>
       <c r="C47" s="20"/>
       <c r="D47" s="15"/>
-      <c r="E47" s="21"/>
+      <c r="E47" s="23"/>
       <c r="F47" s="20"/>
       <c r="G47" s="20"/>
       <c r="H47" s="20"/>
@@ -6160,7 +6138,7 @@
       <c r="K47" s="15"/>
       <c r="L47" s="19"/>
       <c r="M47" s="20"/>
-      <c r="N47" s="21"/>
+      <c r="N47" s="23"/>
       <c r="O47" s="15"/>
       <c r="P47" s="15"/>
       <c r="Q47" s="15"/>
@@ -6183,7 +6161,7 @@
       <c r="AH47" s="15"/>
       <c r="AI47" s="20"/>
       <c r="AJ47" s="40"/>
-      <c r="AK47" s="21"/>
+      <c r="AK47" s="23"/>
       <c r="AL47" s="20"/>
       <c r="AM47" s="40"/>
       <c r="AN47" s="40"/>
@@ -6191,32 +6169,32 @@
       <c r="AP47" s="40"/>
       <c r="AQ47" s="20"/>
       <c r="AR47" s="20"/>
-      <c r="AS47" s="22"/>
+      <c r="AS47" s="24"/>
       <c r="AT47" s="15"/>
       <c r="AU47" s="15"/>
       <c r="AV47" s="15"/>
       <c r="AW47" s="15"/>
       <c r="AX47" s="15"/>
-      <c r="AY47" s="22"/>
-      <c r="AZ47" s="22"/>
+      <c r="AY47" s="24"/>
+      <c r="AZ47" s="24"/>
       <c r="BA47" s="15"/>
       <c r="BB47" s="15"/>
       <c r="BC47" s="18"/>
       <c r="BD47" s="15"/>
       <c r="BE47" s="18"/>
       <c r="BF47" s="41"/>
-      <c r="BG47" s="24"/>
+      <c r="BG47" s="26"/>
       <c r="BH47" s="32"/>
-      <c r="BI47" s="24"/>
-      <c r="BJ47" s="24"/>
-      <c r="BK47" s="25"/>
+      <c r="BI47" s="26"/>
+      <c r="BJ47" s="26"/>
+      <c r="BK47" s="27"/>
     </row>
     <row r="48">
       <c r="A48" s="15"/>
       <c r="B48" s="40"/>
       <c r="C48" s="20"/>
       <c r="D48" s="15"/>
-      <c r="E48" s="21"/>
+      <c r="E48" s="23"/>
       <c r="F48" s="20"/>
       <c r="G48" s="20"/>
       <c r="H48" s="20"/>
@@ -6225,12 +6203,12 @@
       <c r="K48" s="15"/>
       <c r="L48" s="19"/>
       <c r="M48" s="20"/>
-      <c r="N48" s="21"/>
+      <c r="N48" s="23"/>
       <c r="O48" s="20"/>
       <c r="P48" s="15"/>
       <c r="Q48" s="15"/>
       <c r="R48" s="19"/>
-      <c r="S48" s="21"/>
+      <c r="S48" s="23"/>
       <c r="T48" s="20"/>
       <c r="U48" s="20"/>
       <c r="V48" s="15"/>
@@ -6256,25 +6234,25 @@
       <c r="AP48" s="15"/>
       <c r="AQ48" s="20"/>
       <c r="AR48" s="20"/>
-      <c r="AS48" s="22"/>
+      <c r="AS48" s="24"/>
       <c r="AT48" s="15"/>
       <c r="AU48" s="15"/>
       <c r="AV48" s="15"/>
       <c r="AW48" s="15"/>
       <c r="AX48" s="15"/>
-      <c r="AY48" s="22"/>
-      <c r="AZ48" s="22"/>
+      <c r="AY48" s="24"/>
+      <c r="AZ48" s="24"/>
       <c r="BA48" s="15"/>
       <c r="BB48" s="15"/>
       <c r="BC48" s="15"/>
       <c r="BD48" s="15"/>
       <c r="BE48" s="18"/>
-      <c r="BF48" s="23"/>
-      <c r="BG48" s="24"/>
-      <c r="BH48" s="24"/>
-      <c r="BI48" s="24"/>
-      <c r="BJ48" s="24"/>
-      <c r="BK48" s="25"/>
+      <c r="BF48" s="25"/>
+      <c r="BG48" s="26"/>
+      <c r="BH48" s="26"/>
+      <c r="BI48" s="26"/>
+      <c r="BJ48" s="26"/>
+      <c r="BK48" s="27"/>
     </row>
     <row r="49">
       <c r="A49" s="15"/>
@@ -6295,7 +6273,7 @@
       <c r="P49" s="15"/>
       <c r="Q49" s="15"/>
       <c r="R49" s="19"/>
-      <c r="S49" s="21"/>
+      <c r="S49" s="23"/>
       <c r="T49" s="20"/>
       <c r="U49" s="20"/>
       <c r="V49" s="15"/>
@@ -6321,32 +6299,32 @@
       <c r="AP49" s="15"/>
       <c r="AQ49" s="20"/>
       <c r="AR49" s="20"/>
-      <c r="AS49" s="22"/>
+      <c r="AS49" s="24"/>
       <c r="AT49" s="15"/>
       <c r="AU49" s="15"/>
       <c r="AV49" s="15"/>
       <c r="AW49" s="15"/>
       <c r="AX49" s="15"/>
-      <c r="AY49" s="22"/>
-      <c r="AZ49" s="22"/>
+      <c r="AY49" s="24"/>
+      <c r="AZ49" s="24"/>
       <c r="BA49" s="15"/>
       <c r="BB49" s="15"/>
       <c r="BC49" s="15"/>
       <c r="BD49" s="15"/>
       <c r="BE49" s="18"/>
-      <c r="BF49" s="23"/>
-      <c r="BG49" s="24"/>
-      <c r="BH49" s="24"/>
-      <c r="BI49" s="24"/>
-      <c r="BJ49" s="24"/>
-      <c r="BK49" s="25"/>
+      <c r="BF49" s="25"/>
+      <c r="BG49" s="26"/>
+      <c r="BH49" s="26"/>
+      <c r="BI49" s="26"/>
+      <c r="BJ49" s="26"/>
+      <c r="BK49" s="27"/>
     </row>
     <row r="50">
       <c r="A50" s="15"/>
       <c r="B50" s="40"/>
       <c r="C50" s="17"/>
       <c r="D50" s="15"/>
-      <c r="E50" s="21"/>
+      <c r="E50" s="23"/>
       <c r="F50" s="20"/>
       <c r="G50" s="20"/>
       <c r="H50" s="20"/>
@@ -6355,12 +6333,12 @@
       <c r="K50" s="15"/>
       <c r="L50" s="15"/>
       <c r="M50" s="20"/>
-      <c r="N50" s="21"/>
+      <c r="N50" s="23"/>
       <c r="O50" s="15"/>
       <c r="P50" s="15"/>
       <c r="Q50" s="15"/>
       <c r="R50" s="19"/>
-      <c r="S50" s="21"/>
+      <c r="S50" s="23"/>
       <c r="T50" s="20"/>
       <c r="U50" s="20"/>
       <c r="V50" s="15"/>
@@ -6378,7 +6356,7 @@
       <c r="AH50" s="15"/>
       <c r="AI50" s="15"/>
       <c r="AJ50" s="20"/>
-      <c r="AK50" s="21"/>
+      <c r="AK50" s="23"/>
       <c r="AL50" s="20"/>
       <c r="AM50" s="18"/>
       <c r="AN50" s="15"/>
@@ -6386,23 +6364,23 @@
       <c r="AP50" s="18"/>
       <c r="AQ50" s="20"/>
       <c r="AR50" s="20"/>
-      <c r="AS50" s="22"/>
+      <c r="AS50" s="24"/>
       <c r="AT50" s="15"/>
       <c r="AU50" s="15"/>
       <c r="AV50" s="15"/>
       <c r="AW50" s="15"/>
       <c r="AX50" s="15"/>
-      <c r="AY50" s="22"/>
-      <c r="AZ50" s="22"/>
+      <c r="AY50" s="24"/>
+      <c r="AZ50" s="24"/>
       <c r="BA50" s="31"/>
       <c r="BB50" s="31"/>
       <c r="BC50" s="15"/>
       <c r="BD50" s="15"/>
       <c r="BE50" s="18"/>
-      <c r="BF50" s="23"/>
-      <c r="BG50" s="24"/>
-      <c r="BH50" s="24"/>
-      <c r="BI50" s="24"/>
+      <c r="BF50" s="25"/>
+      <c r="BG50" s="26"/>
+      <c r="BH50" s="26"/>
+      <c r="BI50" s="26"/>
       <c r="BJ50" s="38"/>
       <c r="BK50" s="39"/>
     </row>
@@ -6411,7 +6389,7 @@
       <c r="B51" s="40"/>
       <c r="C51" s="17"/>
       <c r="D51" s="15"/>
-      <c r="E51" s="21"/>
+      <c r="E51" s="23"/>
       <c r="F51" s="20"/>
       <c r="G51" s="40"/>
       <c r="H51" s="20"/>
@@ -6443,7 +6421,7 @@
       <c r="AH51" s="40"/>
       <c r="AI51" s="15"/>
       <c r="AJ51" s="20"/>
-      <c r="AK51" s="21"/>
+      <c r="AK51" s="23"/>
       <c r="AL51" s="20"/>
       <c r="AM51" s="40"/>
       <c r="AN51" s="40"/>
@@ -6457,26 +6435,26 @@
       <c r="AV51" s="15"/>
       <c r="AW51" s="15"/>
       <c r="AX51" s="15"/>
-      <c r="AY51" s="22"/>
-      <c r="AZ51" s="22"/>
+      <c r="AY51" s="24"/>
+      <c r="AZ51" s="24"/>
       <c r="BA51" s="15"/>
       <c r="BB51" s="15"/>
       <c r="BC51" s="50"/>
       <c r="BD51" s="50"/>
       <c r="BE51" s="15"/>
-      <c r="BF51" s="23"/>
-      <c r="BG51" s="24"/>
-      <c r="BH51" s="24"/>
-      <c r="BI51" s="24"/>
-      <c r="BJ51" s="24"/>
-      <c r="BK51" s="25"/>
+      <c r="BF51" s="25"/>
+      <c r="BG51" s="26"/>
+      <c r="BH51" s="26"/>
+      <c r="BI51" s="26"/>
+      <c r="BJ51" s="26"/>
+      <c r="BK51" s="27"/>
     </row>
     <row r="52">
       <c r="A52" s="15"/>
       <c r="B52" s="40"/>
       <c r="C52" s="20"/>
       <c r="D52" s="15"/>
-      <c r="E52" s="21"/>
+      <c r="E52" s="23"/>
       <c r="F52" s="20"/>
       <c r="G52" s="20"/>
       <c r="H52" s="20"/>
@@ -6485,12 +6463,12 @@
       <c r="K52" s="15"/>
       <c r="L52" s="19"/>
       <c r="M52" s="20"/>
-      <c r="N52" s="21"/>
+      <c r="N52" s="23"/>
       <c r="O52" s="20"/>
       <c r="P52" s="15"/>
       <c r="Q52" s="15"/>
       <c r="R52" s="19"/>
-      <c r="S52" s="21"/>
+      <c r="S52" s="23"/>
       <c r="T52" s="20"/>
       <c r="U52" s="20"/>
       <c r="V52" s="15"/>
@@ -6508,7 +6486,7 @@
       <c r="AH52" s="15"/>
       <c r="AI52" s="20"/>
       <c r="AJ52" s="20"/>
-      <c r="AK52" s="21"/>
+      <c r="AK52" s="23"/>
       <c r="AL52" s="20"/>
       <c r="AM52" s="18"/>
       <c r="AN52" s="15"/>
@@ -6516,25 +6494,25 @@
       <c r="AP52" s="15"/>
       <c r="AQ52" s="20"/>
       <c r="AR52" s="20"/>
-      <c r="AS52" s="22"/>
+      <c r="AS52" s="24"/>
       <c r="AT52" s="15"/>
       <c r="AU52" s="15"/>
       <c r="AV52" s="15"/>
       <c r="AW52" s="15"/>
       <c r="AX52" s="15"/>
-      <c r="AY52" s="22"/>
-      <c r="AZ52" s="22"/>
+      <c r="AY52" s="24"/>
+      <c r="AZ52" s="24"/>
       <c r="BA52" s="15"/>
       <c r="BB52" s="15"/>
       <c r="BC52" s="15"/>
       <c r="BD52" s="15"/>
       <c r="BE52" s="18"/>
-      <c r="BF52" s="23"/>
-      <c r="BG52" s="24"/>
-      <c r="BH52" s="24"/>
-      <c r="BI52" s="24"/>
-      <c r="BJ52" s="24"/>
-      <c r="BK52" s="25"/>
+      <c r="BF52" s="25"/>
+      <c r="BG52" s="26"/>
+      <c r="BH52" s="26"/>
+      <c r="BI52" s="26"/>
+      <c r="BJ52" s="26"/>
+      <c r="BK52" s="27"/>
     </row>
     <row r="53">
       <c r="A53" s="15"/>
@@ -6587,26 +6565,26 @@
       <c r="AV53" s="31"/>
       <c r="AW53" s="31"/>
       <c r="AX53" s="31"/>
-      <c r="AY53" s="22"/>
-      <c r="AZ53" s="22"/>
+      <c r="AY53" s="24"/>
+      <c r="AZ53" s="24"/>
       <c r="BA53" s="15"/>
       <c r="BB53" s="15"/>
       <c r="BC53" s="15"/>
       <c r="BD53" s="15"/>
       <c r="BE53" s="18"/>
-      <c r="BF53" s="23"/>
-      <c r="BG53" s="24"/>
-      <c r="BH53" s="24"/>
-      <c r="BI53" s="24"/>
-      <c r="BJ53" s="24"/>
-      <c r="BK53" s="25"/>
+      <c r="BF53" s="25"/>
+      <c r="BG53" s="26"/>
+      <c r="BH53" s="26"/>
+      <c r="BI53" s="26"/>
+      <c r="BJ53" s="26"/>
+      <c r="BK53" s="27"/>
     </row>
     <row r="54">
       <c r="A54" s="15"/>
       <c r="B54" s="40"/>
       <c r="C54" s="17"/>
       <c r="D54" s="15"/>
-      <c r="E54" s="21"/>
+      <c r="E54" s="23"/>
       <c r="F54" s="20"/>
       <c r="G54" s="20"/>
       <c r="H54" s="20"/>
@@ -6615,12 +6593,12 @@
       <c r="K54" s="15"/>
       <c r="L54" s="19"/>
       <c r="M54" s="20"/>
-      <c r="N54" s="21"/>
+      <c r="N54" s="23"/>
       <c r="O54" s="15"/>
       <c r="P54" s="15"/>
       <c r="Q54" s="15"/>
       <c r="R54" s="19"/>
-      <c r="S54" s="21"/>
+      <c r="S54" s="23"/>
       <c r="T54" s="20"/>
       <c r="U54" s="20"/>
       <c r="V54" s="15"/>
@@ -6652,19 +6630,19 @@
       <c r="AV54" s="15"/>
       <c r="AW54" s="15"/>
       <c r="AX54" s="15"/>
-      <c r="AY54" s="22"/>
-      <c r="AZ54" s="22"/>
+      <c r="AY54" s="24"/>
+      <c r="AZ54" s="24"/>
       <c r="BA54" s="15"/>
       <c r="BB54" s="15"/>
       <c r="BC54" s="15"/>
       <c r="BD54" s="15"/>
       <c r="BE54" s="18"/>
-      <c r="BF54" s="23"/>
-      <c r="BG54" s="24"/>
-      <c r="BH54" s="24"/>
-      <c r="BI54" s="24"/>
-      <c r="BJ54" s="24"/>
-      <c r="BK54" s="25"/>
+      <c r="BF54" s="25"/>
+      <c r="BG54" s="26"/>
+      <c r="BH54" s="26"/>
+      <c r="BI54" s="26"/>
+      <c r="BJ54" s="26"/>
+      <c r="BK54" s="27"/>
     </row>
     <row r="55">
       <c r="A55" s="15"/>
@@ -6735,7 +6713,7 @@
       <c r="B56" s="40"/>
       <c r="C56" s="17"/>
       <c r="D56" s="31"/>
-      <c r="E56" s="21"/>
+      <c r="E56" s="23"/>
       <c r="F56" s="20"/>
       <c r="G56" s="20"/>
       <c r="H56" s="20"/>
@@ -6749,7 +6727,7 @@
       <c r="P56" s="15"/>
       <c r="Q56" s="15"/>
       <c r="R56" s="19"/>
-      <c r="S56" s="21"/>
+      <c r="S56" s="23"/>
       <c r="T56" s="20"/>
       <c r="U56" s="20"/>
       <c r="V56" s="15"/>
@@ -6775,25 +6753,25 @@
       <c r="AP56" s="15"/>
       <c r="AQ56" s="20"/>
       <c r="AR56" s="20"/>
-      <c r="AS56" s="22"/>
+      <c r="AS56" s="24"/>
       <c r="AT56" s="15"/>
       <c r="AU56" s="15"/>
       <c r="AV56" s="15"/>
       <c r="AW56" s="15"/>
       <c r="AX56" s="15"/>
-      <c r="AY56" s="22"/>
-      <c r="AZ56" s="22"/>
+      <c r="AY56" s="24"/>
+      <c r="AZ56" s="24"/>
       <c r="BA56" s="31"/>
       <c r="BB56" s="31"/>
       <c r="BC56" s="15"/>
       <c r="BD56" s="15"/>
       <c r="BE56" s="18"/>
-      <c r="BF56" s="23"/>
-      <c r="BG56" s="24"/>
-      <c r="BH56" s="24"/>
-      <c r="BI56" s="24"/>
-      <c r="BJ56" s="24"/>
-      <c r="BK56" s="25"/>
+      <c r="BF56" s="25"/>
+      <c r="BG56" s="26"/>
+      <c r="BH56" s="26"/>
+      <c r="BI56" s="26"/>
+      <c r="BJ56" s="26"/>
+      <c r="BK56" s="27"/>
     </row>
     <row r="57">
       <c r="A57" s="15"/>
@@ -6809,7 +6787,7 @@
       <c r="K57" s="31"/>
       <c r="L57" s="31"/>
       <c r="M57" s="31"/>
-      <c r="N57" s="21"/>
+      <c r="N57" s="23"/>
       <c r="O57" s="31"/>
       <c r="P57" s="31"/>
       <c r="Q57" s="31"/>
@@ -6873,12 +6851,12 @@
       <c r="K58" s="15"/>
       <c r="L58" s="19"/>
       <c r="M58" s="20"/>
-      <c r="N58" s="21"/>
+      <c r="N58" s="23"/>
       <c r="O58" s="20"/>
       <c r="P58" s="15"/>
       <c r="Q58" s="15"/>
       <c r="R58" s="19"/>
-      <c r="S58" s="21"/>
+      <c r="S58" s="23"/>
       <c r="T58" s="20"/>
       <c r="U58" s="20"/>
       <c r="V58" s="15"/>
@@ -6904,32 +6882,32 @@
       <c r="AP58" s="15"/>
       <c r="AQ58" s="20"/>
       <c r="AR58" s="20"/>
-      <c r="AS58" s="22"/>
+      <c r="AS58" s="24"/>
       <c r="AT58" s="15"/>
       <c r="AU58" s="15"/>
       <c r="AV58" s="15"/>
       <c r="AW58" s="15"/>
       <c r="AX58" s="15"/>
-      <c r="AY58" s="22"/>
-      <c r="AZ58" s="22"/>
+      <c r="AY58" s="24"/>
+      <c r="AZ58" s="24"/>
       <c r="BA58" s="15"/>
       <c r="BB58" s="15"/>
       <c r="BC58" s="15"/>
       <c r="BD58" s="15"/>
       <c r="BE58" s="18"/>
-      <c r="BF58" s="23"/>
-      <c r="BG58" s="24"/>
-      <c r="BH58" s="24"/>
-      <c r="BI58" s="24"/>
-      <c r="BJ58" s="24"/>
-      <c r="BK58" s="25"/>
+      <c r="BF58" s="25"/>
+      <c r="BG58" s="26"/>
+      <c r="BH58" s="26"/>
+      <c r="BI58" s="26"/>
+      <c r="BJ58" s="26"/>
+      <c r="BK58" s="27"/>
     </row>
     <row r="59">
       <c r="A59" s="44"/>
       <c r="B59" s="40"/>
       <c r="C59" s="20"/>
       <c r="D59" s="15"/>
-      <c r="E59" s="21"/>
+      <c r="E59" s="23"/>
       <c r="F59" s="20"/>
       <c r="G59" s="20"/>
       <c r="H59" s="20"/>
@@ -6938,12 +6916,12 @@
       <c r="K59" s="15"/>
       <c r="L59" s="19"/>
       <c r="M59" s="20"/>
-      <c r="N59" s="21"/>
+      <c r="N59" s="23"/>
       <c r="O59" s="15"/>
       <c r="P59" s="15"/>
       <c r="Q59" s="15"/>
       <c r="R59" s="19"/>
-      <c r="S59" s="21"/>
+      <c r="S59" s="23"/>
       <c r="T59" s="20"/>
       <c r="U59" s="20"/>
       <c r="V59" s="15"/>
@@ -6975,19 +6953,19 @@
       <c r="AV59" s="15"/>
       <c r="AW59" s="15"/>
       <c r="AX59" s="15"/>
-      <c r="AY59" s="22"/>
-      <c r="AZ59" s="22"/>
+      <c r="AY59" s="24"/>
+      <c r="AZ59" s="24"/>
       <c r="BA59" s="15"/>
       <c r="BB59" s="15"/>
       <c r="BC59" s="15"/>
       <c r="BD59" s="15"/>
       <c r="BE59" s="18"/>
-      <c r="BF59" s="23"/>
-      <c r="BG59" s="24"/>
-      <c r="BH59" s="24"/>
-      <c r="BI59" s="24"/>
-      <c r="BJ59" s="24"/>
-      <c r="BK59" s="25"/>
+      <c r="BF59" s="25"/>
+      <c r="BG59" s="26"/>
+      <c r="BH59" s="26"/>
+      <c r="BI59" s="26"/>
+      <c r="BJ59" s="26"/>
+      <c r="BK59" s="27"/>
     </row>
     <row r="60">
       <c r="A60" s="15"/>
@@ -7003,7 +6981,7 @@
       <c r="K60" s="15"/>
       <c r="L60" s="19"/>
       <c r="M60" s="20"/>
-      <c r="N60" s="21"/>
+      <c r="N60" s="23"/>
       <c r="O60" s="20"/>
       <c r="P60" s="15"/>
       <c r="Q60" s="15"/>
@@ -7034,23 +7012,23 @@
       <c r="AP60" s="18"/>
       <c r="AQ60" s="20"/>
       <c r="AR60" s="20"/>
-      <c r="AS60" s="22"/>
+      <c r="AS60" s="24"/>
       <c r="AT60" s="15"/>
       <c r="AU60" s="15"/>
       <c r="AV60" s="15"/>
       <c r="AW60" s="15"/>
       <c r="AX60" s="15"/>
-      <c r="AY60" s="22"/>
-      <c r="AZ60" s="22"/>
+      <c r="AY60" s="24"/>
+      <c r="AZ60" s="24"/>
       <c r="BA60" s="15"/>
       <c r="BB60" s="15"/>
       <c r="BC60" s="18"/>
       <c r="BD60" s="15"/>
       <c r="BE60" s="18"/>
-      <c r="BF60" s="23"/>
-      <c r="BG60" s="24"/>
-      <c r="BH60" s="24"/>
-      <c r="BI60" s="24"/>
+      <c r="BF60" s="25"/>
+      <c r="BG60" s="26"/>
+      <c r="BH60" s="26"/>
+      <c r="BI60" s="26"/>
       <c r="BJ60" s="38"/>
       <c r="BK60" s="39"/>
     </row>
@@ -7059,7 +7037,7 @@
       <c r="B61" s="40"/>
       <c r="C61" s="20"/>
       <c r="D61" s="15"/>
-      <c r="E61" s="21"/>
+      <c r="E61" s="23"/>
       <c r="F61" s="20"/>
       <c r="G61" s="20"/>
       <c r="H61" s="20"/>
@@ -7068,7 +7046,7 @@
       <c r="K61" s="15"/>
       <c r="L61" s="19"/>
       <c r="M61" s="20"/>
-      <c r="N61" s="21"/>
+      <c r="N61" s="23"/>
       <c r="O61" s="20"/>
       <c r="P61" s="15"/>
       <c r="Q61" s="15"/>
@@ -7099,32 +7077,32 @@
       <c r="AP61" s="15"/>
       <c r="AQ61" s="20"/>
       <c r="AR61" s="20"/>
-      <c r="AS61" s="22"/>
+      <c r="AS61" s="24"/>
       <c r="AT61" s="15"/>
       <c r="AU61" s="15"/>
       <c r="AV61" s="15"/>
       <c r="AW61" s="15"/>
       <c r="AX61" s="15"/>
-      <c r="AY61" s="22"/>
-      <c r="AZ61" s="22"/>
+      <c r="AY61" s="24"/>
+      <c r="AZ61" s="24"/>
       <c r="BA61" s="15"/>
       <c r="BB61" s="15"/>
       <c r="BC61" s="15"/>
       <c r="BD61" s="15"/>
       <c r="BE61" s="18"/>
-      <c r="BF61" s="23"/>
-      <c r="BG61" s="24"/>
-      <c r="BH61" s="24"/>
-      <c r="BI61" s="24"/>
-      <c r="BJ61" s="24"/>
-      <c r="BK61" s="25"/>
+      <c r="BF61" s="25"/>
+      <c r="BG61" s="26"/>
+      <c r="BH61" s="26"/>
+      <c r="BI61" s="26"/>
+      <c r="BJ61" s="26"/>
+      <c r="BK61" s="27"/>
     </row>
     <row r="62">
       <c r="A62" s="44"/>
       <c r="B62" s="40"/>
       <c r="C62" s="20"/>
       <c r="D62" s="15"/>
-      <c r="E62" s="21"/>
+      <c r="E62" s="23"/>
       <c r="F62" s="20"/>
       <c r="G62" s="20"/>
       <c r="H62" s="20"/>
@@ -7133,12 +7111,12 @@
       <c r="K62" s="15"/>
       <c r="L62" s="19"/>
       <c r="M62" s="20"/>
-      <c r="N62" s="21"/>
+      <c r="N62" s="23"/>
       <c r="O62" s="15"/>
       <c r="P62" s="15"/>
       <c r="Q62" s="15"/>
       <c r="R62" s="19"/>
-      <c r="S62" s="21"/>
+      <c r="S62" s="23"/>
       <c r="T62" s="20"/>
       <c r="U62" s="20"/>
       <c r="V62" s="15"/>
@@ -7164,32 +7142,32 @@
       <c r="AP62" s="15"/>
       <c r="AQ62" s="20"/>
       <c r="AR62" s="20"/>
-      <c r="AS62" s="22"/>
+      <c r="AS62" s="24"/>
       <c r="AT62" s="15"/>
       <c r="AU62" s="50"/>
       <c r="AV62" s="50"/>
       <c r="AW62" s="50"/>
       <c r="AX62" s="50"/>
-      <c r="AY62" s="22"/>
-      <c r="AZ62" s="22"/>
+      <c r="AY62" s="24"/>
+      <c r="AZ62" s="24"/>
       <c r="BA62" s="15"/>
       <c r="BB62" s="15"/>
       <c r="BC62" s="15"/>
       <c r="BD62" s="15"/>
       <c r="BE62" s="18"/>
-      <c r="BF62" s="23"/>
-      <c r="BG62" s="24"/>
-      <c r="BH62" s="24"/>
-      <c r="BI62" s="24"/>
-      <c r="BJ62" s="24"/>
-      <c r="BK62" s="25"/>
+      <c r="BF62" s="25"/>
+      <c r="BG62" s="26"/>
+      <c r="BH62" s="26"/>
+      <c r="BI62" s="26"/>
+      <c r="BJ62" s="26"/>
+      <c r="BK62" s="27"/>
     </row>
     <row r="63">
       <c r="A63" s="44"/>
       <c r="B63" s="40"/>
       <c r="C63" s="20"/>
       <c r="D63" s="15"/>
-      <c r="E63" s="21"/>
+      <c r="E63" s="23"/>
       <c r="F63" s="20"/>
       <c r="G63" s="20"/>
       <c r="H63" s="20"/>
@@ -7198,12 +7176,12 @@
       <c r="K63" s="15"/>
       <c r="L63" s="19"/>
       <c r="M63" s="20"/>
-      <c r="N63" s="21"/>
+      <c r="N63" s="23"/>
       <c r="O63" s="20"/>
       <c r="P63" s="15"/>
       <c r="Q63" s="15"/>
       <c r="R63" s="19"/>
-      <c r="S63" s="21"/>
+      <c r="S63" s="23"/>
       <c r="T63" s="20"/>
       <c r="U63" s="20"/>
       <c r="V63" s="15"/>
@@ -7221,7 +7199,7 @@
       <c r="AH63" s="15"/>
       <c r="AI63" s="20"/>
       <c r="AJ63" s="20"/>
-      <c r="AK63" s="21"/>
+      <c r="AK63" s="23"/>
       <c r="AL63" s="20"/>
       <c r="AM63" s="18"/>
       <c r="AN63" s="15"/>
@@ -7229,32 +7207,32 @@
       <c r="AP63" s="15"/>
       <c r="AQ63" s="20"/>
       <c r="AR63" s="20"/>
-      <c r="AS63" s="22"/>
+      <c r="AS63" s="24"/>
       <c r="AT63" s="15"/>
       <c r="AU63" s="15"/>
       <c r="AV63" s="15"/>
       <c r="AW63" s="15"/>
       <c r="AX63" s="15"/>
-      <c r="AY63" s="22"/>
-      <c r="AZ63" s="22"/>
+      <c r="AY63" s="24"/>
+      <c r="AZ63" s="24"/>
       <c r="BA63" s="15"/>
       <c r="BB63" s="15"/>
       <c r="BC63" s="15"/>
       <c r="BD63" s="15"/>
       <c r="BE63" s="18"/>
-      <c r="BF63" s="23"/>
-      <c r="BG63" s="24"/>
-      <c r="BH63" s="24"/>
-      <c r="BI63" s="24"/>
-      <c r="BJ63" s="24"/>
-      <c r="BK63" s="25"/>
+      <c r="BF63" s="25"/>
+      <c r="BG63" s="26"/>
+      <c r="BH63" s="26"/>
+      <c r="BI63" s="26"/>
+      <c r="BJ63" s="26"/>
+      <c r="BK63" s="27"/>
     </row>
     <row r="64">
       <c r="A64" s="15"/>
       <c r="B64" s="40"/>
       <c r="C64" s="20"/>
       <c r="D64" s="15"/>
-      <c r="E64" s="21"/>
+      <c r="E64" s="23"/>
       <c r="F64" s="31"/>
       <c r="G64" s="31"/>
       <c r="H64" s="31"/>
@@ -7364,26 +7342,26 @@
       <c r="AV65" s="15"/>
       <c r="AW65" s="15"/>
       <c r="AX65" s="15"/>
-      <c r="AY65" s="22"/>
-      <c r="AZ65" s="22"/>
+      <c r="AY65" s="24"/>
+      <c r="AZ65" s="24"/>
       <c r="BA65" s="15"/>
       <c r="BB65" s="15"/>
       <c r="BC65" s="31"/>
       <c r="BD65" s="31"/>
       <c r="BE65" s="18"/>
-      <c r="BF65" s="23"/>
-      <c r="BG65" s="24"/>
-      <c r="BH65" s="24"/>
-      <c r="BI65" s="24"/>
-      <c r="BJ65" s="24"/>
-      <c r="BK65" s="25"/>
+      <c r="BF65" s="25"/>
+      <c r="BG65" s="26"/>
+      <c r="BH65" s="26"/>
+      <c r="BI65" s="26"/>
+      <c r="BJ65" s="26"/>
+      <c r="BK65" s="27"/>
     </row>
     <row r="66">
       <c r="A66" s="15"/>
       <c r="B66" s="40"/>
       <c r="C66" s="20"/>
       <c r="D66" s="15"/>
-      <c r="E66" s="21"/>
+      <c r="E66" s="23"/>
       <c r="F66" s="20"/>
       <c r="G66" s="20"/>
       <c r="H66" s="20"/>
@@ -7392,12 +7370,12 @@
       <c r="K66" s="15"/>
       <c r="L66" s="19"/>
       <c r="M66" s="20"/>
-      <c r="N66" s="21"/>
+      <c r="N66" s="23"/>
       <c r="O66" s="20"/>
       <c r="P66" s="15"/>
       <c r="Q66" s="15"/>
       <c r="R66" s="19"/>
-      <c r="S66" s="21"/>
+      <c r="S66" s="23"/>
       <c r="T66" s="20"/>
       <c r="U66" s="20"/>
       <c r="V66" s="15"/>
@@ -7423,32 +7401,32 @@
       <c r="AP66" s="15"/>
       <c r="AQ66" s="20"/>
       <c r="AR66" s="20"/>
-      <c r="AS66" s="22"/>
+      <c r="AS66" s="24"/>
       <c r="AT66" s="15"/>
       <c r="AU66" s="15"/>
       <c r="AV66" s="15"/>
       <c r="AW66" s="15"/>
       <c r="AX66" s="15"/>
-      <c r="AY66" s="22"/>
-      <c r="AZ66" s="22"/>
+      <c r="AY66" s="24"/>
+      <c r="AZ66" s="24"/>
       <c r="BA66" s="15"/>
       <c r="BB66" s="15"/>
       <c r="BC66" s="18"/>
       <c r="BD66" s="15"/>
       <c r="BE66" s="18"/>
-      <c r="BF66" s="23"/>
-      <c r="BG66" s="24"/>
-      <c r="BH66" s="24"/>
-      <c r="BI66" s="24"/>
-      <c r="BJ66" s="24"/>
-      <c r="BK66" s="25"/>
+      <c r="BF66" s="25"/>
+      <c r="BG66" s="26"/>
+      <c r="BH66" s="26"/>
+      <c r="BI66" s="26"/>
+      <c r="BJ66" s="26"/>
+      <c r="BK66" s="27"/>
     </row>
     <row r="67">
       <c r="A67" s="44"/>
       <c r="B67" s="40"/>
       <c r="C67" s="20"/>
       <c r="D67" s="15"/>
-      <c r="E67" s="21"/>
+      <c r="E67" s="23"/>
       <c r="F67" s="20"/>
       <c r="G67" s="20"/>
       <c r="H67" s="20"/>
@@ -7457,12 +7435,12 @@
       <c r="K67" s="15"/>
       <c r="L67" s="19"/>
       <c r="M67" s="20"/>
-      <c r="N67" s="21"/>
+      <c r="N67" s="23"/>
       <c r="O67" s="20"/>
       <c r="P67" s="15"/>
       <c r="Q67" s="15"/>
       <c r="R67" s="19"/>
-      <c r="S67" s="21"/>
+      <c r="S67" s="23"/>
       <c r="T67" s="20"/>
       <c r="U67" s="20"/>
       <c r="V67" s="15"/>
@@ -7488,25 +7466,25 @@
       <c r="AP67" s="15"/>
       <c r="AQ67" s="20"/>
       <c r="AR67" s="20"/>
-      <c r="AS67" s="22"/>
+      <c r="AS67" s="24"/>
       <c r="AT67" s="15"/>
       <c r="AU67" s="15"/>
       <c r="AV67" s="15"/>
       <c r="AW67" s="15"/>
       <c r="AX67" s="15"/>
-      <c r="AY67" s="22"/>
-      <c r="AZ67" s="22"/>
+      <c r="AY67" s="24"/>
+      <c r="AZ67" s="24"/>
       <c r="BA67" s="15"/>
       <c r="BB67" s="15"/>
       <c r="BC67" s="18"/>
       <c r="BD67" s="15"/>
       <c r="BE67" s="18"/>
-      <c r="BF67" s="23"/>
-      <c r="BG67" s="24"/>
-      <c r="BH67" s="24"/>
+      <c r="BF67" s="25"/>
+      <c r="BG67" s="26"/>
+      <c r="BH67" s="26"/>
       <c r="BI67" s="33"/>
-      <c r="BJ67" s="24"/>
-      <c r="BK67" s="25"/>
+      <c r="BJ67" s="26"/>
+      <c r="BK67" s="27"/>
     </row>
     <row r="68">
       <c r="A68" s="15"/>
@@ -7586,12 +7564,12 @@
       <c r="K69" s="15"/>
       <c r="L69" s="19"/>
       <c r="M69" s="20"/>
-      <c r="N69" s="21"/>
+      <c r="N69" s="23"/>
       <c r="O69" s="20"/>
       <c r="P69" s="15"/>
       <c r="Q69" s="15"/>
       <c r="R69" s="19"/>
-      <c r="S69" s="21"/>
+      <c r="S69" s="23"/>
       <c r="T69" s="20"/>
       <c r="U69" s="20"/>
       <c r="V69" s="15"/>
@@ -7609,7 +7587,7 @@
       <c r="AH69" s="15"/>
       <c r="AI69" s="15"/>
       <c r="AJ69" s="20"/>
-      <c r="AK69" s="21"/>
+      <c r="AK69" s="23"/>
       <c r="AL69" s="20"/>
       <c r="AM69" s="40"/>
       <c r="AN69" s="40"/>
@@ -7617,32 +7595,32 @@
       <c r="AP69" s="40"/>
       <c r="AQ69" s="20"/>
       <c r="AR69" s="20"/>
-      <c r="AS69" s="22"/>
+      <c r="AS69" s="24"/>
       <c r="AT69" s="15"/>
       <c r="AU69" s="15"/>
       <c r="AV69" s="15"/>
       <c r="AW69" s="15"/>
       <c r="AX69" s="15"/>
-      <c r="AY69" s="22"/>
-      <c r="AZ69" s="22"/>
+      <c r="AY69" s="24"/>
+      <c r="AZ69" s="24"/>
       <c r="BA69" s="15"/>
       <c r="BB69" s="15"/>
       <c r="BC69" s="15"/>
       <c r="BD69" s="15"/>
       <c r="BE69" s="18"/>
-      <c r="BF69" s="23"/>
-      <c r="BG69" s="24"/>
-      <c r="BH69" s="24"/>
-      <c r="BI69" s="24"/>
-      <c r="BJ69" s="24"/>
-      <c r="BK69" s="25"/>
+      <c r="BF69" s="25"/>
+      <c r="BG69" s="26"/>
+      <c r="BH69" s="26"/>
+      <c r="BI69" s="26"/>
+      <c r="BJ69" s="26"/>
+      <c r="BK69" s="27"/>
     </row>
     <row r="70">
       <c r="A70" s="44"/>
       <c r="B70" s="40"/>
       <c r="C70" s="20"/>
       <c r="D70" s="15"/>
-      <c r="E70" s="21"/>
+      <c r="E70" s="23"/>
       <c r="F70" s="20"/>
       <c r="G70" s="20"/>
       <c r="H70" s="20"/>
@@ -7651,12 +7629,12 @@
       <c r="K70" s="15"/>
       <c r="L70" s="19"/>
       <c r="M70" s="20"/>
-      <c r="N70" s="21"/>
+      <c r="N70" s="23"/>
       <c r="O70" s="20"/>
       <c r="P70" s="15"/>
       <c r="Q70" s="15"/>
       <c r="R70" s="19"/>
-      <c r="S70" s="21"/>
+      <c r="S70" s="23"/>
       <c r="T70" s="20"/>
       <c r="U70" s="20"/>
       <c r="V70" s="15"/>
@@ -7682,25 +7660,25 @@
       <c r="AP70" s="15"/>
       <c r="AQ70" s="20"/>
       <c r="AR70" s="20"/>
-      <c r="AS70" s="22"/>
+      <c r="AS70" s="24"/>
       <c r="AT70" s="15"/>
       <c r="AU70" s="15"/>
       <c r="AV70" s="15"/>
       <c r="AW70" s="15"/>
       <c r="AX70" s="15"/>
-      <c r="AY70" s="22"/>
-      <c r="AZ70" s="22"/>
+      <c r="AY70" s="24"/>
+      <c r="AZ70" s="24"/>
       <c r="BA70" s="15"/>
       <c r="BB70" s="15"/>
       <c r="BC70" s="15"/>
       <c r="BD70" s="15"/>
       <c r="BE70" s="18"/>
-      <c r="BF70" s="23"/>
-      <c r="BG70" s="24"/>
-      <c r="BH70" s="24"/>
-      <c r="BI70" s="24"/>
-      <c r="BJ70" s="24"/>
-      <c r="BK70" s="25"/>
+      <c r="BF70" s="25"/>
+      <c r="BG70" s="26"/>
+      <c r="BH70" s="26"/>
+      <c r="BI70" s="26"/>
+      <c r="BJ70" s="26"/>
+      <c r="BK70" s="27"/>
     </row>
     <row r="71">
       <c r="A71" s="15"/>
@@ -7753,26 +7731,26 @@
       <c r="AV71" s="31"/>
       <c r="AW71" s="31"/>
       <c r="AX71" s="31"/>
-      <c r="AY71" s="22"/>
-      <c r="AZ71" s="22"/>
+      <c r="AY71" s="24"/>
+      <c r="AZ71" s="24"/>
       <c r="BA71" s="15"/>
       <c r="BB71" s="15"/>
       <c r="BC71" s="31"/>
       <c r="BD71" s="31"/>
       <c r="BE71" s="18"/>
-      <c r="BF71" s="23"/>
-      <c r="BG71" s="24"/>
+      <c r="BF71" s="25"/>
+      <c r="BG71" s="26"/>
       <c r="BH71" s="32"/>
-      <c r="BI71" s="24"/>
-      <c r="BJ71" s="24"/>
-      <c r="BK71" s="25"/>
+      <c r="BI71" s="26"/>
+      <c r="BJ71" s="26"/>
+      <c r="BK71" s="27"/>
     </row>
     <row r="72">
       <c r="A72" s="15"/>
       <c r="B72" s="40"/>
       <c r="C72" s="20"/>
       <c r="D72" s="15"/>
-      <c r="E72" s="21"/>
+      <c r="E72" s="23"/>
       <c r="F72" s="20"/>
       <c r="G72" s="20"/>
       <c r="H72" s="20"/>
@@ -7781,12 +7759,12 @@
       <c r="K72" s="15"/>
       <c r="L72" s="19"/>
       <c r="M72" s="20"/>
-      <c r="N72" s="21"/>
+      <c r="N72" s="23"/>
       <c r="O72" s="15"/>
       <c r="P72" s="15"/>
       <c r="Q72" s="15"/>
       <c r="R72" s="19"/>
-      <c r="S72" s="21"/>
+      <c r="S72" s="23"/>
       <c r="T72" s="20"/>
       <c r="U72" s="20"/>
       <c r="V72" s="15"/>
@@ -7812,32 +7790,32 @@
       <c r="AP72" s="15"/>
       <c r="AQ72" s="20"/>
       <c r="AR72" s="20"/>
-      <c r="AS72" s="22"/>
+      <c r="AS72" s="24"/>
       <c r="AT72" s="15"/>
       <c r="AU72" s="15"/>
       <c r="AV72" s="15"/>
       <c r="AW72" s="15"/>
       <c r="AX72" s="15"/>
-      <c r="AY72" s="22"/>
-      <c r="AZ72" s="22"/>
+      <c r="AY72" s="24"/>
+      <c r="AZ72" s="24"/>
       <c r="BA72" s="15"/>
       <c r="BB72" s="15"/>
       <c r="BC72" s="15"/>
       <c r="BD72" s="15"/>
       <c r="BE72" s="18"/>
-      <c r="BF72" s="23"/>
-      <c r="BG72" s="24"/>
-      <c r="BH72" s="24"/>
-      <c r="BI72" s="24"/>
-      <c r="BJ72" s="24"/>
-      <c r="BK72" s="25"/>
+      <c r="BF72" s="25"/>
+      <c r="BG72" s="26"/>
+      <c r="BH72" s="26"/>
+      <c r="BI72" s="26"/>
+      <c r="BJ72" s="26"/>
+      <c r="BK72" s="27"/>
     </row>
     <row r="73">
       <c r="A73" s="44"/>
       <c r="B73" s="40"/>
       <c r="C73" s="17"/>
       <c r="D73" s="15"/>
-      <c r="E73" s="21"/>
+      <c r="E73" s="23"/>
       <c r="F73" s="20"/>
       <c r="G73" s="20"/>
       <c r="H73" s="20"/>
@@ -7846,12 +7824,12 @@
       <c r="K73" s="15"/>
       <c r="L73" s="19"/>
       <c r="M73" s="20"/>
-      <c r="N73" s="21"/>
+      <c r="N73" s="23"/>
       <c r="O73" s="20"/>
       <c r="P73" s="15"/>
       <c r="Q73" s="15"/>
       <c r="R73" s="19"/>
-      <c r="S73" s="21"/>
+      <c r="S73" s="23"/>
       <c r="T73" s="15"/>
       <c r="U73" s="20"/>
       <c r="V73" s="15"/>
@@ -7877,13 +7855,13 @@
       <c r="AP73" s="40"/>
       <c r="AQ73" s="20"/>
       <c r="AR73" s="20"/>
-      <c r="AS73" s="22"/>
+      <c r="AS73" s="24"/>
       <c r="AT73" s="15"/>
       <c r="AU73" s="15"/>
       <c r="AV73" s="15"/>
       <c r="AW73" s="15"/>
       <c r="AX73" s="15"/>
-      <c r="AY73" s="22"/>
+      <c r="AY73" s="24"/>
       <c r="AZ73" s="15"/>
       <c r="BA73" s="15"/>
       <c r="BB73" s="15"/>
@@ -7891,18 +7869,18 @@
       <c r="BD73" s="15"/>
       <c r="BE73" s="18"/>
       <c r="BF73" s="41"/>
-      <c r="BG73" s="24"/>
-      <c r="BH73" s="24"/>
-      <c r="BI73" s="24"/>
-      <c r="BJ73" s="24"/>
-      <c r="BK73" s="25"/>
+      <c r="BG73" s="26"/>
+      <c r="BH73" s="26"/>
+      <c r="BI73" s="26"/>
+      <c r="BJ73" s="26"/>
+      <c r="BK73" s="27"/>
     </row>
     <row r="74">
       <c r="A74" s="15"/>
       <c r="B74" s="40"/>
       <c r="C74" s="17"/>
       <c r="D74" s="15"/>
-      <c r="E74" s="21"/>
+      <c r="E74" s="23"/>
       <c r="F74" s="31"/>
       <c r="G74" s="20"/>
       <c r="H74" s="31"/>
@@ -7948,26 +7926,26 @@
       <c r="AV74" s="15"/>
       <c r="AW74" s="15"/>
       <c r="AX74" s="15"/>
-      <c r="AY74" s="22"/>
-      <c r="AZ74" s="22"/>
+      <c r="AY74" s="24"/>
+      <c r="AZ74" s="24"/>
       <c r="BA74" s="31"/>
       <c r="BB74" s="31"/>
       <c r="BC74" s="31"/>
       <c r="BD74" s="31"/>
       <c r="BE74" s="18"/>
-      <c r="BF74" s="23"/>
-      <c r="BG74" s="24"/>
-      <c r="BH74" s="24"/>
-      <c r="BI74" s="24"/>
-      <c r="BJ74" s="24"/>
-      <c r="BK74" s="25"/>
+      <c r="BF74" s="25"/>
+      <c r="BG74" s="26"/>
+      <c r="BH74" s="26"/>
+      <c r="BI74" s="26"/>
+      <c r="BJ74" s="26"/>
+      <c r="BK74" s="27"/>
     </row>
     <row r="75">
       <c r="A75" s="15"/>
       <c r="B75" s="40"/>
       <c r="C75" s="37"/>
       <c r="D75" s="31"/>
-      <c r="E75" s="21"/>
+      <c r="E75" s="23"/>
       <c r="F75" s="31"/>
       <c r="G75" s="20"/>
       <c r="H75" s="20"/>
@@ -7999,7 +7977,7 @@
       <c r="AH75" s="31"/>
       <c r="AI75" s="20"/>
       <c r="AJ75" s="20"/>
-      <c r="AK75" s="21"/>
+      <c r="AK75" s="23"/>
       <c r="AL75" s="20"/>
       <c r="AM75" s="18"/>
       <c r="AN75" s="15"/>
@@ -8007,32 +7985,32 @@
       <c r="AP75" s="15"/>
       <c r="AQ75" s="31"/>
       <c r="AR75" s="31"/>
-      <c r="AS75" s="22"/>
+      <c r="AS75" s="24"/>
       <c r="AT75" s="15"/>
       <c r="AU75" s="15"/>
       <c r="AV75" s="15"/>
       <c r="AW75" s="15"/>
       <c r="AX75" s="15"/>
-      <c r="AY75" s="22"/>
-      <c r="AZ75" s="22"/>
+      <c r="AY75" s="24"/>
+      <c r="AZ75" s="24"/>
       <c r="BA75" s="31"/>
       <c r="BB75" s="31"/>
       <c r="BC75" s="31"/>
       <c r="BD75" s="31"/>
       <c r="BE75" s="18"/>
-      <c r="BF75" s="23"/>
-      <c r="BG75" s="24"/>
-      <c r="BH75" s="24"/>
-      <c r="BI75" s="24"/>
-      <c r="BJ75" s="24"/>
-      <c r="BK75" s="25"/>
+      <c r="BF75" s="25"/>
+      <c r="BG75" s="26"/>
+      <c r="BH75" s="26"/>
+      <c r="BI75" s="26"/>
+      <c r="BJ75" s="26"/>
+      <c r="BK75" s="27"/>
     </row>
     <row r="76">
       <c r="A76" s="44"/>
       <c r="B76" s="40"/>
       <c r="C76" s="17"/>
       <c r="D76" s="15"/>
-      <c r="E76" s="21"/>
+      <c r="E76" s="23"/>
       <c r="F76" s="40"/>
       <c r="G76" s="20"/>
       <c r="H76" s="20"/>
@@ -8046,7 +8024,7 @@
       <c r="P76" s="15"/>
       <c r="Q76" s="15"/>
       <c r="R76" s="19"/>
-      <c r="S76" s="21"/>
+      <c r="S76" s="23"/>
       <c r="T76" s="15"/>
       <c r="U76" s="20"/>
       <c r="V76" s="15"/>
@@ -8072,32 +8050,32 @@
       <c r="AP76" s="15"/>
       <c r="AQ76" s="20"/>
       <c r="AR76" s="20"/>
-      <c r="AS76" s="22"/>
+      <c r="AS76" s="24"/>
       <c r="AT76" s="15"/>
       <c r="AU76" s="15"/>
       <c r="AV76" s="15"/>
       <c r="AW76" s="15"/>
       <c r="AX76" s="15"/>
-      <c r="AY76" s="22"/>
-      <c r="AZ76" s="22"/>
+      <c r="AY76" s="24"/>
+      <c r="AZ76" s="24"/>
       <c r="BA76" s="50"/>
       <c r="BB76" s="50"/>
       <c r="BC76" s="15"/>
       <c r="BD76" s="15"/>
       <c r="BE76" s="18"/>
-      <c r="BF76" s="23"/>
-      <c r="BG76" s="24"/>
+      <c r="BF76" s="25"/>
+      <c r="BG76" s="26"/>
       <c r="BH76" s="32"/>
       <c r="BI76" s="33"/>
-      <c r="BJ76" s="24"/>
-      <c r="BK76" s="25"/>
+      <c r="BJ76" s="26"/>
+      <c r="BK76" s="27"/>
     </row>
     <row r="77">
       <c r="A77" s="15"/>
       <c r="B77" s="40"/>
       <c r="C77" s="17"/>
       <c r="D77" s="15"/>
-      <c r="E77" s="21"/>
+      <c r="E77" s="23"/>
       <c r="F77" s="20"/>
       <c r="G77" s="20"/>
       <c r="H77" s="20"/>
@@ -8143,19 +8121,19 @@
       <c r="AV77" s="15"/>
       <c r="AW77" s="15"/>
       <c r="AX77" s="15"/>
-      <c r="AY77" s="22"/>
-      <c r="AZ77" s="22"/>
+      <c r="AY77" s="24"/>
+      <c r="AZ77" s="24"/>
       <c r="BA77" s="15"/>
       <c r="BB77" s="15"/>
       <c r="BC77" s="15"/>
       <c r="BD77" s="15"/>
       <c r="BE77" s="18"/>
-      <c r="BF77" s="23"/>
-      <c r="BG77" s="24"/>
-      <c r="BH77" s="24"/>
-      <c r="BI77" s="24"/>
-      <c r="BJ77" s="24"/>
-      <c r="BK77" s="25"/>
+      <c r="BF77" s="25"/>
+      <c r="BG77" s="26"/>
+      <c r="BH77" s="26"/>
+      <c r="BI77" s="26"/>
+      <c r="BJ77" s="26"/>
+      <c r="BK77" s="27"/>
     </row>
     <row r="78">
       <c r="A78" s="15"/>
@@ -8290,7 +8268,7 @@
       <c r="B80" s="40"/>
       <c r="C80" s="20"/>
       <c r="D80" s="15"/>
-      <c r="E80" s="21"/>
+      <c r="E80" s="23"/>
       <c r="F80" s="20"/>
       <c r="G80" s="20"/>
       <c r="H80" s="31"/>
@@ -8304,7 +8282,7 @@
       <c r="P80" s="15"/>
       <c r="Q80" s="15"/>
       <c r="R80" s="19"/>
-      <c r="S80" s="21"/>
+      <c r="S80" s="23"/>
       <c r="T80" s="20"/>
       <c r="U80" s="20"/>
       <c r="V80" s="15"/>
@@ -8322,7 +8300,7 @@
       <c r="AH80" s="31"/>
       <c r="AI80" s="20"/>
       <c r="AJ80" s="20"/>
-      <c r="AK80" s="21"/>
+      <c r="AK80" s="23"/>
       <c r="AL80" s="20"/>
       <c r="AM80" s="31"/>
       <c r="AN80" s="31"/>
@@ -8330,7 +8308,7 @@
       <c r="AP80" s="31"/>
       <c r="AQ80" s="20"/>
       <c r="AR80" s="20"/>
-      <c r="AS80" s="22"/>
+      <c r="AS80" s="24"/>
       <c r="AT80" s="15"/>
       <c r="AU80" s="15"/>
       <c r="AV80" s="15"/>
@@ -8343,12 +8321,12 @@
       <c r="BC80" s="15"/>
       <c r="BD80" s="15"/>
       <c r="BE80" s="18"/>
-      <c r="BF80" s="23"/>
-      <c r="BG80" s="24"/>
-      <c r="BH80" s="24"/>
-      <c r="BI80" s="24"/>
-      <c r="BJ80" s="24"/>
-      <c r="BK80" s="25"/>
+      <c r="BF80" s="25"/>
+      <c r="BG80" s="26"/>
+      <c r="BH80" s="26"/>
+      <c r="BI80" s="26"/>
+      <c r="BJ80" s="26"/>
+      <c r="BK80" s="27"/>
     </row>
     <row r="81">
       <c r="A81" s="15"/>
@@ -8364,12 +8342,12 @@
       <c r="K81" s="15"/>
       <c r="L81" s="19"/>
       <c r="M81" s="20"/>
-      <c r="N81" s="21"/>
+      <c r="N81" s="23"/>
       <c r="O81" s="20"/>
       <c r="P81" s="15"/>
       <c r="Q81" s="15"/>
       <c r="R81" s="19"/>
-      <c r="S81" s="21"/>
+      <c r="S81" s="23"/>
       <c r="T81" s="20"/>
       <c r="U81" s="20"/>
       <c r="V81" s="15"/>
@@ -8387,7 +8365,7 @@
       <c r="AH81" s="15"/>
       <c r="AI81" s="20"/>
       <c r="AJ81" s="20"/>
-      <c r="AK81" s="21"/>
+      <c r="AK81" s="23"/>
       <c r="AL81" s="20"/>
       <c r="AM81" s="18"/>
       <c r="AN81" s="15"/>
@@ -8395,23 +8373,23 @@
       <c r="AP81" s="18"/>
       <c r="AQ81" s="20"/>
       <c r="AR81" s="20"/>
-      <c r="AS81" s="22"/>
+      <c r="AS81" s="24"/>
       <c r="AT81" s="15"/>
       <c r="AU81" s="15"/>
       <c r="AV81" s="15"/>
       <c r="AW81" s="15"/>
       <c r="AX81" s="15"/>
-      <c r="AY81" s="22"/>
-      <c r="AZ81" s="22"/>
+      <c r="AY81" s="24"/>
+      <c r="AZ81" s="24"/>
       <c r="BA81" s="15"/>
       <c r="BB81" s="15"/>
       <c r="BC81" s="18"/>
       <c r="BD81" s="15"/>
       <c r="BE81" s="18"/>
       <c r="BF81" s="41"/>
-      <c r="BG81" s="24"/>
-      <c r="BH81" s="24"/>
-      <c r="BI81" s="24"/>
+      <c r="BG81" s="26"/>
+      <c r="BH81" s="26"/>
+      <c r="BI81" s="26"/>
       <c r="BJ81" s="38"/>
       <c r="BK81" s="39"/>
     </row>
@@ -8429,12 +8407,12 @@
       <c r="K82" s="15"/>
       <c r="L82" s="19"/>
       <c r="M82" s="20"/>
-      <c r="N82" s="21"/>
+      <c r="N82" s="23"/>
       <c r="O82" s="20"/>
       <c r="P82" s="15"/>
       <c r="Q82" s="15"/>
       <c r="R82" s="19"/>
-      <c r="S82" s="21"/>
+      <c r="S82" s="23"/>
       <c r="T82" s="20"/>
       <c r="U82" s="20"/>
       <c r="V82" s="15"/>
@@ -8460,32 +8438,32 @@
       <c r="AP82" s="15"/>
       <c r="AQ82" s="20"/>
       <c r="AR82" s="20"/>
-      <c r="AS82" s="22"/>
+      <c r="AS82" s="24"/>
       <c r="AT82" s="15"/>
       <c r="AU82" s="15"/>
       <c r="AV82" s="15"/>
       <c r="AW82" s="15"/>
       <c r="AX82" s="15"/>
-      <c r="AY82" s="22"/>
-      <c r="AZ82" s="22"/>
+      <c r="AY82" s="24"/>
+      <c r="AZ82" s="24"/>
       <c r="BA82" s="15"/>
       <c r="BB82" s="15"/>
       <c r="BC82" s="15"/>
       <c r="BD82" s="15"/>
       <c r="BE82" s="18"/>
-      <c r="BF82" s="23"/>
-      <c r="BG82" s="24"/>
-      <c r="BH82" s="24"/>
-      <c r="BI82" s="24"/>
-      <c r="BJ82" s="24"/>
-      <c r="BK82" s="25"/>
+      <c r="BF82" s="25"/>
+      <c r="BG82" s="26"/>
+      <c r="BH82" s="26"/>
+      <c r="BI82" s="26"/>
+      <c r="BJ82" s="26"/>
+      <c r="BK82" s="27"/>
     </row>
     <row r="83">
       <c r="A83" s="44"/>
       <c r="B83" s="40"/>
       <c r="C83" s="17"/>
       <c r="D83" s="15"/>
-      <c r="E83" s="21"/>
+      <c r="E83" s="23"/>
       <c r="F83" s="20"/>
       <c r="G83" s="20"/>
       <c r="H83" s="20"/>
@@ -8494,7 +8472,7 @@
       <c r="K83" s="15"/>
       <c r="L83" s="19"/>
       <c r="M83" s="20"/>
-      <c r="N83" s="21"/>
+      <c r="N83" s="23"/>
       <c r="O83" s="20"/>
       <c r="P83" s="15"/>
       <c r="Q83" s="15"/>
@@ -8525,32 +8503,32 @@
       <c r="AP83" s="15"/>
       <c r="AQ83" s="20"/>
       <c r="AR83" s="20"/>
-      <c r="AS83" s="22"/>
+      <c r="AS83" s="24"/>
       <c r="AT83" s="15"/>
       <c r="AU83" s="15"/>
       <c r="AV83" s="15"/>
       <c r="AW83" s="15"/>
       <c r="AX83" s="15"/>
-      <c r="AY83" s="22"/>
-      <c r="AZ83" s="22"/>
+      <c r="AY83" s="24"/>
+      <c r="AZ83" s="24"/>
       <c r="BA83" s="15"/>
       <c r="BB83" s="15"/>
       <c r="BC83" s="18"/>
       <c r="BD83" s="15"/>
       <c r="BE83" s="18"/>
-      <c r="BF83" s="23"/>
-      <c r="BG83" s="24"/>
-      <c r="BH83" s="24"/>
-      <c r="BI83" s="24"/>
-      <c r="BJ83" s="24"/>
-      <c r="BK83" s="25"/>
+      <c r="BF83" s="25"/>
+      <c r="BG83" s="26"/>
+      <c r="BH83" s="26"/>
+      <c r="BI83" s="26"/>
+      <c r="BJ83" s="26"/>
+      <c r="BK83" s="27"/>
     </row>
     <row r="84">
       <c r="A84" s="15"/>
       <c r="B84" s="40"/>
       <c r="C84" s="20"/>
       <c r="D84" s="15"/>
-      <c r="E84" s="21"/>
+      <c r="E84" s="23"/>
       <c r="F84" s="31"/>
       <c r="G84" s="20"/>
       <c r="H84" s="20"/>
@@ -8614,7 +8592,7 @@
       <c r="B85" s="40"/>
       <c r="C85" s="20"/>
       <c r="D85" s="15"/>
-      <c r="E85" s="21"/>
+      <c r="E85" s="23"/>
       <c r="F85" s="20"/>
       <c r="G85" s="20"/>
       <c r="H85" s="20"/>
@@ -8623,12 +8601,12 @@
       <c r="K85" s="15"/>
       <c r="L85" s="19"/>
       <c r="M85" s="20"/>
-      <c r="N85" s="21"/>
+      <c r="N85" s="23"/>
       <c r="O85" s="20"/>
       <c r="P85" s="15"/>
       <c r="Q85" s="15"/>
       <c r="R85" s="19"/>
-      <c r="S85" s="21"/>
+      <c r="S85" s="23"/>
       <c r="T85" s="20"/>
       <c r="U85" s="20"/>
       <c r="V85" s="15"/>
@@ -8654,23 +8632,23 @@
       <c r="AP85" s="15"/>
       <c r="AQ85" s="20"/>
       <c r="AR85" s="20"/>
-      <c r="AS85" s="22"/>
+      <c r="AS85" s="24"/>
       <c r="AT85" s="15"/>
       <c r="AU85" s="15"/>
       <c r="AV85" s="15"/>
       <c r="AW85" s="15"/>
       <c r="AX85" s="15"/>
-      <c r="AY85" s="22"/>
-      <c r="AZ85" s="22"/>
+      <c r="AY85" s="24"/>
+      <c r="AZ85" s="24"/>
       <c r="BA85" s="50"/>
       <c r="BB85" s="53"/>
       <c r="BC85" s="18"/>
-      <c r="BD85" s="47"/>
+      <c r="BD85" s="46"/>
       <c r="BE85" s="18"/>
-      <c r="BF85" s="23"/>
-      <c r="BG85" s="24"/>
+      <c r="BF85" s="25"/>
+      <c r="BG85" s="26"/>
       <c r="BH85" s="32"/>
-      <c r="BI85" s="24"/>
+      <c r="BI85" s="26"/>
       <c r="BJ85" s="38"/>
       <c r="BK85" s="39"/>
     </row>
@@ -8679,7 +8657,7 @@
       <c r="B86" s="40"/>
       <c r="C86" s="20"/>
       <c r="D86" s="15"/>
-      <c r="E86" s="21"/>
+      <c r="E86" s="23"/>
       <c r="F86" s="20"/>
       <c r="G86" s="20"/>
       <c r="H86" s="20"/>
@@ -8688,12 +8666,12 @@
       <c r="K86" s="15"/>
       <c r="L86" s="19"/>
       <c r="M86" s="20"/>
-      <c r="N86" s="21"/>
+      <c r="N86" s="23"/>
       <c r="O86" s="20"/>
       <c r="P86" s="15"/>
       <c r="Q86" s="15"/>
       <c r="R86" s="19"/>
-      <c r="S86" s="21"/>
+      <c r="S86" s="23"/>
       <c r="T86" s="20"/>
       <c r="U86" s="20"/>
       <c r="V86" s="15"/>
@@ -8711,7 +8689,7 @@
       <c r="AH86" s="15"/>
       <c r="AI86" s="20"/>
       <c r="AJ86" s="20"/>
-      <c r="AK86" s="21"/>
+      <c r="AK86" s="23"/>
       <c r="AL86" s="20"/>
       <c r="AM86" s="18"/>
       <c r="AN86" s="15"/>
@@ -8719,32 +8697,32 @@
       <c r="AP86" s="15"/>
       <c r="AQ86" s="20"/>
       <c r="AR86" s="20"/>
-      <c r="AS86" s="22"/>
+      <c r="AS86" s="24"/>
       <c r="AT86" s="15"/>
       <c r="AU86" s="15"/>
       <c r="AV86" s="15"/>
       <c r="AW86" s="15"/>
       <c r="AX86" s="15"/>
-      <c r="AY86" s="22"/>
-      <c r="AZ86" s="22"/>
+      <c r="AY86" s="24"/>
+      <c r="AZ86" s="24"/>
       <c r="BA86" s="15"/>
       <c r="BB86" s="15"/>
       <c r="BC86" s="15"/>
       <c r="BD86" s="15"/>
       <c r="BE86" s="18"/>
-      <c r="BF86" s="23"/>
-      <c r="BG86" s="24"/>
-      <c r="BH86" s="24"/>
-      <c r="BI86" s="24"/>
-      <c r="BJ86" s="24"/>
-      <c r="BK86" s="25"/>
+      <c r="BF86" s="25"/>
+      <c r="BG86" s="26"/>
+      <c r="BH86" s="26"/>
+      <c r="BI86" s="26"/>
+      <c r="BJ86" s="26"/>
+      <c r="BK86" s="27"/>
     </row>
     <row r="87">
       <c r="A87" s="15"/>
       <c r="B87" s="40"/>
       <c r="C87" s="20"/>
       <c r="D87" s="15"/>
-      <c r="E87" s="21"/>
+      <c r="E87" s="23"/>
       <c r="F87" s="20"/>
       <c r="G87" s="20"/>
       <c r="H87" s="20"/>
@@ -8753,12 +8731,12 @@
       <c r="K87" s="15"/>
       <c r="L87" s="19"/>
       <c r="M87" s="20"/>
-      <c r="N87" s="21"/>
+      <c r="N87" s="23"/>
       <c r="O87" s="15"/>
       <c r="P87" s="15"/>
       <c r="Q87" s="15"/>
       <c r="R87" s="19"/>
-      <c r="S87" s="21"/>
+      <c r="S87" s="23"/>
       <c r="T87" s="20"/>
       <c r="U87" s="20"/>
       <c r="V87" s="15"/>
@@ -8790,26 +8768,26 @@
       <c r="AV87" s="15"/>
       <c r="AW87" s="15"/>
       <c r="AX87" s="15"/>
-      <c r="AY87" s="22"/>
-      <c r="AZ87" s="22"/>
+      <c r="AY87" s="24"/>
+      <c r="AZ87" s="24"/>
       <c r="BA87" s="15"/>
-      <c r="BB87" s="47"/>
+      <c r="BB87" s="46"/>
       <c r="BC87" s="15"/>
-      <c r="BD87" s="47"/>
+      <c r="BD87" s="46"/>
       <c r="BE87" s="18"/>
-      <c r="BF87" s="23"/>
-      <c r="BG87" s="24"/>
-      <c r="BH87" s="24"/>
-      <c r="BI87" s="24"/>
-      <c r="BJ87" s="24"/>
-      <c r="BK87" s="25"/>
+      <c r="BF87" s="25"/>
+      <c r="BG87" s="26"/>
+      <c r="BH87" s="26"/>
+      <c r="BI87" s="26"/>
+      <c r="BJ87" s="26"/>
+      <c r="BK87" s="27"/>
     </row>
     <row r="88">
       <c r="A88" s="44"/>
       <c r="B88" s="40"/>
       <c r="C88" s="17"/>
       <c r="D88" s="15"/>
-      <c r="E88" s="21"/>
+      <c r="E88" s="23"/>
       <c r="F88" s="20"/>
       <c r="G88" s="20"/>
       <c r="H88" s="20"/>
@@ -8818,12 +8796,12 @@
       <c r="K88" s="15"/>
       <c r="L88" s="19"/>
       <c r="M88" s="20"/>
-      <c r="N88" s="21"/>
+      <c r="N88" s="23"/>
       <c r="O88" s="15"/>
       <c r="P88" s="15"/>
       <c r="Q88" s="15"/>
       <c r="R88" s="19"/>
-      <c r="S88" s="21"/>
+      <c r="S88" s="23"/>
       <c r="T88" s="15"/>
       <c r="U88" s="20"/>
       <c r="V88" s="15"/>
@@ -8855,26 +8833,26 @@
       <c r="AV88" s="15"/>
       <c r="AW88" s="15"/>
       <c r="AX88" s="15"/>
-      <c r="AY88" s="22"/>
-      <c r="AZ88" s="22"/>
+      <c r="AY88" s="24"/>
+      <c r="AZ88" s="24"/>
       <c r="BA88" s="15"/>
-      <c r="BB88" s="47"/>
+      <c r="BB88" s="46"/>
       <c r="BC88" s="18"/>
       <c r="BD88" s="15"/>
       <c r="BE88" s="18"/>
-      <c r="BF88" s="23"/>
+      <c r="BF88" s="25"/>
       <c r="BG88" s="32"/>
-      <c r="BH88" s="24"/>
+      <c r="BH88" s="26"/>
       <c r="BI88" s="33"/>
-      <c r="BJ88" s="24"/>
-      <c r="BK88" s="25"/>
+      <c r="BJ88" s="26"/>
+      <c r="BK88" s="27"/>
     </row>
     <row r="89">
       <c r="A89" s="44"/>
       <c r="B89" s="40"/>
       <c r="C89" s="17"/>
       <c r="D89" s="15"/>
-      <c r="E89" s="21"/>
+      <c r="E89" s="23"/>
       <c r="F89" s="20"/>
       <c r="G89" s="20"/>
       <c r="H89" s="20"/>
@@ -8883,7 +8861,7 @@
       <c r="K89" s="15"/>
       <c r="L89" s="19"/>
       <c r="M89" s="20"/>
-      <c r="N89" s="21"/>
+      <c r="N89" s="23"/>
       <c r="O89" s="15"/>
       <c r="P89" s="15"/>
       <c r="Q89" s="15"/>
@@ -8906,7 +8884,7 @@
       <c r="AH89" s="15"/>
       <c r="AI89" s="20"/>
       <c r="AJ89" s="20"/>
-      <c r="AK89" s="21"/>
+      <c r="AK89" s="23"/>
       <c r="AL89" s="20"/>
       <c r="AM89" s="18"/>
       <c r="AN89" s="15"/>
@@ -8914,23 +8892,23 @@
       <c r="AP89" s="18"/>
       <c r="AQ89" s="20"/>
       <c r="AR89" s="20"/>
-      <c r="AS89" s="22"/>
+      <c r="AS89" s="24"/>
       <c r="AT89" s="15"/>
       <c r="AU89" s="15"/>
       <c r="AV89" s="15"/>
       <c r="AW89" s="15"/>
       <c r="AX89" s="15"/>
-      <c r="AY89" s="22"/>
-      <c r="AZ89" s="22"/>
+      <c r="AY89" s="24"/>
+      <c r="AZ89" s="24"/>
       <c r="BA89" s="15"/>
       <c r="BB89" s="15"/>
       <c r="BC89" s="18"/>
       <c r="BD89" s="15"/>
       <c r="BE89" s="18"/>
-      <c r="BF89" s="23"/>
-      <c r="BG89" s="24"/>
+      <c r="BF89" s="25"/>
+      <c r="BG89" s="26"/>
       <c r="BH89" s="32"/>
-      <c r="BI89" s="24"/>
+      <c r="BI89" s="26"/>
       <c r="BJ89" s="38"/>
       <c r="BK89" s="39"/>
     </row>
@@ -8939,7 +8917,7 @@
       <c r="B90" s="40"/>
       <c r="C90" s="17"/>
       <c r="D90" s="15"/>
-      <c r="E90" s="21"/>
+      <c r="E90" s="23"/>
       <c r="F90" s="20"/>
       <c r="G90" s="20"/>
       <c r="H90" s="20"/>
@@ -8948,12 +8926,12 @@
       <c r="K90" s="15"/>
       <c r="L90" s="19"/>
       <c r="M90" s="20"/>
-      <c r="N90" s="21"/>
+      <c r="N90" s="23"/>
       <c r="O90" s="20"/>
       <c r="P90" s="15"/>
       <c r="Q90" s="15"/>
       <c r="R90" s="19"/>
-      <c r="S90" s="21"/>
+      <c r="S90" s="23"/>
       <c r="T90" s="20"/>
       <c r="U90" s="20"/>
       <c r="V90" s="15"/>
@@ -8979,25 +8957,25 @@
       <c r="AP90" s="15"/>
       <c r="AQ90" s="20"/>
       <c r="AR90" s="20"/>
-      <c r="AS90" s="22"/>
+      <c r="AS90" s="24"/>
       <c r="AT90" s="15"/>
       <c r="AU90" s="15"/>
       <c r="AV90" s="15"/>
       <c r="AW90" s="15"/>
       <c r="AX90" s="15"/>
-      <c r="AY90" s="22"/>
-      <c r="AZ90" s="22"/>
+      <c r="AY90" s="24"/>
+      <c r="AZ90" s="24"/>
       <c r="BA90" s="15"/>
       <c r="BB90" s="15"/>
       <c r="BC90" s="18"/>
-      <c r="BD90" s="47"/>
+      <c r="BD90" s="46"/>
       <c r="BE90" s="18"/>
-      <c r="BF90" s="23"/>
-      <c r="BG90" s="24"/>
-      <c r="BH90" s="24"/>
-      <c r="BI90" s="24"/>
-      <c r="BJ90" s="24"/>
-      <c r="BK90" s="25"/>
+      <c r="BF90" s="25"/>
+      <c r="BG90" s="26"/>
+      <c r="BH90" s="26"/>
+      <c r="BI90" s="26"/>
+      <c r="BJ90" s="26"/>
+      <c r="BK90" s="27"/>
     </row>
     <row r="91">
       <c r="A91" s="44"/>
@@ -9013,12 +8991,12 @@
       <c r="K91" s="15"/>
       <c r="L91" s="19"/>
       <c r="M91" s="20"/>
-      <c r="N91" s="21"/>
+      <c r="N91" s="23"/>
       <c r="O91" s="20"/>
       <c r="P91" s="15"/>
       <c r="Q91" s="15"/>
       <c r="R91" s="19"/>
-      <c r="S91" s="21"/>
+      <c r="S91" s="23"/>
       <c r="T91" s="20"/>
       <c r="U91" s="20"/>
       <c r="V91" s="15"/>
@@ -9044,25 +9022,25 @@
       <c r="AP91" s="15"/>
       <c r="AQ91" s="20"/>
       <c r="AR91" s="20"/>
-      <c r="AS91" s="22"/>
+      <c r="AS91" s="24"/>
       <c r="AT91" s="15"/>
       <c r="AU91" s="15"/>
       <c r="AV91" s="15"/>
       <c r="AW91" s="15"/>
       <c r="AX91" s="15"/>
-      <c r="AY91" s="22"/>
-      <c r="AZ91" s="22"/>
+      <c r="AY91" s="24"/>
+      <c r="AZ91" s="24"/>
       <c r="BA91" s="15"/>
       <c r="BB91" s="15"/>
       <c r="BC91" s="18"/>
       <c r="BD91" s="15"/>
       <c r="BE91" s="18"/>
-      <c r="BF91" s="23"/>
-      <c r="BG91" s="24"/>
-      <c r="BH91" s="24"/>
-      <c r="BI91" s="24"/>
-      <c r="BJ91" s="24"/>
-      <c r="BK91" s="25"/>
+      <c r="BF91" s="25"/>
+      <c r="BG91" s="26"/>
+      <c r="BH91" s="26"/>
+      <c r="BI91" s="26"/>
+      <c r="BJ91" s="26"/>
+      <c r="BK91" s="27"/>
     </row>
     <row r="92">
       <c r="A92" s="15"/>
@@ -9125,7 +9103,7 @@
       <c r="BF92" s="43"/>
       <c r="BG92" s="45"/>
       <c r="BH92" s="45"/>
-      <c r="BI92" s="24"/>
+      <c r="BI92" s="26"/>
       <c r="BJ92" s="38"/>
       <c r="BK92" s="39"/>
     </row>
@@ -9143,7 +9121,7 @@
       <c r="K93" s="15"/>
       <c r="L93" s="19"/>
       <c r="M93" s="20"/>
-      <c r="N93" s="21"/>
+      <c r="N93" s="23"/>
       <c r="O93" s="15"/>
       <c r="P93" s="15"/>
       <c r="Q93" s="15"/>
@@ -9166,7 +9144,7 @@
       <c r="AH93" s="15"/>
       <c r="AI93" s="20"/>
       <c r="AJ93" s="15"/>
-      <c r="AK93" s="21"/>
+      <c r="AK93" s="23"/>
       <c r="AL93" s="20"/>
       <c r="AM93" s="18"/>
       <c r="AN93" s="15"/>
@@ -9183,14 +9161,14 @@
       <c r="AY93" s="31"/>
       <c r="AZ93" s="31"/>
       <c r="BA93" s="15"/>
-      <c r="BB93" s="47"/>
+      <c r="BB93" s="46"/>
       <c r="BC93" s="15"/>
-      <c r="BD93" s="47"/>
+      <c r="BD93" s="46"/>
       <c r="BE93" s="18"/>
-      <c r="BF93" s="23"/>
-      <c r="BG93" s="24"/>
-      <c r="BH93" s="24"/>
-      <c r="BI93" s="24"/>
+      <c r="BF93" s="25"/>
+      <c r="BG93" s="26"/>
+      <c r="BH93" s="26"/>
+      <c r="BI93" s="26"/>
       <c r="BJ93" s="38"/>
       <c r="BK93" s="39"/>
     </row>
@@ -9199,7 +9177,7 @@
       <c r="B94" s="40"/>
       <c r="C94" s="17"/>
       <c r="D94" s="15"/>
-      <c r="E94" s="21"/>
+      <c r="E94" s="23"/>
       <c r="F94" s="20"/>
       <c r="G94" s="20"/>
       <c r="H94" s="20"/>
@@ -9208,12 +9186,12 @@
       <c r="K94" s="15"/>
       <c r="L94" s="19"/>
       <c r="M94" s="20"/>
-      <c r="N94" s="21"/>
+      <c r="N94" s="23"/>
       <c r="O94" s="15"/>
       <c r="P94" s="15"/>
       <c r="Q94" s="15"/>
       <c r="R94" s="19"/>
-      <c r="S94" s="21"/>
+      <c r="S94" s="23"/>
       <c r="T94" s="20"/>
       <c r="U94" s="20"/>
       <c r="V94" s="15"/>
@@ -9239,23 +9217,23 @@
       <c r="AP94" s="15"/>
       <c r="AQ94" s="20"/>
       <c r="AR94" s="20"/>
-      <c r="AS94" s="22"/>
+      <c r="AS94" s="24"/>
       <c r="AT94" s="15"/>
       <c r="AU94" s="15"/>
       <c r="AV94" s="15"/>
       <c r="AW94" s="15"/>
       <c r="AX94" s="15"/>
-      <c r="AY94" s="22"/>
-      <c r="AZ94" s="22"/>
+      <c r="AY94" s="24"/>
+      <c r="AZ94" s="24"/>
       <c r="BA94" s="15"/>
-      <c r="BB94" s="47"/>
+      <c r="BB94" s="46"/>
       <c r="BC94" s="31"/>
       <c r="BD94" s="31"/>
       <c r="BE94" s="18"/>
-      <c r="BF94" s="23"/>
-      <c r="BG94" s="24"/>
+      <c r="BF94" s="25"/>
+      <c r="BG94" s="26"/>
       <c r="BH94" s="32"/>
-      <c r="BI94" s="24"/>
+      <c r="BI94" s="26"/>
       <c r="BJ94" s="38"/>
       <c r="BK94" s="39"/>
     </row>
@@ -9264,7 +9242,7 @@
       <c r="B95" s="40"/>
       <c r="C95" s="20"/>
       <c r="D95" s="15"/>
-      <c r="E95" s="21"/>
+      <c r="E95" s="23"/>
       <c r="F95" s="20"/>
       <c r="G95" s="20"/>
       <c r="H95" s="20"/>
@@ -9273,12 +9251,12 @@
       <c r="K95" s="15"/>
       <c r="L95" s="19"/>
       <c r="M95" s="20"/>
-      <c r="N95" s="21"/>
+      <c r="N95" s="23"/>
       <c r="O95" s="20"/>
       <c r="P95" s="15"/>
       <c r="Q95" s="15"/>
       <c r="R95" s="19"/>
-      <c r="S95" s="21"/>
+      <c r="S95" s="23"/>
       <c r="T95" s="20"/>
       <c r="U95" s="20"/>
       <c r="V95" s="15"/>
@@ -9296,7 +9274,7 @@
       <c r="AH95" s="15"/>
       <c r="AI95" s="15"/>
       <c r="AJ95" s="20"/>
-      <c r="AK95" s="21"/>
+      <c r="AK95" s="23"/>
       <c r="AL95" s="20"/>
       <c r="AM95" s="18"/>
       <c r="AN95" s="15"/>
@@ -9304,32 +9282,32 @@
       <c r="AP95" s="18"/>
       <c r="AQ95" s="20"/>
       <c r="AR95" s="20"/>
-      <c r="AS95" s="22"/>
+      <c r="AS95" s="24"/>
       <c r="AT95" s="15"/>
       <c r="AU95" s="15"/>
       <c r="AV95" s="15"/>
       <c r="AW95" s="15"/>
       <c r="AX95" s="15"/>
-      <c r="AY95" s="22"/>
-      <c r="AZ95" s="22"/>
+      <c r="AY95" s="24"/>
+      <c r="AZ95" s="24"/>
       <c r="BA95" s="15"/>
-      <c r="BB95" s="47"/>
+      <c r="BB95" s="46"/>
       <c r="BC95" s="18"/>
       <c r="BD95" s="15"/>
       <c r="BE95" s="18"/>
-      <c r="BF95" s="23"/>
-      <c r="BG95" s="24"/>
+      <c r="BF95" s="25"/>
+      <c r="BG95" s="26"/>
       <c r="BH95" s="32"/>
-      <c r="BI95" s="24"/>
-      <c r="BJ95" s="24"/>
-      <c r="BK95" s="25"/>
+      <c r="BI95" s="26"/>
+      <c r="BJ95" s="26"/>
+      <c r="BK95" s="27"/>
     </row>
     <row r="96">
       <c r="A96" s="15"/>
       <c r="B96" s="40"/>
       <c r="C96" s="20"/>
       <c r="D96" s="15"/>
-      <c r="E96" s="21"/>
+      <c r="E96" s="23"/>
       <c r="F96" s="20"/>
       <c r="G96" s="20"/>
       <c r="H96" s="20"/>
@@ -9343,7 +9321,7 @@
       <c r="P96" s="15"/>
       <c r="Q96" s="15"/>
       <c r="R96" s="19"/>
-      <c r="S96" s="21"/>
+      <c r="S96" s="23"/>
       <c r="T96" s="20"/>
       <c r="U96" s="20"/>
       <c r="V96" s="15"/>
@@ -9369,32 +9347,32 @@
       <c r="AP96" s="15"/>
       <c r="AQ96" s="20"/>
       <c r="AR96" s="20"/>
-      <c r="AS96" s="22"/>
+      <c r="AS96" s="24"/>
       <c r="AT96" s="15"/>
       <c r="AU96" s="15"/>
       <c r="AV96" s="15"/>
       <c r="AW96" s="15"/>
       <c r="AX96" s="15"/>
-      <c r="AY96" s="22"/>
-      <c r="AZ96" s="22"/>
+      <c r="AY96" s="24"/>
+      <c r="AZ96" s="24"/>
       <c r="BA96" s="15"/>
       <c r="BB96" s="15"/>
       <c r="BC96" s="18"/>
       <c r="BD96" s="15"/>
       <c r="BE96" s="18"/>
-      <c r="BF96" s="23"/>
-      <c r="BG96" s="24"/>
-      <c r="BH96" s="24"/>
-      <c r="BI96" s="24"/>
-      <c r="BJ96" s="24"/>
-      <c r="BK96" s="25"/>
+      <c r="BF96" s="25"/>
+      <c r="BG96" s="26"/>
+      <c r="BH96" s="26"/>
+      <c r="BI96" s="26"/>
+      <c r="BJ96" s="26"/>
+      <c r="BK96" s="27"/>
     </row>
     <row r="97">
       <c r="A97" s="15"/>
       <c r="B97" s="40"/>
       <c r="C97" s="20"/>
       <c r="D97" s="15"/>
-      <c r="E97" s="21"/>
+      <c r="E97" s="23"/>
       <c r="F97" s="20"/>
       <c r="G97" s="20"/>
       <c r="H97" s="20"/>
@@ -9403,12 +9381,12 @@
       <c r="K97" s="15"/>
       <c r="L97" s="19"/>
       <c r="M97" s="19"/>
-      <c r="N97" s="21"/>
+      <c r="N97" s="23"/>
       <c r="O97" s="20"/>
       <c r="P97" s="15"/>
       <c r="Q97" s="15"/>
       <c r="R97" s="19"/>
-      <c r="S97" s="21"/>
+      <c r="S97" s="23"/>
       <c r="T97" s="20"/>
       <c r="U97" s="20"/>
       <c r="V97" s="15"/>
@@ -9426,7 +9404,7 @@
       <c r="AH97" s="15"/>
       <c r="AI97" s="20"/>
       <c r="AJ97" s="20"/>
-      <c r="AK97" s="21"/>
+      <c r="AK97" s="23"/>
       <c r="AL97" s="20"/>
       <c r="AM97" s="18"/>
       <c r="AN97" s="15"/>
@@ -9434,32 +9412,32 @@
       <c r="AP97" s="15"/>
       <c r="AQ97" s="20"/>
       <c r="AR97" s="20"/>
-      <c r="AS97" s="22"/>
+      <c r="AS97" s="24"/>
       <c r="AT97" s="15"/>
       <c r="AU97" s="15"/>
       <c r="AV97" s="15"/>
       <c r="AW97" s="15"/>
       <c r="AX97" s="15"/>
-      <c r="AY97" s="22"/>
-      <c r="AZ97" s="22"/>
+      <c r="AY97" s="24"/>
+      <c r="AZ97" s="24"/>
       <c r="BA97" s="15"/>
       <c r="BB97" s="15"/>
       <c r="BC97" s="18"/>
-      <c r="BD97" s="47"/>
+      <c r="BD97" s="46"/>
       <c r="BE97" s="18"/>
       <c r="BF97" s="54"/>
-      <c r="BG97" s="24"/>
-      <c r="BH97" s="24"/>
-      <c r="BI97" s="24"/>
-      <c r="BJ97" s="24"/>
-      <c r="BK97" s="25"/>
+      <c r="BG97" s="26"/>
+      <c r="BH97" s="26"/>
+      <c r="BI97" s="26"/>
+      <c r="BJ97" s="26"/>
+      <c r="BK97" s="27"/>
     </row>
     <row r="98">
       <c r="A98" s="15"/>
       <c r="B98" s="40"/>
       <c r="C98" s="20"/>
       <c r="D98" s="15"/>
-      <c r="E98" s="21"/>
+      <c r="E98" s="23"/>
       <c r="F98" s="20"/>
       <c r="G98" s="20"/>
       <c r="H98" s="20"/>
@@ -9468,12 +9446,12 @@
       <c r="K98" s="15"/>
       <c r="L98" s="19"/>
       <c r="M98" s="20"/>
-      <c r="N98" s="21"/>
+      <c r="N98" s="23"/>
       <c r="O98" s="20"/>
       <c r="P98" s="15"/>
       <c r="Q98" s="15"/>
       <c r="R98" s="19"/>
-      <c r="S98" s="21"/>
+      <c r="S98" s="23"/>
       <c r="T98" s="20"/>
       <c r="U98" s="20"/>
       <c r="V98" s="15"/>
@@ -9491,7 +9469,7 @@
       <c r="AH98" s="15"/>
       <c r="AI98" s="20"/>
       <c r="AJ98" s="20"/>
-      <c r="AK98" s="21"/>
+      <c r="AK98" s="23"/>
       <c r="AL98" s="20"/>
       <c r="AM98" s="18"/>
       <c r="AN98" s="15"/>
@@ -9499,32 +9477,32 @@
       <c r="AP98" s="15"/>
       <c r="AQ98" s="20"/>
       <c r="AR98" s="20"/>
-      <c r="AS98" s="22"/>
+      <c r="AS98" s="24"/>
       <c r="AT98" s="15"/>
       <c r="AU98" s="15"/>
       <c r="AV98" s="15"/>
       <c r="AW98" s="15"/>
       <c r="AX98" s="15"/>
-      <c r="AY98" s="22"/>
-      <c r="AZ98" s="22"/>
+      <c r="AY98" s="24"/>
+      <c r="AZ98" s="24"/>
       <c r="BA98" s="15"/>
       <c r="BB98" s="15"/>
       <c r="BC98" s="15"/>
       <c r="BD98" s="15"/>
       <c r="BE98" s="18"/>
       <c r="BF98" s="55"/>
-      <c r="BG98" s="24"/>
-      <c r="BH98" s="24"/>
-      <c r="BI98" s="24"/>
-      <c r="BJ98" s="24"/>
-      <c r="BK98" s="25"/>
+      <c r="BG98" s="26"/>
+      <c r="BH98" s="26"/>
+      <c r="BI98" s="26"/>
+      <c r="BJ98" s="26"/>
+      <c r="BK98" s="27"/>
     </row>
     <row r="99">
       <c r="A99" s="44"/>
       <c r="B99" s="40"/>
       <c r="C99" s="20"/>
       <c r="D99" s="15"/>
-      <c r="E99" s="21"/>
+      <c r="E99" s="23"/>
       <c r="F99" s="20"/>
       <c r="G99" s="20"/>
       <c r="H99" s="20"/>
@@ -9533,12 +9511,12 @@
       <c r="K99" s="15"/>
       <c r="L99" s="19"/>
       <c r="M99" s="20"/>
-      <c r="N99" s="21"/>
+      <c r="N99" s="23"/>
       <c r="O99" s="20"/>
       <c r="P99" s="15"/>
       <c r="Q99" s="15"/>
       <c r="R99" s="19"/>
-      <c r="S99" s="21"/>
+      <c r="S99" s="23"/>
       <c r="T99" s="20"/>
       <c r="U99" s="20"/>
       <c r="V99" s="15"/>
@@ -9564,23 +9542,23 @@
       <c r="AP99" s="15"/>
       <c r="AQ99" s="20"/>
       <c r="AR99" s="20"/>
-      <c r="AS99" s="22"/>
+      <c r="AS99" s="24"/>
       <c r="AT99" s="15"/>
       <c r="AU99" s="15"/>
       <c r="AV99" s="15"/>
       <c r="AW99" s="15"/>
       <c r="AX99" s="15"/>
-      <c r="AY99" s="22"/>
-      <c r="AZ99" s="22"/>
+      <c r="AY99" s="24"/>
+      <c r="AZ99" s="24"/>
       <c r="BA99" s="15"/>
-      <c r="BB99" s="47"/>
+      <c r="BB99" s="46"/>
       <c r="BC99" s="18"/>
       <c r="BD99" s="15"/>
       <c r="BE99" s="18"/>
       <c r="BF99" s="55"/>
-      <c r="BG99" s="24"/>
+      <c r="BG99" s="26"/>
       <c r="BH99" s="32"/>
-      <c r="BI99" s="24"/>
+      <c r="BI99" s="26"/>
       <c r="BJ99" s="38"/>
       <c r="BK99" s="39"/>
     </row>
@@ -9589,7 +9567,7 @@
       <c r="B100" s="40"/>
       <c r="C100" s="17"/>
       <c r="D100" s="15"/>
-      <c r="E100" s="21"/>
+      <c r="E100" s="23"/>
       <c r="F100" s="20"/>
       <c r="G100" s="20"/>
       <c r="H100" s="20"/>
@@ -9598,7 +9576,7 @@
       <c r="K100" s="15"/>
       <c r="L100" s="19"/>
       <c r="M100" s="31"/>
-      <c r="N100" s="21"/>
+      <c r="N100" s="23"/>
       <c r="O100" s="15"/>
       <c r="P100" s="15"/>
       <c r="Q100" s="15"/>
@@ -9621,7 +9599,7 @@
       <c r="AH100" s="15"/>
       <c r="AI100" s="20"/>
       <c r="AJ100" s="20"/>
-      <c r="AK100" s="21"/>
+      <c r="AK100" s="23"/>
       <c r="AL100" s="20"/>
       <c r="AM100" s="18"/>
       <c r="AN100" s="15"/>
@@ -9629,25 +9607,25 @@
       <c r="AP100" s="15"/>
       <c r="AQ100" s="20"/>
       <c r="AR100" s="20"/>
-      <c r="AS100" s="22"/>
+      <c r="AS100" s="24"/>
       <c r="AT100" s="15"/>
       <c r="AU100" s="15"/>
       <c r="AV100" s="15"/>
       <c r="AW100" s="15"/>
       <c r="AX100" s="15"/>
-      <c r="AY100" s="22"/>
-      <c r="AZ100" s="22"/>
+      <c r="AY100" s="24"/>
+      <c r="AZ100" s="24"/>
       <c r="BA100" s="15"/>
-      <c r="BB100" s="47"/>
+      <c r="BB100" s="46"/>
       <c r="BC100" s="15"/>
-      <c r="BD100" s="47"/>
+      <c r="BD100" s="46"/>
       <c r="BE100" s="18"/>
-      <c r="BF100" s="23"/>
-      <c r="BG100" s="24"/>
-      <c r="BH100" s="24"/>
-      <c r="BI100" s="24"/>
-      <c r="BJ100" s="24"/>
-      <c r="BK100" s="25"/>
+      <c r="BF100" s="25"/>
+      <c r="BG100" s="26"/>
+      <c r="BH100" s="26"/>
+      <c r="BI100" s="26"/>
+      <c r="BJ100" s="26"/>
+      <c r="BK100" s="27"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c r="A101" s="15"/>
@@ -9668,7 +9646,7 @@
       <c r="P101" s="31"/>
       <c r="Q101" s="31"/>
       <c r="R101" s="31"/>
-      <c r="S101" s="21"/>
+      <c r="S101" s="23"/>
       <c r="T101" s="15"/>
       <c r="U101" s="20"/>
       <c r="V101" s="15"/>
@@ -9694,25 +9672,25 @@
       <c r="AP101" s="15"/>
       <c r="AQ101" s="20"/>
       <c r="AR101" s="20"/>
-      <c r="AS101" s="22"/>
+      <c r="AS101" s="24"/>
       <c r="AT101" s="15"/>
       <c r="AU101" s="15"/>
       <c r="AV101" s="15"/>
       <c r="AW101" s="15"/>
       <c r="AX101" s="15"/>
-      <c r="AY101" s="22"/>
-      <c r="AZ101" s="22"/>
+      <c r="AY101" s="24"/>
+      <c r="AZ101" s="24"/>
       <c r="BA101" s="15"/>
-      <c r="BB101" s="47"/>
+      <c r="BB101" s="46"/>
       <c r="BC101" s="15"/>
-      <c r="BD101" s="47"/>
+      <c r="BD101" s="46"/>
       <c r="BE101" s="18"/>
-      <c r="BF101" s="23"/>
-      <c r="BG101" s="24"/>
-      <c r="BH101" s="24"/>
-      <c r="BI101" s="24"/>
-      <c r="BJ101" s="24"/>
-      <c r="BK101" s="25"/>
+      <c r="BF101" s="25"/>
+      <c r="BG101" s="26"/>
+      <c r="BH101" s="26"/>
+      <c r="BI101" s="26"/>
+      <c r="BJ101" s="26"/>
+      <c r="BK101" s="27"/>
     </row>
     <row r="102">
       <c r="A102" s="15"/>
@@ -9728,7 +9706,7 @@
       <c r="K102" s="15"/>
       <c r="L102" s="19"/>
       <c r="M102" s="20"/>
-      <c r="N102" s="21"/>
+      <c r="N102" s="23"/>
       <c r="O102" s="20"/>
       <c r="P102" s="15"/>
       <c r="Q102" s="15"/>
@@ -9751,7 +9729,7 @@
       <c r="AH102" s="15"/>
       <c r="AI102" s="20"/>
       <c r="AJ102" s="20"/>
-      <c r="AK102" s="21"/>
+      <c r="AK102" s="23"/>
       <c r="AL102" s="20"/>
       <c r="AM102" s="18"/>
       <c r="AN102" s="15"/>
@@ -9759,32 +9737,32 @@
       <c r="AP102" s="18"/>
       <c r="AQ102" s="20"/>
       <c r="AR102" s="20"/>
-      <c r="AS102" s="22"/>
+      <c r="AS102" s="24"/>
       <c r="AT102" s="31"/>
       <c r="AU102" s="15"/>
       <c r="AV102" s="15"/>
       <c r="AW102" s="15"/>
       <c r="AX102" s="15"/>
-      <c r="AY102" s="22"/>
-      <c r="AZ102" s="22"/>
+      <c r="AY102" s="24"/>
+      <c r="AZ102" s="24"/>
       <c r="BA102" s="31"/>
       <c r="BB102" s="42"/>
       <c r="BC102" s="15"/>
       <c r="BD102" s="15"/>
       <c r="BE102" s="15"/>
       <c r="BF102" s="55"/>
-      <c r="BG102" s="24"/>
-      <c r="BH102" s="24"/>
+      <c r="BG102" s="26"/>
+      <c r="BH102" s="26"/>
       <c r="BI102" s="33"/>
-      <c r="BJ102" s="24"/>
-      <c r="BK102" s="25"/>
+      <c r="BJ102" s="26"/>
+      <c r="BK102" s="27"/>
     </row>
     <row r="103">
       <c r="A103" s="15"/>
       <c r="B103" s="40"/>
       <c r="C103" s="20"/>
       <c r="D103" s="15"/>
-      <c r="E103" s="21"/>
+      <c r="E103" s="23"/>
       <c r="F103" s="20"/>
       <c r="G103" s="31"/>
       <c r="H103" s="31"/>
@@ -9848,7 +9826,7 @@
       <c r="B104" s="40"/>
       <c r="C104" s="20"/>
       <c r="D104" s="15"/>
-      <c r="E104" s="21"/>
+      <c r="E104" s="23"/>
       <c r="F104" s="20"/>
       <c r="G104" s="20"/>
       <c r="H104" s="20"/>
@@ -9857,12 +9835,12 @@
       <c r="K104" s="15"/>
       <c r="L104" s="19"/>
       <c r="M104" s="20"/>
-      <c r="N104" s="21"/>
+      <c r="N104" s="23"/>
       <c r="O104" s="20"/>
       <c r="P104" s="15"/>
       <c r="Q104" s="15"/>
       <c r="R104" s="15"/>
-      <c r="S104" s="21"/>
+      <c r="S104" s="23"/>
       <c r="T104" s="20"/>
       <c r="U104" s="20"/>
       <c r="V104" s="15"/>
@@ -9888,23 +9866,23 @@
       <c r="AP104" s="15"/>
       <c r="AQ104" s="20"/>
       <c r="AR104" s="20"/>
-      <c r="AS104" s="22"/>
+      <c r="AS104" s="24"/>
       <c r="AT104" s="15"/>
       <c r="AU104" s="15"/>
       <c r="AV104" s="15"/>
       <c r="AW104" s="15"/>
       <c r="AX104" s="15"/>
-      <c r="AY104" s="22"/>
-      <c r="AZ104" s="22"/>
+      <c r="AY104" s="24"/>
+      <c r="AZ104" s="24"/>
       <c r="BA104" s="15"/>
       <c r="BB104" s="15"/>
       <c r="BC104" s="18"/>
       <c r="BD104" s="15"/>
       <c r="BE104" s="18"/>
-      <c r="BF104" s="23"/>
-      <c r="BG104" s="24"/>
-      <c r="BH104" s="24"/>
-      <c r="BI104" s="24"/>
+      <c r="BF104" s="25"/>
+      <c r="BG104" s="26"/>
+      <c r="BH104" s="26"/>
+      <c r="BI104" s="26"/>
       <c r="BJ104" s="38"/>
       <c r="BK104" s="39"/>
     </row>
@@ -9953,25 +9931,25 @@
       <c r="AP105" s="15"/>
       <c r="AQ105" s="20"/>
       <c r="AR105" s="20"/>
-      <c r="AS105" s="22"/>
+      <c r="AS105" s="24"/>
       <c r="AT105" s="15"/>
       <c r="AU105" s="15"/>
       <c r="AV105" s="15"/>
       <c r="AW105" s="15"/>
       <c r="AX105" s="15"/>
-      <c r="AY105" s="22"/>
-      <c r="AZ105" s="22"/>
+      <c r="AY105" s="24"/>
+      <c r="AZ105" s="24"/>
       <c r="BA105" s="15"/>
       <c r="BB105" s="15"/>
       <c r="BC105" s="15"/>
       <c r="BD105" s="15"/>
       <c r="BE105" s="18"/>
       <c r="BF105" s="55"/>
-      <c r="BG105" s="24"/>
-      <c r="BH105" s="24"/>
-      <c r="BI105" s="24"/>
-      <c r="BJ105" s="24"/>
-      <c r="BK105" s="25"/>
+      <c r="BG105" s="26"/>
+      <c r="BH105" s="26"/>
+      <c r="BI105" s="26"/>
+      <c r="BJ105" s="26"/>
+      <c r="BK105" s="27"/>
     </row>
     <row r="106">
       <c r="A106" s="56"/>
@@ -10032,11 +10010,11 @@
       <c r="BD106" s="56"/>
       <c r="BE106" s="62"/>
       <c r="BF106" s="64"/>
-      <c r="BG106" s="24"/>
-      <c r="BH106" s="24"/>
-      <c r="BI106" s="24"/>
-      <c r="BJ106" s="24"/>
-      <c r="BK106" s="25"/>
+      <c r="BG106" s="26"/>
+      <c r="BH106" s="26"/>
+      <c r="BI106" s="26"/>
+      <c r="BJ106" s="26"/>
+      <c r="BK106" s="27"/>
     </row>
     <row r="107">
       <c r="A107" s="65"/>
@@ -10101,7 +10079,7 @@
       <c r="BH107" s="70"/>
       <c r="BI107" s="70"/>
       <c r="BJ107" s="70"/>
-      <c r="BK107" s="25"/>
+      <c r="BK107" s="27"/>
     </row>
     <row r="108">
       <c r="A108" s="56"/>
@@ -10307,7 +10285,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="76" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B1" s="76"/>
       <c r="C1" s="76"/>
@@ -10365,7 +10343,7 @@
     </row>
     <row r="3">
       <c r="A3" s="77" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B3" s="76"/>
       <c r="C3" s="76"/>
@@ -10423,7 +10401,7 @@
     </row>
     <row r="5">
       <c r="A5" s="77" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B5" s="76"/>
       <c r="C5" s="76"/>
@@ -10481,7 +10459,7 @@
     </row>
     <row r="7">
       <c r="A7" s="77" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B7" s="76"/>
       <c r="C7" s="76"/>
@@ -10539,7 +10517,7 @@
     </row>
     <row r="9">
       <c r="A9" s="77" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B9" s="76"/>
       <c r="C9" s="76"/>
@@ -10597,7 +10575,7 @@
     </row>
     <row r="11">
       <c r="A11" s="77" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B11" s="76"/>
       <c r="C11" s="76"/>
@@ -10655,7 +10633,7 @@
     </row>
     <row r="13">
       <c r="A13" s="77" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B13" s="76"/>
       <c r="C13" s="76"/>
@@ -10713,7 +10691,7 @@
     </row>
     <row r="15">
       <c r="A15" s="79" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B15" s="76"/>
       <c r="C15" s="76"/>
@@ -10771,7 +10749,7 @@
     </row>
     <row r="17">
       <c r="A17" s="78" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B17" s="76"/>
       <c r="C17" s="76"/>
@@ -10829,7 +10807,7 @@
     </row>
     <row r="19">
       <c r="A19" s="78" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B19" s="76"/>
       <c r="C19" s="76"/>
@@ -10862,7 +10840,7 @@
       <c r="B20" s="76"/>
       <c r="C20" s="76"/>
       <c r="D20" s="79" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E20" s="76"/>
       <c r="F20" s="76"/>
@@ -10889,7 +10867,7 @@
     </row>
     <row r="21">
       <c r="A21" s="78" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B21" s="76"/>
       <c r="C21" s="76"/>
@@ -10947,7 +10925,7 @@
     </row>
     <row r="23">
       <c r="A23" s="78" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B23" s="76"/>
       <c r="C23" s="76"/>
@@ -11005,7 +10983,7 @@
     </row>
     <row r="25">
       <c r="A25" s="78" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B25" s="76"/>
       <c r="C25" s="76"/>
@@ -11063,7 +11041,7 @@
     </row>
     <row r="27">
       <c r="A27" s="78" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B27" s="76"/>
       <c r="C27" s="76"/>
@@ -38298,25 +38276,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="80" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="80" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="80" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="81" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="80" t="s">
+      <c r="G1" s="82" t="s">
         <v>65</v>
-      </c>
-      <c r="C1" s="80" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="80" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="81" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="81" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="82" t="s">
-        <v>70</v>
       </c>
       <c r="H1" s="83"/>
       <c r="I1" s="83"/>
@@ -38345,19 +38323,19 @@
         <v>46185.0</v>
       </c>
       <c r="C2" s="80" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D2" s="85">
         <v>0.020833333333333332</v>
       </c>
       <c r="E2" s="81" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F2" s="81" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G2" s="82" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
@@ -38386,19 +38364,19 @@
         <v>46185.0</v>
       </c>
       <c r="C3" s="80" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D3" s="85">
         <v>0.3125</v>
       </c>
       <c r="E3" s="81" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F3" s="81" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G3" s="82" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H3" s="83"/>
       <c r="I3" s="83"/>
@@ -38427,19 +38405,19 @@
         <v>46186.0</v>
       </c>
       <c r="C4" s="80" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D4" s="85">
         <v>0.020833333333333332</v>
       </c>
       <c r="E4" s="81" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F4" s="81" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G4" s="82" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
@@ -38468,19 +38446,19 @@
         <v>46186.0</v>
       </c>
       <c r="C5" s="80" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D5" s="85">
         <v>0.2708333333333333</v>
       </c>
       <c r="E5" s="81" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F5" s="81" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G5" s="82" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H5" s="83"/>
       <c r="I5" s="83"/>
@@ -38509,19 +38487,19 @@
         <v>46187.0</v>
       </c>
       <c r="C6" s="80" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D6" s="85">
         <v>0.020833333333333332</v>
       </c>
       <c r="E6" s="81" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F6" s="81" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G6" s="82" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H6" s="83"/>
       <c r="I6" s="83"/>
@@ -38550,19 +38528,19 @@
         <v>46187.0</v>
       </c>
       <c r="C7" s="80" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D7" s="85">
         <v>0.14583333333333334</v>
       </c>
       <c r="E7" s="81" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F7" s="81" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G7" s="82" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H7" s="83"/>
       <c r="I7" s="83"/>
@@ -38591,19 +38569,19 @@
         <v>46187.0</v>
       </c>
       <c r="C8" s="80" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D8" s="85">
         <v>0.2708333333333333</v>
       </c>
       <c r="E8" s="81" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F8" s="81" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G8" s="82" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H8" s="83"/>
       <c r="I8" s="83"/>
@@ -38632,19 +38610,19 @@
         <v>46187.0</v>
       </c>
       <c r="C9" s="80" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D9" s="85">
         <v>0.3958333333333333</v>
       </c>
       <c r="E9" s="81" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F9" s="81" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G9" s="82" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H9" s="83"/>
       <c r="I9" s="83"/>
@@ -38673,19 +38651,19 @@
         <v>46187.0</v>
       </c>
       <c r="C10" s="80" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D10" s="85">
         <v>0.9375</v>
       </c>
       <c r="E10" s="81" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F10" s="81" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G10" s="82" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H10" s="83"/>
       <c r="I10" s="83"/>
@@ -38714,19 +38692,19 @@
         <v>46188.0</v>
       </c>
       <c r="C11" s="80" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D11" s="85">
         <v>0.0625</v>
       </c>
       <c r="E11" s="81" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F11" s="81" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G11" s="82" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H11" s="83"/>
       <c r="I11" s="83"/>
@@ -38755,19 +38733,19 @@
         <v>46188.0</v>
       </c>
       <c r="C12" s="80" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D12" s="85">
         <v>0.1875</v>
       </c>
       <c r="E12" s="81" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F12" s="81" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G12" s="82" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H12" s="83"/>
       <c r="I12" s="83"/>
@@ -38796,19 +38774,19 @@
         <v>46188.0</v>
       </c>
       <c r="C13" s="80" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D13" s="85">
         <v>0.3125</v>
       </c>
       <c r="E13" s="81" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F13" s="81" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G13" s="82" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H13" s="83"/>
       <c r="I13" s="83"/>
@@ -38837,19 +38815,19 @@
         <v>46188.0</v>
       </c>
       <c r="C14" s="80" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D14" s="85">
         <v>0.8958333333333334</v>
       </c>
       <c r="E14" s="81" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F14" s="81" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G14" s="82" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H14" s="83"/>
       <c r="I14" s="83"/>
@@ -38878,19 +38856,19 @@
         <v>46189.0</v>
       </c>
       <c r="C15" s="80" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D15" s="85">
         <v>0.020833333333333332</v>
       </c>
       <c r="E15" s="81" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F15" s="81" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G15" s="82" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H15" s="83"/>
       <c r="I15" s="83"/>
@@ -38919,19 +38897,19 @@
         <v>46189.0</v>
       </c>
       <c r="C16" s="80" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D16" s="85">
         <v>0.14583333333333334</v>
       </c>
       <c r="E16" s="81" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F16" s="81" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G16" s="82" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H16" s="83"/>
       <c r="I16" s="83"/>
@@ -38960,19 +38938,19 @@
         <v>46189.0</v>
       </c>
       <c r="C17" s="80" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D17" s="85">
         <v>0.2708333333333333</v>
       </c>
       <c r="E17" s="81" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F17" s="81" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G17" s="82" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H17" s="83"/>
       <c r="I17" s="83"/>
@@ -39001,19 +38979,19 @@
         <v>46190.0</v>
       </c>
       <c r="C18" s="80" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D18" s="85">
         <v>0.020833333333333332</v>
       </c>
       <c r="E18" s="81" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F18" s="81" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G18" s="82" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H18" s="83"/>
       <c r="I18" s="83"/>
@@ -39042,19 +39020,19 @@
         <v>46190.0</v>
       </c>
       <c r="C19" s="80" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D19" s="85">
         <v>0.14583333333333334</v>
       </c>
       <c r="E19" s="81" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F19" s="81" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G19" s="82" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H19" s="83"/>
       <c r="I19" s="83"/>
@@ -39083,19 +39061,19 @@
         <v>46190.0</v>
       </c>
       <c r="C20" s="80" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D20" s="85">
         <v>0.2708333333333333</v>
       </c>
       <c r="E20" s="81" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F20" s="81" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G20" s="82" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H20" s="83"/>
       <c r="I20" s="83"/>
@@ -39124,19 +39102,19 @@
         <v>46190.0</v>
       </c>
       <c r="C21" s="80" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D21" s="85">
         <v>0.3958333333333333</v>
       </c>
       <c r="E21" s="81" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F21" s="81" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G21" s="82" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H21" s="83"/>
       <c r="I21" s="83"/>
@@ -39165,16 +39143,16 @@
         <v>46190.0</v>
       </c>
       <c r="C22" s="80" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D22" s="85">
         <v>0.9375</v>
       </c>
       <c r="E22" s="81" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F22" s="81" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G22" s="83"/>
       <c r="H22" s="83"/>
@@ -39204,16 +39182,16 @@
         <v>46191.0</v>
       </c>
       <c r="C23" s="80" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D23" s="85">
         <v>0.0625</v>
       </c>
       <c r="E23" s="81" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F23" s="81" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G23" s="83"/>
       <c r="H23" s="83"/>
@@ -39243,16 +39221,16 @@
         <v>46191.0</v>
       </c>
       <c r="C24" s="80" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D24" s="85">
         <v>0.1875</v>
       </c>
       <c r="E24" s="81" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F24" s="81" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G24" s="83"/>
       <c r="H24" s="83"/>
@@ -39282,16 +39260,16 @@
         <v>46191.0</v>
       </c>
       <c r="C25" s="80" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D25" s="85">
         <v>0.3125</v>
       </c>
       <c r="E25" s="81" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F25" s="81" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G25" s="83"/>
       <c r="H25" s="83"/>
@@ -39321,16 +39299,16 @@
         <v>46191.0</v>
       </c>
       <c r="C26" s="80" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D26" s="85">
         <v>0.8958333333333334</v>
       </c>
       <c r="E26" s="81" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F26" s="81" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G26" s="83"/>
       <c r="H26" s="83"/>
@@ -39360,16 +39338,16 @@
         <v>46192.0</v>
       </c>
       <c r="C27" s="80" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D27" s="85">
         <v>0.020833333333333332</v>
       </c>
       <c r="E27" s="81" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F27" s="81" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G27" s="83"/>
       <c r="H27" s="83"/>
@@ -39399,16 +39377,16 @@
         <v>46192.0</v>
       </c>
       <c r="C28" s="80" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D28" s="85">
         <v>0.14583333333333334</v>
       </c>
       <c r="E28" s="81" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F28" s="81" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G28" s="83"/>
       <c r="H28" s="83"/>
@@ -39438,16 +39416,16 @@
         <v>46192.0</v>
       </c>
       <c r="C29" s="80" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D29" s="85">
         <v>0.2708333333333333</v>
       </c>
       <c r="E29" s="81" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F29" s="81" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G29" s="83"/>
       <c r="H29" s="83"/>
@@ -39477,16 +39455,16 @@
         <v>46193.0</v>
       </c>
       <c r="C30" s="80" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D30" s="85">
         <v>0.020833333333333332</v>
       </c>
       <c r="E30" s="81" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F30" s="81" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G30" s="83"/>
       <c r="H30" s="83"/>
@@ -39516,16 +39494,16 @@
         <v>46193.0</v>
       </c>
       <c r="C31" s="80" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D31" s="85">
         <v>0.14583333333333334</v>
       </c>
       <c r="E31" s="81" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F31" s="81" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G31" s="83"/>
       <c r="H31" s="83"/>
@@ -39555,16 +39533,16 @@
         <v>46193.0</v>
       </c>
       <c r="C32" s="80" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D32" s="85">
         <v>0.25</v>
       </c>
       <c r="E32" s="81" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F32" s="81" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G32" s="83"/>
       <c r="H32" s="83"/>
@@ -39594,16 +39572,16 @@
         <v>46193.0</v>
       </c>
       <c r="C33" s="80" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D33" s="85">
         <v>0.3541666666666667</v>
       </c>
       <c r="E33" s="81" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F33" s="81" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G33" s="83"/>
       <c r="H33" s="83"/>
@@ -39633,16 +39611,16 @@
         <v>46193.0</v>
       </c>
       <c r="C34" s="80" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D34" s="85">
         <v>0.9375</v>
       </c>
       <c r="E34" s="81" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F34" s="81" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G34" s="83"/>
       <c r="H34" s="83"/>
@@ -39672,16 +39650,16 @@
         <v>46194.0</v>
       </c>
       <c r="C35" s="80" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D35" s="85">
         <v>0.0625</v>
       </c>
       <c r="E35" s="81" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F35" s="81" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G35" s="83"/>
       <c r="H35" s="83"/>
@@ -39711,16 +39689,16 @@
         <v>46194.0</v>
       </c>
       <c r="C36" s="80" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D36" s="85">
         <v>0.22916666666666666</v>
       </c>
       <c r="E36" s="81" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F36" s="81" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G36" s="83"/>
       <c r="H36" s="83"/>
@@ -39750,16 +39728,16 @@
         <v>46194.0</v>
       </c>
       <c r="C37" s="80" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D37" s="85">
         <v>0.3958333333333333</v>
       </c>
       <c r="E37" s="81" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F37" s="81" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G37" s="83"/>
       <c r="H37" s="83"/>
@@ -39789,16 +39767,16 @@
         <v>46194.0</v>
       </c>
       <c r="C38" s="80" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D38" s="85">
         <v>0.8958333333333334</v>
       </c>
       <c r="E38" s="81" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F38" s="81" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G38" s="83"/>
       <c r="H38" s="83"/>
@@ -39828,16 +39806,16 @@
         <v>46195.0</v>
       </c>
       <c r="C39" s="80" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D39" s="85">
         <v>0.020833333333333332</v>
       </c>
       <c r="E39" s="81" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F39" s="81" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G39" s="83"/>
       <c r="H39" s="83"/>
@@ -39867,16 +39845,16 @@
         <v>46195.0</v>
       </c>
       <c r="C40" s="80" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D40" s="85">
         <v>0.14583333333333334</v>
       </c>
       <c r="E40" s="81" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F40" s="81" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G40" s="83"/>
       <c r="H40" s="83"/>
@@ -39906,16 +39884,16 @@
         <v>46195.0</v>
       </c>
       <c r="C41" s="80" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D41" s="85">
         <v>0.2708333333333333</v>
       </c>
       <c r="E41" s="81" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F41" s="81" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G41" s="83"/>
       <c r="H41" s="83"/>
@@ -39945,16 +39923,16 @@
         <v>46195.0</v>
       </c>
       <c r="C42" s="80" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D42" s="85">
         <v>0.9375</v>
       </c>
       <c r="E42" s="81" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="F42" s="81" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G42" s="83"/>
       <c r="H42" s="83"/>
@@ -39984,16 +39962,16 @@
         <v>46196.0</v>
       </c>
       <c r="C43" s="80" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D43" s="85">
         <v>0.10416666666666667</v>
       </c>
       <c r="E43" s="81" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F43" s="81" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G43" s="83"/>
       <c r="H43" s="83"/>
@@ -40023,16 +40001,16 @@
         <v>46196.0</v>
       </c>
       <c r="C44" s="80" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D44" s="85">
         <v>0.22916666666666666</v>
       </c>
       <c r="E44" s="81" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F44" s="81" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G44" s="83"/>
       <c r="H44" s="83"/>
@@ -40062,16 +40040,16 @@
         <v>46196.0</v>
       </c>
       <c r="C45" s="80" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D45" s="85">
         <v>0.3541666666666667</v>
       </c>
       <c r="E45" s="81" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F45" s="81" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G45" s="83"/>
       <c r="H45" s="83"/>
@@ -40101,16 +40079,16 @@
         <v>46196.0</v>
       </c>
       <c r="C46" s="80" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D46" s="85">
         <v>0.9375</v>
       </c>
       <c r="E46" s="81" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F46" s="81" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G46" s="83"/>
       <c r="H46" s="83"/>
@@ -40140,16 +40118,16 @@
         <v>46197.0</v>
       </c>
       <c r="C47" s="80" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D47" s="85">
         <v>0.0625</v>
       </c>
       <c r="E47" s="81" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F47" s="81" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G47" s="83"/>
       <c r="H47" s="83"/>
@@ -40179,16 +40157,16 @@
         <v>46197.0</v>
       </c>
       <c r="C48" s="80" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D48" s="85">
         <v>0.1875</v>
       </c>
       <c r="E48" s="81" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F48" s="81" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G48" s="83"/>
       <c r="H48" s="83"/>
@@ -40218,16 +40196,16 @@
         <v>46197.0</v>
       </c>
       <c r="C49" s="80" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D49" s="85">
         <v>0.3125</v>
       </c>
       <c r="E49" s="81" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F49" s="81" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G49" s="83"/>
       <c r="H49" s="83"/>
@@ -40257,16 +40235,16 @@
         <v>46198.0</v>
       </c>
       <c r="C50" s="80" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D50" s="85">
         <v>0.020833333333333332</v>
       </c>
       <c r="E50" s="81" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F50" s="81" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G50" s="83"/>
       <c r="H50" s="83"/>
@@ -40296,16 +40274,16 @@
         <v>46198.0</v>
       </c>
       <c r="C51" s="80" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D51" s="85">
         <v>0.020833333333333332</v>
       </c>
       <c r="E51" s="81" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F51" s="81" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G51" s="83"/>
       <c r="H51" s="83"/>
@@ -40335,16 +40313,16 @@
         <v>46198.0</v>
       </c>
       <c r="C52" s="80" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D52" s="85">
         <v>0.14583333333333334</v>
       </c>
       <c r="E52" s="81" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F52" s="81" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G52" s="83"/>
       <c r="H52" s="83"/>
@@ -40374,16 +40352,16 @@
         <v>46198.0</v>
       </c>
       <c r="C53" s="80" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D53" s="85">
         <v>0.14583333333333334</v>
       </c>
       <c r="E53" s="81" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F53" s="81" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G53" s="83"/>
       <c r="H53" s="83"/>
@@ -40413,16 +40391,16 @@
         <v>46198.0</v>
       </c>
       <c r="C54" s="80" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D54" s="85">
         <v>0.2708333333333333</v>
       </c>
       <c r="E54" s="81" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F54" s="81" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G54" s="83"/>
       <c r="H54" s="83"/>
@@ -40452,16 +40430,16 @@
         <v>46198.0</v>
       </c>
       <c r="C55" s="80" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D55" s="85">
         <v>0.2708333333333333</v>
       </c>
       <c r="E55" s="81" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F55" s="81" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G55" s="83"/>
       <c r="H55" s="83"/>
@@ -40491,16 +40469,16 @@
         <v>46199.0</v>
       </c>
       <c r="C56" s="80" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D56" s="85">
         <v>0.0625</v>
       </c>
       <c r="E56" s="81" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F56" s="81" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G56" s="83"/>
       <c r="H56" s="83"/>
@@ -40530,16 +40508,16 @@
         <v>46199.0</v>
       </c>
       <c r="C57" s="80" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D57" s="85">
         <v>0.0625</v>
       </c>
       <c r="E57" s="81" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="F57" s="81" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G57" s="83"/>
       <c r="H57" s="83"/>
@@ -40569,16 +40547,16 @@
         <v>46199.0</v>
       </c>
       <c r="C58" s="80" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D58" s="85">
         <v>0.1875</v>
       </c>
       <c r="E58" s="81" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F58" s="81" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G58" s="83"/>
       <c r="H58" s="83"/>
@@ -40608,16 +40586,16 @@
         <v>46199.0</v>
       </c>
       <c r="C59" s="80" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D59" s="85">
         <v>0.1875</v>
       </c>
       <c r="E59" s="81" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="F59" s="81" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G59" s="83"/>
       <c r="H59" s="83"/>
@@ -40647,16 +40625,16 @@
         <v>46199.0</v>
       </c>
       <c r="C60" s="80" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D60" s="85">
         <v>0.3125</v>
       </c>
       <c r="E60" s="81" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F60" s="81" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G60" s="83"/>
       <c r="H60" s="83"/>
@@ -40686,16 +40664,16 @@
         <v>46199.0</v>
       </c>
       <c r="C61" s="80" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D61" s="85">
         <v>0.3125</v>
       </c>
       <c r="E61" s="81" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F61" s="81" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G61" s="83"/>
       <c r="H61" s="83"/>
@@ -40725,16 +40703,16 @@
         <v>46200.0</v>
       </c>
       <c r="C62" s="80" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D62" s="85">
         <v>0.020833333333333332</v>
       </c>
       <c r="E62" s="81" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F62" s="81" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G62" s="83"/>
       <c r="H62" s="83"/>
@@ -40764,16 +40742,16 @@
         <v>46200.0</v>
       </c>
       <c r="C63" s="80" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D63" s="85">
         <v>0.020833333333333332</v>
       </c>
       <c r="E63" s="81" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F63" s="81" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G63" s="83"/>
       <c r="H63" s="83"/>
@@ -40803,16 +40781,16 @@
         <v>46200.0</v>
       </c>
       <c r="C64" s="86" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D64" s="88">
         <v>0.22916666666666666</v>
       </c>
       <c r="E64" s="86" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="F64" s="86" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G64" s="83"/>
       <c r="H64" s="83"/>
@@ -40842,16 +40820,16 @@
         <v>46200.0</v>
       </c>
       <c r="C65" s="89" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D65" s="91">
         <v>0.22916666666666666</v>
       </c>
       <c r="E65" s="89" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F65" s="89" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G65" s="83"/>
       <c r="H65" s="83"/>
@@ -40881,16 +40859,16 @@
         <v>46200.0</v>
       </c>
       <c r="C66" s="86" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D66" s="88">
         <v>0.3541666666666667</v>
       </c>
       <c r="E66" s="86" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F66" s="86" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G66" s="83"/>
       <c r="H66" s="83"/>
@@ -40920,16 +40898,16 @@
         <v>46200.0</v>
       </c>
       <c r="C67" s="89" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D67" s="91">
         <v>0.3541666666666667</v>
       </c>
       <c r="E67" s="89" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F67" s="89" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G67" s="83"/>
       <c r="H67" s="83"/>
@@ -40959,16 +40937,16 @@
         <v>46201.0</v>
       </c>
       <c r="C68" s="82" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D68" s="93">
         <v>0.10416666666666667</v>
       </c>
       <c r="E68" s="82" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F68" s="82" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G68" s="83"/>
       <c r="H68" s="83"/>
@@ -40998,16 +40976,16 @@
         <v>46201.0</v>
       </c>
       <c r="C69" s="82" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D69" s="93">
         <v>0.10416666666666667</v>
       </c>
       <c r="E69" s="82" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F69" s="82" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G69" s="83"/>
       <c r="H69" s="83"/>
@@ -41037,16 +41015,16 @@
         <v>46201.0</v>
       </c>
       <c r="C70" s="82" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D70" s="93">
         <v>0.20833333333333334</v>
       </c>
       <c r="E70" s="82" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F70" s="82" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G70" s="83"/>
       <c r="H70" s="83"/>
@@ -41076,16 +41054,16 @@
         <v>46201.0</v>
       </c>
       <c r="C71" s="82" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D71" s="93">
         <v>0.20833333333333334</v>
       </c>
       <c r="E71" s="82" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F71" s="82" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G71" s="83"/>
       <c r="H71" s="83"/>
@@ -41115,16 +41093,16 @@
         <v>46201.0</v>
       </c>
       <c r="C72" s="82" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D72" s="93">
         <v>0.3125</v>
       </c>
       <c r="E72" s="82" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F72" s="82" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G72" s="83"/>
       <c r="H72" s="83"/>
@@ -41154,16 +41132,16 @@
         <v>46201.0</v>
       </c>
       <c r="C73" s="82" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D73" s="93">
         <v>0.3125</v>
       </c>
       <c r="E73" s="82" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F73" s="82" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G73" s="83"/>
       <c r="H73" s="83"/>
@@ -41193,16 +41171,16 @@
         <v>46202.0</v>
       </c>
       <c r="C74" s="82" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D74" s="93">
         <v>0.020833333333333332</v>
       </c>
       <c r="E74" s="82" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F74" s="82" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G74" s="83"/>
       <c r="H74" s="83"/>
@@ -41232,16 +41210,16 @@
         <v>46202.0</v>
       </c>
       <c r="C75" s="82" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D75" s="93">
         <v>0.9375</v>
       </c>
       <c r="E75" s="82" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F75" s="82" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G75" s="83"/>
       <c r="H75" s="83"/>
@@ -41271,16 +41249,16 @@
         <v>46203.0</v>
       </c>
       <c r="C76" s="82" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D76" s="93">
         <v>0.08333333333333333</v>
       </c>
       <c r="E76" s="82" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F76" s="82" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G76" s="83"/>
       <c r="H76" s="83"/>
@@ -41310,16 +41288,16 @@
         <v>46203.0</v>
       </c>
       <c r="C77" s="82" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D77" s="93">
         <v>0.2708333333333333</v>
       </c>
       <c r="E77" s="82" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F77" s="82" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G77" s="83"/>
       <c r="H77" s="83"/>
@@ -41349,16 +41327,16 @@
         <v>46203.0</v>
       </c>
       <c r="C78" s="82" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D78" s="93">
         <v>0.9375</v>
       </c>
       <c r="E78" s="82" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F78" s="82" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G78" s="83"/>
       <c r="H78" s="83"/>
@@ -41388,16 +41366,16 @@
         <v>46204.0</v>
       </c>
       <c r="C79" s="82" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D79" s="93">
         <v>0.10416666666666667</v>
       </c>
       <c r="E79" s="82" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F79" s="82" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G79" s="83"/>
       <c r="H79" s="83"/>
@@ -41427,16 +41405,16 @@
         <v>46204.0</v>
       </c>
       <c r="C80" s="82" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D80" s="93">
         <v>0.2708333333333333</v>
       </c>
       <c r="E80" s="82" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F80" s="82" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G80" s="83"/>
       <c r="H80" s="83"/>
@@ -41466,16 +41444,16 @@
         <v>46204.0</v>
       </c>
       <c r="C81" s="82" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D81" s="93">
         <v>0.8958333333333334</v>
       </c>
       <c r="E81" s="82" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="F81" s="82" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G81" s="83"/>
       <c r="H81" s="83"/>
@@ -41505,16 +41483,16 @@
         <v>46205.0</v>
       </c>
       <c r="C82" s="82" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D82" s="93">
         <v>0.0625</v>
       </c>
       <c r="E82" s="82" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F82" s="82" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G82" s="83"/>
       <c r="H82" s="83"/>
@@ -41544,16 +41522,16 @@
         <v>46205.0</v>
       </c>
       <c r="C83" s="82" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D83" s="93">
         <v>0.0625</v>
       </c>
       <c r="E83" s="82" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F83" s="82" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G83" s="83"/>
       <c r="H83" s="83"/>
@@ -41583,16 +41561,16 @@
         <v>46205.0</v>
       </c>
       <c r="C84" s="82" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D84" s="93">
         <v>0.22916666666666666</v>
       </c>
       <c r="E84" s="82" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F84" s="82" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G84" s="83"/>
       <c r="H84" s="83"/>
@@ -41622,16 +41600,16 @@
         <v>46206.0</v>
       </c>
       <c r="C85" s="82" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D85" s="93">
         <v>0.020833333333333332</v>
       </c>
       <c r="E85" s="82" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F85" s="82" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G85" s="83"/>
       <c r="H85" s="83"/>
@@ -41661,16 +41639,16 @@
         <v>46206.0</v>
       </c>
       <c r="C86" s="82" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D86" s="93">
         <v>0.1875</v>
       </c>
       <c r="E86" s="82" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F86" s="82" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G86" s="83"/>
       <c r="H86" s="83"/>
@@ -41700,16 +41678,16 @@
         <v>46206.0</v>
       </c>
       <c r="C87" s="82" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D87" s="93">
         <v>0.3541666666666667</v>
       </c>
       <c r="E87" s="82" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F87" s="82" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G87" s="83"/>
       <c r="H87" s="83"/>
@@ -41739,16 +41717,16 @@
         <v>46206.0</v>
       </c>
       <c r="C88" s="82" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D88" s="93">
         <v>0.9791666666666666</v>
       </c>
       <c r="E88" s="82" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F88" s="82" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G88" s="83"/>
       <c r="H88" s="83"/>
@@ -41778,16 +41756,16 @@
         <v>46207.0</v>
       </c>
       <c r="C89" s="82" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D89" s="93">
         <v>0.14583333333333334</v>
       </c>
       <c r="E89" s="82" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F89" s="82" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G89" s="83"/>
       <c r="H89" s="83"/>
@@ -41817,16 +41795,16 @@
         <v>46207.0</v>
       </c>
       <c r="C90" s="82" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D90" s="93">
         <v>0.2916666666666667</v>
       </c>
       <c r="E90" s="82" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F90" s="82" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G90" s="83"/>
       <c r="H90" s="83"/>
@@ -41856,16 +41834,16 @@
         <v>46207.0</v>
       </c>
       <c r="C91" s="82" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D91" s="93">
         <v>0.9375</v>
       </c>
       <c r="E91" s="82" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F91" s="82" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G91" s="83"/>
       <c r="H91" s="83"/>
@@ -41895,16 +41873,16 @@
         <v>46208.0</v>
       </c>
       <c r="C92" s="82" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D92" s="93">
         <v>0.10416666666666667</v>
       </c>
       <c r="E92" s="82" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F92" s="82" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G92" s="83"/>
       <c r="H92" s="83"/>
@@ -41934,16 +41912,16 @@
         <v>46209.0</v>
       </c>
       <c r="C93" s="82" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D93" s="93">
         <v>0.0625</v>
       </c>
       <c r="E93" s="82" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F93" s="82" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G93" s="83"/>
       <c r="H93" s="83"/>
@@ -41973,16 +41951,16 @@
         <v>46209.0</v>
       </c>
       <c r="C94" s="82" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D94" s="93">
         <v>0.22916666666666666</v>
       </c>
       <c r="E94" s="82" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F94" s="82" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G94" s="83"/>
       <c r="H94" s="83"/>
@@ -42012,16 +41990,16 @@
         <v>46210.0</v>
       </c>
       <c r="C95" s="82" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D95" s="93">
         <v>0.0625</v>
       </c>
       <c r="E95" s="82" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F95" s="82" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G95" s="83"/>
       <c r="H95" s="83"/>
@@ -42051,16 +42029,16 @@
         <v>46210.0</v>
       </c>
       <c r="C96" s="82" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D96" s="93">
         <v>0.8958333333333334</v>
       </c>
       <c r="E96" s="82" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F96" s="82" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G96" s="83"/>
       <c r="H96" s="83"/>
@@ -42090,16 +42068,16 @@
         <v>46211.0</v>
       </c>
       <c r="C97" s="82" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D97" s="93">
         <v>0.0625</v>
       </c>
       <c r="E97" s="82" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F97" s="82" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G97" s="83"/>
       <c r="H97" s="83"/>
@@ -42129,16 +42107,16 @@
         <v>46213.0</v>
       </c>
       <c r="C98" s="82" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D98" s="93">
         <v>0.0625</v>
       </c>
       <c r="E98" s="82" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F98" s="82" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G98" s="83"/>
       <c r="H98" s="83"/>
@@ -42168,16 +42146,16 @@
         <v>46214.0</v>
       </c>
       <c r="C99" s="82" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D99" s="93">
         <v>0.020833333333333332</v>
       </c>
       <c r="E99" s="82" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="F99" s="82" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G99" s="83"/>
       <c r="H99" s="83"/>
@@ -42207,16 +42185,16 @@
         <v>46215.0</v>
       </c>
       <c r="C100" s="82" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D100" s="93">
         <v>0.10416666666666667</v>
       </c>
       <c r="E100" s="82" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F100" s="82" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G100" s="83"/>
       <c r="H100" s="83"/>
@@ -42246,16 +42224,16 @@
         <v>46215.0</v>
       </c>
       <c r="C101" s="82" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D101" s="93">
         <v>0.2708333333333333</v>
       </c>
       <c r="E101" s="82" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F101" s="82" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G101" s="83"/>
       <c r="H101" s="83"/>
@@ -42285,16 +42263,16 @@
         <v>46218.0</v>
       </c>
       <c r="C102" s="82" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D102" s="93">
         <v>0.020833333333333332</v>
       </c>
       <c r="E102" s="82" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F102" s="82" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G102" s="83"/>
       <c r="H102" s="83"/>
@@ -42324,16 +42302,16 @@
         <v>46219.0</v>
       </c>
       <c r="C103" s="82" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D103" s="93">
         <v>0.020833333333333332</v>
       </c>
       <c r="E103" s="82" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F103" s="82" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G103" s="83"/>
       <c r="H103" s="83"/>
@@ -42363,16 +42341,16 @@
         <v>46222.0</v>
       </c>
       <c r="C104" s="82" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D104" s="93">
         <v>0.10416666666666667</v>
       </c>
       <c r="E104" s="82" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F104" s="82" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G104" s="83"/>
       <c r="H104" s="83"/>
@@ -42402,16 +42380,16 @@
         <v>46223.0</v>
       </c>
       <c r="C105" s="82" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D105" s="93">
         <v>0.020833333333333332</v>
       </c>
       <c r="E105" s="82" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F105" s="89" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G105" s="83"/>
       <c r="H105" s="83"/>
@@ -66532,28 +66510,28 @@
     <row r="1">
       <c r="A1" s="94"/>
       <c r="B1" s="95" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C1" s="96"/>
     </row>
     <row r="2">
       <c r="A2" s="94" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B2" s="95" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C2" s="33"/>
     </row>
     <row r="3">
       <c r="A3" s="97" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B3" s="73" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4">
@@ -66562,10 +66540,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C4" s="16">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="5">
@@ -66574,10 +66552,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C5" s="16">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="6">
@@ -66586,10 +66564,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C6" s="16">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="7">
@@ -66598,10 +66576,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C7" s="16">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="8">
@@ -66610,10 +66588,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C8" s="16">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="9">
@@ -66622,10 +66600,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" s="16">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="10">
@@ -66634,10 +66612,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C10" s="16">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="11">
@@ -66646,10 +66624,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C11" s="16">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="12">
@@ -66658,10 +66636,10 @@
         <v>4</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C12" s="16">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="13">
@@ -66673,7 +66651,7 @@
         <v>34</v>
       </c>
       <c r="C13" s="16">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="14">
@@ -66682,46 +66660,46 @@
         <v>4</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C14" s="16">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="97">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>41</v>
       </c>
       <c r="C15" s="16">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="97">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C16" s="16">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="97">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C17" s="16">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="18">
@@ -66730,10 +66708,10 @@
         <v>7</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C18" s="16">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="19">
@@ -66742,10 +66720,10 @@
         <v>7</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C19" s="16">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="20">
@@ -66754,10 +66732,10 @@
         <v>7</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C20" s="16">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="21">
@@ -66766,10 +66744,10 @@
         <v>8</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C21" s="16">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="22">
@@ -66778,10 +66756,10 @@
         <v>8</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C22" s="16">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="23">
@@ -66790,10 +66768,10 @@
         <v>8</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C23" s="16">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="24">
@@ -66802,10 +66780,10 @@
         <v>8</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C24" s="16">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="25">
@@ -66814,10 +66792,10 @@
         <v>8</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C25" s="16">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="26">
@@ -66826,10 +66804,10 @@
         <v>9</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C26" s="16">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="27">
@@ -66838,10 +66816,10 @@
         <v>9</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C27" s="16">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="28">
@@ -66850,10 +66828,10 @@
         <v>10</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C28" s="16">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="29">
@@ -66862,10 +66840,10 @@
         <v>10</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C29" s="16">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="30">
@@ -66874,10 +66852,10 @@
         <v>11</v>
       </c>
       <c r="B30" s="44" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C30" s="16">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="31">
@@ -66886,10 +66864,10 @@
         <v>12</v>
       </c>
       <c r="B31" s="44" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C31" s="16">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="32">
@@ -66898,7 +66876,7 @@
         <v>13</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C32" s="16">
         <v>11.0</v>
@@ -66910,7 +66888,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C33" s="16">
         <v>8.0</v>
